--- a/docs/data/jp/xlsx/3778.xlsx
+++ b/docs/data/jp/xlsx/3778.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC211"/>
+  <dimension ref="A1:AC218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4383,10 +4386,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>2927</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4421,7 +4426,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>41890700</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5620,7 +5627,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5872,1326 +5879,1375 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>3884.069</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>3929.928</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>4457.149</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>4236.884</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>4685.563</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>5159.102</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>6100.555</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>5948.216</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>6534.127</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>6504.314</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>8358.476000000001</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>7713.234</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>4032.635</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>4032.751</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>4457.149</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>6100.555</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>8358.476000000001</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>1353.442</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>1385.901</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>1710.647</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>1698.9</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>2650.323</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>2966.284</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>3914.771</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>1543.935</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>1604.883</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1889.092</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>2918.605</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>3421.363</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>1364.087</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>1546.199</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>1710.647</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>3914.771</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>2918.605</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 전입</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>1.108</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>1.976</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>-0.201</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>3.618</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>-1.174</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>1.108</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>0.505</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>급여·수당</t>
-        </is>
-      </c>
-      <c r="C82" s="22" t="n">
-        <v>352.304</v>
-      </c>
-      <c r="D82" s="22" t="n">
-        <v>490.886</v>
-      </c>
-      <c r="E82" s="22" t="n">
-        <v>368.378</v>
-      </c>
-      <c r="F82" s="22" t="n">
-        <v>453.048</v>
-      </c>
-      <c r="G82" s="22" t="n">
-        <v>465.006</v>
-      </c>
-      <c r="H82" s="22" t="n">
-        <v>656.981</v>
-      </c>
-      <c r="I82" s="22" t="n">
-        <v>607.722</v>
-      </c>
-      <c r="J82" s="22" t="n">
-        <v>615.433</v>
-      </c>
-      <c r="K82" s="22" t="n">
-        <v>679.801</v>
-      </c>
-      <c r="L82" s="22" t="n">
-        <v>925.864</v>
-      </c>
-      <c r="M82" s="22" t="n">
-        <v>715.853</v>
-      </c>
-      <c r="N82" s="22" t="n">
-        <v>796.379</v>
-      </c>
-      <c r="T82" s="22" t="n">
-        <v>289.519</v>
-      </c>
-      <c r="U82" s="22" t="n">
-        <v>328.029</v>
-      </c>
-      <c r="V82" s="22" t="n">
-        <v>368.378</v>
-      </c>
-      <c r="W82" s="22" t="n">
-        <v>607.722</v>
-      </c>
-      <c r="X82" s="22" t="n">
-        <v>715.853</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 전입</t>
+          <t>대손충당금 전입</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>78.821</v>
+        <v>0.577</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>-59.454</v>
+        <v>0.316</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>67.70399999999999</v>
+        <v>-0.49</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>92.941</v>
+        <v>0.984</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>88.996</v>
+        <v>0.332</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>-70.34999999999999</v>
+        <v>0.345</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>178.681</v>
+        <v>1.108</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>124.814</v>
+        <v>1.976</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>162.47</v>
+        <v>-0.201</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>-129.591</v>
+        <v>3.618</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>179.255</v>
+        <v>0.505</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>159.367</v>
+        <v>0.043</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>61.683</v>
+        <v>0.005</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>69.19199999999999</v>
+        <v>-1.174</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>67.70399999999999</v>
+        <v>-0.49</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>178.681</v>
+        <v>1.108</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>179.255</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>임원 퇴직위로 충당금 전입</t>
-        </is>
+          <t>급여·수당</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="n">
+        <v>352.304</v>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>490.886</v>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>368.378</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>0</v>
+        <v>453.048</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>0</v>
+        <v>465.006</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>0</v>
+        <v>656.981</v>
       </c>
       <c r="I84" s="22" t="n">
-        <v>50.638</v>
+        <v>607.722</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>12.802</v>
+        <v>615.433</v>
       </c>
       <c r="K84" s="22" t="n">
-        <v>2.446</v>
+        <v>679.801</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>2.446</v>
+        <v>925.864</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>2.447</v>
+        <v>715.853</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>14.446</v>
+        <v>796.379</v>
+      </c>
+      <c r="T84" s="22" t="n">
+        <v>289.519</v>
+      </c>
+      <c r="U84" s="22" t="n">
+        <v>328.029</v>
+      </c>
+      <c r="V84" s="22" t="n">
+        <v>368.378</v>
       </c>
       <c r="W84" s="22" t="n">
-        <v>50.638</v>
+        <v>607.722</v>
       </c>
       <c r="X84" s="22" t="n">
-        <v>2.447</v>
+        <v>715.853</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여비용</t>
-        </is>
+          <t>상여충당금 전입</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="n">
+        <v>78.821</v>
+      </c>
+      <c r="D85" s="22" t="n">
+        <v>-59.454</v>
+      </c>
+      <c r="E85" s="22" t="n">
+        <v>67.70399999999999</v>
+      </c>
+      <c r="F85" s="22" t="n">
+        <v>92.941</v>
+      </c>
+      <c r="G85" s="22" t="n">
+        <v>88.996</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>0</v>
+        <v>-70.34999999999999</v>
       </c>
       <c r="I85" s="22" t="n">
-        <v>30</v>
+        <v>178.681</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>0</v>
+        <v>124.814</v>
       </c>
       <c r="K85" s="22" t="n">
-        <v>1.5</v>
+        <v>162.47</v>
       </c>
       <c r="L85" s="22" t="n">
-        <v>0.75</v>
+        <v>-129.591</v>
       </c>
       <c r="M85" s="22" t="n">
-        <v>0.8</v>
+        <v>179.255</v>
       </c>
       <c r="N85" s="22" t="n">
-        <v>0.9</v>
+        <v>159.367</v>
+      </c>
+      <c r="T85" s="22" t="n">
+        <v>61.683</v>
+      </c>
+      <c r="U85" s="22" t="n">
+        <v>69.19199999999999</v>
+      </c>
+      <c r="V85" s="22" t="n">
+        <v>67.70399999999999</v>
       </c>
       <c r="W85" s="22" t="n">
-        <v>30</v>
+        <v>178.681</v>
       </c>
       <c r="X85" s="22" t="n">
-        <v>0.8</v>
+        <v>179.255</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>임원 퇴직위로 충당금 전입</t>
         </is>
       </c>
       <c r="F86" s="22" t="n">
-        <v>305.837</v>
+        <v>0</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>356.703</v>
+        <v>0</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>361.766</v>
+        <v>0</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>432.686</v>
+        <v>50.638</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>450.458</v>
+        <v>12.802</v>
       </c>
       <c r="K86" s="22" t="n">
-        <v>361.404</v>
+        <v>2.446</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>385.465</v>
+        <v>2.446</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>413.389</v>
+        <v>2.447</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>330.858</v>
+        <v>14.446</v>
       </c>
       <c r="W86" s="22" t="n">
-        <v>432.686</v>
+        <v>50.638</v>
       </c>
       <c r="X86" s="22" t="n">
-        <v>413.389</v>
+        <v>2.447</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C87" s="22" t="n">
-        <v>776.659</v>
-      </c>
-      <c r="D87" s="22" t="n">
-        <v>755.061</v>
-      </c>
-      <c r="E87" s="22" t="n">
-        <v>-429.901</v>
-      </c>
-      <c r="F87" s="22" t="n">
-        <v>614.321</v>
-      </c>
-      <c r="G87" s="22" t="n">
-        <v>675.165</v>
+          <t>퇴직급여비용</t>
+        </is>
       </c>
       <c r="H87" s="22" t="n">
-        <v>728.013</v>
+        <v>0</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>714.141</v>
+        <v>30</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>795.621</v>
+        <v>0</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>861.106</v>
+        <v>1.5</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>897.207</v>
+        <v>0.75</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>515.975</v>
+        <v>0.8</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>888.688</v>
-      </c>
-      <c r="T87" s="22" t="n">
-        <v>-461.657</v>
-      </c>
-      <c r="U87" s="22" t="n">
-        <v>-383.781</v>
-      </c>
-      <c r="V87" s="22" t="n">
-        <v>-429.901</v>
+        <v>0.9</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>714.141</v>
+        <v>30</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>515.975</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>판매비와 관리비 합계</t>
-        </is>
-      </c>
-      <c r="C88" s="22" t="n">
-        <v>1208.361</v>
-      </c>
-      <c r="D88" s="22" t="n">
-        <v>1186.81</v>
-      </c>
-      <c r="E88" s="22" t="n">
-        <v>1274.723</v>
+          <t>지급수수료</t>
+        </is>
       </c>
       <c r="F88" s="22" t="n">
-        <v>1467.133</v>
+        <v>305.837</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>1586.202</v>
+        <v>356.703</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>1676.755</v>
+        <v>361.766</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>2354.602</v>
+        <v>432.686</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>2001.106</v>
+        <v>450.458</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>2068.527</v>
+        <v>361.404</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>2085.757</v>
+        <v>385.465</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>2204.78</v>
+        <v>413.389</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>2190.684</v>
-      </c>
-      <c r="T88" s="22" t="n">
-        <v>1039.892</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>1147.174</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>1274.723</v>
+        <v>330.858</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>2354.602</v>
+        <v>432.686</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>2204.78</v>
+        <v>413.389</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>영업이익(손실)</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="n">
-        <v>145.081</v>
-      </c>
-      <c r="D89" s="12" t="n">
-        <v>199.092</v>
-      </c>
-      <c r="E89" s="12" t="n">
-        <v>435.923</v>
-      </c>
-      <c r="F89" s="12" t="n">
-        <v>231.767</v>
-      </c>
-      <c r="G89" s="12" t="n">
-        <v>1064.12</v>
-      </c>
-      <c r="H89" s="12" t="n">
-        <v>1289.53</v>
-      </c>
-      <c r="I89" s="12" t="n">
-        <v>1560.169</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>-457.171</v>
-      </c>
-      <c r="K89" s="12" t="n">
-        <v>-463.644</v>
-      </c>
-      <c r="L89" s="12" t="n">
-        <v>-196.665</v>
-      </c>
-      <c r="M89" s="12" t="n">
-        <v>713.826</v>
-      </c>
-      <c r="N89" s="12" t="n">
-        <v>1230.678</v>
-      </c>
-      <c r="T89" s="12" t="n">
-        <v>324.195</v>
-      </c>
-      <c r="U89" s="12" t="n">
-        <v>399.025</v>
-      </c>
-      <c r="V89" s="12" t="n">
-        <v>435.923</v>
-      </c>
-      <c r="W89" s="12" t="n">
-        <v>1560.169</v>
-      </c>
-      <c r="X89" s="12" t="n">
-        <v>713.826</v>
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C89" s="22" t="n">
+        <v>776.659</v>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>755.061</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>-429.901</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>614.321</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>675.165</v>
+      </c>
+      <c r="H89" s="22" t="n">
+        <v>728.013</v>
+      </c>
+      <c r="I89" s="22" t="n">
+        <v>714.141</v>
+      </c>
+      <c r="J89" s="22" t="n">
+        <v>795.621</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>861.106</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>897.207</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>515.975</v>
+      </c>
+      <c r="N89" s="22" t="n">
+        <v>888.688</v>
+      </c>
+      <c r="T89" s="22" t="n">
+        <v>-461.657</v>
+      </c>
+      <c r="U89" s="22" t="n">
+        <v>-383.781</v>
+      </c>
+      <c r="V89" s="22" t="n">
+        <v>-429.901</v>
+      </c>
+      <c r="W89" s="22" t="n">
+        <v>714.141</v>
+      </c>
+      <c r="X89" s="22" t="n">
+        <v>515.975</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비 합계</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>0.012</v>
+        <v>1208.361</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>0.011</v>
+        <v>1186.81</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>0.102</v>
+        <v>1274.723</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>1.467</v>
+        <v>1467.133</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>0.3</v>
+        <v>1586.202</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>1.04</v>
+        <v>1676.755</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>14.487</v>
+        <v>2354.602</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>0.994</v>
+        <v>2001.106</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>24.108</v>
+        <v>2068.527</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>9.542999999999999</v>
+        <v>2085.757</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>11.689</v>
+        <v>2204.78</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>14.507</v>
+        <v>2190.684</v>
       </c>
       <c r="T90" s="22" t="n">
-        <v>0.021</v>
+        <v>1039.892</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>0.015</v>
+        <v>1147.174</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>0.102</v>
+        <v>1274.723</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>14.487</v>
+        <v>2354.602</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>11.689</v>
+        <v>2204.78</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="20" t="inlineStr">
-        <is>
-          <t>지분법이익</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>19.571</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>6.642</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>37.234</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>3.122</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>18.229</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>18.686</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>51.464</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="U91" s="22" t="n">
-        <v>-4.654</v>
-      </c>
-      <c r="V91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" s="22" t="n">
-        <v>6.642</v>
-      </c>
-      <c r="X91" s="22" t="n">
-        <v>18.686</v>
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>영업이익(손실)</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>145.081</v>
+      </c>
+      <c r="D91" s="12" t="n">
+        <v>199.092</v>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>435.923</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>231.767</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>1064.12</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>1289.53</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>1560.169</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>-457.171</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>-463.644</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>-196.665</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>713.826</v>
+      </c>
+      <c r="N91" s="12" t="n">
+        <v>1230.678</v>
+      </c>
+      <c r="T91" s="12" t="n">
+        <v>324.195</v>
+      </c>
+      <c r="U91" s="12" t="n">
+        <v>399.025</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <v>435.923</v>
+      </c>
+      <c r="W91" s="12" t="n">
+        <v>1560.169</v>
+      </c>
+      <c r="X91" s="12" t="n">
+        <v>713.826</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 환입</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="D92" s="22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="E92" s="22" t="n">
-        <v>-0.182</v>
-      </c>
-      <c r="F92" s="22" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="G92" s="22" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H92" s="22" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="I92" s="22" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="J92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" s="22" t="n">
-        <v>-0.364</v>
-      </c>
-      <c r="U92" s="22" t="n">
-        <v>-0.274</v>
-      </c>
-      <c r="V92" s="22" t="n">
-        <v>-0.182</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>0</v>
+      <c r="A92" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C92" s="17">
+        <f>IF(OR(C91="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C91/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D92" s="17">
+        <f>IF(OR(D91="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D91/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E92" s="17">
+        <f>IF(OR(E91="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E91/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F92" s="17">
+        <f>IF(OR(F91="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F91/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G92" s="17">
+        <f>IF(OR(G91="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G91/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H92" s="17">
+        <f>IF(OR(H91="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H91/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I92" s="17">
+        <f>IF(OR(I91="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I91/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J92" s="17">
+        <f>IF(OR(J91="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J91/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K92" s="17">
+        <f>IF(OR(K91="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K91/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L92" s="17">
+        <f>IF(OR(L91="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L91/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M92" s="17">
+        <f>IF(OR(M91="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M91/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N92" s="17">
+        <f>IF(OR(N91="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N91/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T92" s="17">
+        <f>IF(OR(T91="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T91/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U92" s="17">
+        <f>IF(OR(U91="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U91/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V92" s="17">
+        <f>IF(OR(V91="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V91/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W92" s="17">
+        <f>IF(OR(W91="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W91/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X92" s="17">
+        <f>IF(OR(X91="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X91/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="20" t="inlineStr">
-        <is>
-          <t>업무수탁료</t>
-        </is>
-      </c>
-      <c r="E93" s="22" t="n">
-        <v>3.575</v>
-      </c>
-      <c r="U93" s="22" t="n">
-        <v>4.115</v>
-      </c>
-      <c r="V93" s="22" t="n">
-        <v>3.575</v>
+      <c r="A93" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G93" s="17">
+        <f>IF(OR(G91="",C91=""),"",IF(C91&lt;=0,"",IFERROR(G91/C91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H93" s="17">
+        <f>IF(OR(H91="",D91=""),"",IF(D91&lt;=0,"",IFERROR(H91/D91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I93" s="17">
+        <f>IF(OR(I91="",E91=""),"",IF(E91&lt;=0,"",IFERROR(I91/E91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J93" s="17">
+        <f>IF(OR(J91="",F91=""),"",IF(F91&lt;=0,"",IFERROR(J91/F91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K93" s="17">
+        <f>IF(OR(K91="",G91=""),"",IF(G91&lt;=0,"",IFERROR(K91/G91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L93" s="17">
+        <f>IF(OR(L91="",H91=""),"",IF(H91&lt;=0,"",IFERROR(L91/H91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M93" s="17">
+        <f>IF(OR(M91="",I91=""),"",IF(I91&lt;=0,"",IFERROR(M91/I91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N93" s="17">
+        <f>IF(OR(N91="",J91=""),"",IF(J91&lt;=0,"",IFERROR(N91/J91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T93" s="17">
+        <f>IF(OR(T91="",S91=""),"",IF(S91&lt;=0,"",IFERROR(T91/S91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U93" s="17">
+        <f>IF(OR(U91="",T91=""),"",IF(T91&lt;=0,"",IFERROR(U91/T91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V93" s="17">
+        <f>IF(OR(V91="",U91=""),"",IF(U91&lt;=0,"",IFERROR(V91/U91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W93" s="17">
+        <f>IF(OR(W91="",V91=""),"",IF(V91&lt;=0,"",IFERROR(W91/V91-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X93" s="17">
+        <f>IF(OR(X91="",W91=""),"",IF(W91&lt;=0,"",IFERROR(X91/W91-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>암호자산 매각이익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0</v>
+        <v>0.011</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>14.487</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>24.108</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>9.542999999999999</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>11.689</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>14.507</v>
+      </c>
+      <c r="T94" s="22" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="U94" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="V94" s="22" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>14.487</v>
+      </c>
+      <c r="X94" s="22" t="n">
+        <v>11.689</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>Temporary Transfer Charges Income NOI</t>
+          <t>지분법이익</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>3.234</v>
+        <v>0</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>1.869</v>
+        <v>0</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="22" t="n">
+        <v>19.571</v>
+      </c>
+      <c r="I95" s="22" t="n">
+        <v>6.642</v>
+      </c>
+      <c r="J95" s="22" t="n">
+        <v>37.234</v>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>3.122</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>18.229</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>18.686</v>
+      </c>
+      <c r="N95" s="22" t="n">
+        <v>51.464</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>5.412</v>
+        <v>4.56</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>4.684</v>
+        <v>-4.654</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>1.869</v>
+        <v>0</v>
+      </c>
+      <c r="W95" s="22" t="n">
+        <v>6.642</v>
+      </c>
+      <c r="X95" s="22" t="n">
+        <v>18.686</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>대손충당금 환입</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>9.494999999999999</v>
+        <v>-0.182</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>25.292</v>
+        <v>0.317</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>20.066</v>
+        <v>0.079</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>51.59</v>
+        <v>0.097</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>63.831</v>
+        <v>0.053</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>92.321</v>
+        <v>0</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>170.64</v>
+        <v>0</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>259.205</v>
+        <v>0</v>
       </c>
       <c r="M96" s="22" t="n">
-        <v>95.462</v>
-      </c>
-      <c r="N96" s="22" t="n">
-        <v>137.969</v>
+        <v>0</v>
+      </c>
+      <c r="T96" s="22" t="n">
+        <v>-0.364</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>-0.274</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>9.494999999999999</v>
+        <v>-0.182</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>63.831</v>
+        <v>0.053</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>95.462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C97" s="22" t="n">
-        <v>14.989</v>
-      </c>
-      <c r="D97" s="22" t="n">
-        <v>7.782</v>
+          <t>업무수탁료</t>
+        </is>
       </c>
       <c r="E97" s="22" t="n">
-        <v>-14.155</v>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>19.502</v>
-      </c>
-      <c r="G97" s="22" t="n">
-        <v>8.898999999999999</v>
-      </c>
-      <c r="H97" s="22" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="I97" s="22" t="n">
-        <v>-33.707</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>18.979</v>
-      </c>
-      <c r="K97" s="22" t="n">
-        <v>25.601</v>
-      </c>
-      <c r="L97" s="22" t="n">
-        <v>40.204</v>
-      </c>
-      <c r="M97" s="22" t="n">
-        <v>-13.139</v>
-      </c>
-      <c r="N97" s="22" t="n">
-        <v>22.532</v>
-      </c>
-      <c r="T97" s="22" t="n">
-        <v>-11.388</v>
+        <v>3.575</v>
       </c>
       <c r="U97" s="22" t="n">
-        <v>-10.132</v>
+        <v>4.115</v>
       </c>
       <c r="V97" s="22" t="n">
-        <v>-14.155</v>
-      </c>
-      <c r="W97" s="22" t="n">
-        <v>-33.707</v>
-      </c>
-      <c r="X97" s="22" t="n">
-        <v>-13.139</v>
+        <v>3.575</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>암호자산 매각이익</t>
         </is>
       </c>
       <c r="C98" s="22" t="n">
-        <v>15.082</v>
+        <v>0</v>
       </c>
       <c r="D98" s="22" t="n">
-        <v>7.783</v>
-      </c>
-      <c r="E98" s="22" t="n">
-        <v>91.265</v>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>46.58</v>
-      </c>
-      <c r="G98" s="22" t="n">
-        <v>29.343</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>128.899</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>92.161</v>
-      </c>
-      <c r="J98" s="22" t="n">
-        <v>149.528</v>
-      </c>
-      <c r="K98" s="22" t="n">
-        <v>223.472</v>
-      </c>
-      <c r="L98" s="22" t="n">
-        <v>327.182</v>
-      </c>
-      <c r="M98" s="22" t="n">
-        <v>363.977</v>
-      </c>
-      <c r="N98" s="22" t="n">
-        <v>226.474</v>
-      </c>
-      <c r="T98" s="22" t="n">
-        <v>25.772</v>
-      </c>
-      <c r="U98" s="22" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>91.265</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>92.161</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>363.977</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>Temporary Transfer Charges Income NOI</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>43.376</v>
+        <v>3.234</v>
       </c>
       <c r="D99" s="22" t="n">
-        <v>44.217</v>
+        <v>2.89</v>
       </c>
       <c r="E99" s="22" t="n">
-        <v>45.299</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>53.729</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>59.73</v>
-      </c>
-      <c r="H99" s="22" t="n">
-        <v>64.011</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>78.092</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>108.696</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <v>125.347</v>
-      </c>
-      <c r="L99" s="22" t="n">
-        <v>143.082</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <v>161.697</v>
-      </c>
-      <c r="N99" s="22" t="n">
-        <v>180.876</v>
+        <v>1.869</v>
       </c>
       <c r="T99" s="22" t="n">
-        <v>39.813</v>
+        <v>5.412</v>
       </c>
       <c r="U99" s="22" t="n">
-        <v>38.398</v>
+        <v>4.684</v>
       </c>
       <c r="V99" s="22" t="n">
-        <v>45.299</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>78.092</v>
-      </c>
-      <c r="X99" s="22" t="n">
-        <v>161.697</v>
+        <v>1.869</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>지분법손실</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C100" s="22" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="D100" s="22" t="n">
-        <v>0.749</v>
+        <v>0</v>
       </c>
       <c r="E100" s="22" t="n">
-        <v>-3.794</v>
+        <v>9.494999999999999</v>
       </c>
       <c r="F100" s="22" t="n">
-        <v>7.383</v>
+        <v>25.292</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>5.031</v>
+        <v>20.066</v>
       </c>
       <c r="H100" s="22" t="n">
-        <v>-12.414</v>
+        <v>51.59</v>
       </c>
       <c r="I100" s="22" t="n">
-        <v>0</v>
+        <v>63.831</v>
       </c>
       <c r="J100" s="22" t="n">
-        <v>0</v>
+        <v>92.321</v>
       </c>
       <c r="K100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="22" t="n">
-        <v>1.688</v>
+        <v>170.64</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>259.205</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>95.462</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>137.969</v>
       </c>
       <c r="V100" s="22" t="n">
-        <v>-3.794</v>
+        <v>9.494999999999999</v>
       </c>
       <c r="W100" s="22" t="n">
-        <v>0</v>
+        <v>63.831</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>95.462</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>0</v>
+        <v>14.989</v>
       </c>
       <c r="D101" s="22" t="n">
-        <v>0</v>
+        <v>7.782</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>0</v>
+        <v>-14.155</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>109.766</v>
+        <v>19.502</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>-0.238</v>
+        <v>8.898999999999999</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>0</v>
+        <v>56.6</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>0</v>
+        <v>-33.707</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>0</v>
+        <v>18.979</v>
       </c>
       <c r="K101" s="22" t="n">
-        <v>0</v>
+        <v>25.601</v>
       </c>
       <c r="L101" s="22" t="n">
-        <v>0</v>
+        <v>40.204</v>
       </c>
       <c r="M101" s="22" t="n">
-        <v>0</v>
+        <v>-13.139</v>
+      </c>
+      <c r="N101" s="22" t="n">
+        <v>22.532</v>
+      </c>
+      <c r="T101" s="22" t="n">
+        <v>-11.388</v>
+      </c>
+      <c r="U101" s="22" t="n">
+        <v>-10.132</v>
       </c>
       <c r="V101" s="22" t="n">
-        <v>0</v>
+        <v>-14.155</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>0</v>
+        <v>-33.707</v>
       </c>
       <c r="X101" s="22" t="n">
-        <v>0</v>
+        <v>-13.139</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>15.501</v>
+        <v>15.082</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>14.857</v>
+        <v>7.783</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>-1.96</v>
+        <v>91.265</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>12.26</v>
+        <v>46.58</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>22.04</v>
+        <v>29.343</v>
       </c>
       <c r="H102" s="22" t="n">
-        <v>-19.526</v>
+        <v>128.899</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>-5.101</v>
+        <v>92.161</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>21.938</v>
+        <v>149.528</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>7.965</v>
+        <v>223.472</v>
       </c>
       <c r="L102" s="22" t="n">
-        <v>-24.739</v>
+        <v>327.182</v>
       </c>
       <c r="M102" s="22" t="n">
-        <v>5.17</v>
+        <v>363.977</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>18.212</v>
+        <v>226.474</v>
       </c>
       <c r="T102" s="22" t="n">
-        <v>11.257</v>
+        <v>25.772</v>
       </c>
       <c r="U102" s="22" t="n">
-        <v>-19.624</v>
+        <v>-0.032</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>-1.96</v>
+        <v>91.265</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>-5.101</v>
+        <v>92.161</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>5.17</v>
+        <v>363.977</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C103" s="22" t="n">
-        <v>60.544</v>
+        <v>43.376</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>59.823</v>
+        <v>44.217</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>82.84099999999999</v>
+        <v>45.299</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>183.138</v>
+        <v>53.729</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>86.565</v>
+        <v>59.73</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>32.07</v>
+        <v>64.011</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>80.364</v>
+        <v>78.092</v>
       </c>
       <c r="J103" s="22" t="n">
-        <v>130.634</v>
+        <v>108.696</v>
       </c>
       <c r="K103" s="22" t="n">
-        <v>133.313</v>
+        <v>125.347</v>
       </c>
       <c r="L103" s="22" t="n">
-        <v>118.343</v>
+        <v>143.082</v>
       </c>
       <c r="M103" s="22" t="n">
-        <v>172.737</v>
+        <v>161.697</v>
       </c>
       <c r="N103" s="22" t="n">
-        <v>199.088</v>
+        <v>180.876</v>
       </c>
       <c r="T103" s="22" t="n">
-        <v>53.426</v>
+        <v>39.813</v>
       </c>
       <c r="U103" s="22" t="n">
-        <v>48.755</v>
+        <v>38.398</v>
       </c>
       <c r="V103" s="22" t="n">
-        <v>82.84099999999999</v>
+        <v>45.299</v>
       </c>
       <c r="W103" s="22" t="n">
-        <v>80.364</v>
+        <v>78.092</v>
       </c>
       <c r="X103" s="22" t="n">
-        <v>172.737</v>
+        <v>161.697</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>경상이익(손실)</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="n">
-        <v>99.619</v>
-      </c>
-      <c r="D104" s="12" t="n">
-        <v>147.052</v>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>444.348</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>95.208</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>1006.9</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>1386.358</v>
-      </c>
-      <c r="I104" s="12" t="n">
-        <v>1571.965</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>-438.277</v>
-      </c>
-      <c r="K104" s="12" t="n">
-        <v>-373.485</v>
-      </c>
-      <c r="L104" s="12" t="n">
-        <v>12.174</v>
-      </c>
-      <c r="M104" s="12" t="n">
-        <v>905.0650000000001</v>
-      </c>
-      <c r="N104" s="12" t="n">
-        <v>1258.064</v>
-      </c>
-      <c r="T104" s="12" t="n">
-        <v>296.54</v>
-      </c>
-      <c r="U104" s="12" t="n">
-        <v>350.237</v>
-      </c>
-      <c r="V104" s="12" t="n">
-        <v>444.348</v>
-      </c>
-      <c r="W104" s="12" t="n">
-        <v>1571.965</v>
-      </c>
-      <c r="X104" s="12" t="n">
-        <v>905.0650000000001</v>
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>지분법손실</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="E104" s="22" t="n">
+        <v>-3.794</v>
+      </c>
+      <c r="F104" s="22" t="n">
+        <v>7.383</v>
+      </c>
+      <c r="G104" s="22" t="n">
+        <v>5.031</v>
+      </c>
+      <c r="H104" s="22" t="n">
+        <v>-12.414</v>
+      </c>
+      <c r="I104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="22" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="V104" s="22" t="n">
+        <v>-3.794</v>
+      </c>
+      <c r="W104" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
+          <t>주식교부비</t>
         </is>
       </c>
       <c r="C105" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D105" s="22" t="n">
-        <v>5.868</v>
+        <v>0</v>
       </c>
       <c r="E105" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="22" t="n">
-        <v>0.034</v>
+        <v>109.766</v>
       </c>
       <c r="G105" s="22" t="n">
-        <v>0</v>
+        <v>-0.238</v>
       </c>
       <c r="H105" s="22" t="n">
-        <v>0.313</v>
+        <v>0</v>
       </c>
       <c r="I105" s="22" t="n">
-        <v>0.459</v>
+        <v>0</v>
       </c>
       <c r="J105" s="22" t="n">
         <v>0</v>
@@ -7200,22 +7256,16 @@
         <v>0</v>
       </c>
       <c r="L105" s="22" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M105" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="22" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="U105" s="22" t="n">
-        <v>4.815</v>
-      </c>
       <c r="V105" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W105" s="22" t="n">
-        <v>0.459</v>
+        <v>0</v>
       </c>
       <c r="X105" s="22" t="n">
         <v>0</v>
@@ -7224,232 +7274,316 @@
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C106" s="22" t="n">
-        <v>0</v>
+        <v>15.501</v>
       </c>
       <c r="D106" s="22" t="n">
-        <v>0</v>
+        <v>14.857</v>
       </c>
       <c r="E106" s="22" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>0</v>
+        <v>12.26</v>
       </c>
       <c r="G106" s="22" t="n">
-        <v>0</v>
+        <v>22.04</v>
       </c>
       <c r="H106" s="22" t="n">
-        <v>0</v>
+        <v>-19.526</v>
       </c>
       <c r="I106" s="22" t="n">
-        <v>0</v>
+        <v>-5.101</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>21.938</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>7.965</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>-24.739</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>18.209</v>
+        <v>5.17</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>18.212</v>
+      </c>
+      <c r="T106" s="22" t="n">
+        <v>11.257</v>
       </c>
       <c r="U106" s="22" t="n">
-        <v>0</v>
+        <v>-19.624</v>
       </c>
       <c r="V106" s="22" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="W106" s="22" t="n">
-        <v>0</v>
+        <v>-5.101</v>
       </c>
       <c r="X106" s="22" t="n">
-        <v>18.209</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>AState Government Subsidy Income EI</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C107" s="22" t="n">
-        <v>0</v>
+        <v>60.544</v>
       </c>
       <c r="D107" s="22" t="n">
-        <v>0</v>
+        <v>59.823</v>
       </c>
       <c r="E107" s="22" t="n">
-        <v>1624.819</v>
+        <v>82.84099999999999</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>3709.381</v>
+        <v>183.138</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>0</v>
+        <v>86.565</v>
       </c>
       <c r="H107" s="22" t="n">
-        <v>1623.063</v>
+        <v>32.07</v>
       </c>
       <c r="I107" s="22" t="n">
-        <v>787.3</v>
+        <v>80.364</v>
       </c>
       <c r="J107" s="22" t="n">
-        <v>6283.839</v>
+        <v>130.634</v>
       </c>
       <c r="K107" s="22" t="n">
-        <v>0</v>
+        <v>133.313</v>
       </c>
       <c r="L107" s="22" t="n">
-        <v>0</v>
+        <v>118.343</v>
       </c>
       <c r="M107" s="22" t="n">
-        <v>8027.854</v>
+        <v>172.737</v>
       </c>
       <c r="N107" s="22" t="n">
-        <v>2503.629</v>
+        <v>199.088</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>53.426</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>48.755</v>
       </c>
       <c r="V107" s="22" t="n">
-        <v>1624.819</v>
+        <v>82.84099999999999</v>
       </c>
       <c r="W107" s="22" t="n">
-        <v>787.3</v>
+        <v>80.364</v>
       </c>
       <c r="X107" s="22" t="n">
-        <v>8027.854</v>
+        <v>172.737</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>특별이익 합계</t>
-        </is>
-      </c>
-      <c r="C108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="22" t="n">
-        <v>5.868</v>
-      </c>
-      <c r="E108" s="22" t="n">
-        <v>1624.819</v>
-      </c>
-      <c r="F108" s="22" t="n">
-        <v>3709.415</v>
-      </c>
-      <c r="G108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="22" t="n">
-        <v>1623.376</v>
-      </c>
-      <c r="I108" s="22" t="n">
-        <v>787.759</v>
-      </c>
-      <c r="J108" s="22" t="n">
-        <v>6283.839</v>
-      </c>
-      <c r="K108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="22" t="n">
-        <v>137.447</v>
-      </c>
-      <c r="M108" s="22" t="n">
-        <v>8046.062</v>
-      </c>
-      <c r="N108" s="22" t="n">
-        <v>2503.629</v>
-      </c>
-      <c r="T108" s="22" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="U108" s="22" t="n">
-        <v>4.815</v>
-      </c>
-      <c r="V108" s="22" t="n">
-        <v>1624.819</v>
-      </c>
-      <c r="W108" s="22" t="n">
-        <v>787.759</v>
-      </c>
-      <c r="X108" s="22" t="n">
-        <v>8046.062</v>
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>경상이익(손실)</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>99.619</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>147.052</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>444.348</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>95.208</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>1006.9</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>1386.358</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>1571.965</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>-438.277</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>-373.485</v>
+      </c>
+      <c r="L108" s="12" t="n">
+        <v>12.174</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>905.0650000000001</v>
+      </c>
+      <c r="N108" s="12" t="n">
+        <v>1258.064</v>
+      </c>
+      <c r="T108" s="12" t="n">
+        <v>296.54</v>
+      </c>
+      <c r="U108" s="12" t="n">
+        <v>350.237</v>
+      </c>
+      <c r="V108" s="12" t="n">
+        <v>444.348</v>
+      </c>
+      <c r="W108" s="12" t="n">
+        <v>1571.965</v>
+      </c>
+      <c r="X108" s="12" t="n">
+        <v>905.0650000000001</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="n">
-        <v>1.334</v>
-      </c>
-      <c r="D109" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E109" s="22" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="F109" s="22" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="G109" s="22" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="H109" s="22" t="n">
-        <v>9.364000000000001</v>
-      </c>
-      <c r="I109" s="22" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <v>13.733</v>
-      </c>
-      <c r="L109" s="22" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="M109" s="22" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="N109" s="22" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="T109" s="22" t="n">
-        <v>2.511</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>9.138999999999999</v>
-      </c>
-      <c r="V109" s="22" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="W109" s="22" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="X109" s="22" t="n">
-        <v>0.989</v>
+      <c r="A109" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G109" s="17">
+        <f>IF(OR(G108="",C108=""),"",IF(C108&lt;=0,"",IFERROR(G108/C108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H109" s="17">
+        <f>IF(OR(H108="",D108=""),"",IF(D108&lt;=0,"",IFERROR(H108/D108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I109" s="17">
+        <f>IF(OR(I108="",E108=""),"",IF(E108&lt;=0,"",IFERROR(I108/E108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J109" s="17">
+        <f>IF(OR(J108="",F108=""),"",IF(F108&lt;=0,"",IFERROR(J108/F108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF(OR(K108="",G108=""),"",IF(G108&lt;=0,"",IFERROR(K108/G108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L109" s="17">
+        <f>IF(OR(L108="",H108=""),"",IF(H108&lt;=0,"",IFERROR(L108/H108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M109" s="17">
+        <f>IF(OR(M108="",I108=""),"",IF(I108&lt;=0,"",IFERROR(M108/I108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N109" s="17">
+        <f>IF(OR(N108="",J108=""),"",IF(J108&lt;=0,"",IFERROR(N108/J108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T109" s="17">
+        <f>IF(OR(T108="",S108=""),"",IF(S108&lt;=0,"",IFERROR(T108/S108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U109" s="17">
+        <f>IF(OR(U108="",T108=""),"",IF(T108&lt;=0,"",IFERROR(U108/T108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V109" s="17">
+        <f>IF(OR(V108="",U108=""),"",IF(U108&lt;=0,"",IFERROR(V108/U108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W109" s="17">
+        <f>IF(OR(W108="",V108=""),"",IF(V108&lt;=0,"",IFERROR(W108/V108-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X109" s="17">
+        <f>IF(OR(X108="",W108=""),"",IF(W108&lt;=0,"",IFERROR(X108/W108-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>고정자산 매각이익</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>5.868</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T110" s="22" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="U110" s="22" t="n">
+        <v>4.815</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="X110" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손실</t>
-        </is>
+          <t>투자유가증권 매각이익</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H111" s="22" t="n">
         <v>0</v>
@@ -7457,29 +7591,26 @@
       <c r="I111" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L111" s="22" t="n">
-        <v>1.205</v>
-      </c>
       <c r="M111" s="22" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>0</v>
+        <v>18.209</v>
       </c>
       <c r="U111" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="V111" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="W111" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X111" s="22" t="n">
-        <v>0.016</v>
+        <v>18.209</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>고정자산 압축손실</t>
+          <t>AState Government Subsidy Income EI</t>
         </is>
       </c>
       <c r="C112" s="22" t="n">
@@ -7498,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="22" t="n">
-        <v>1622.59</v>
+        <v>1623.063</v>
       </c>
       <c r="I112" s="22" t="n">
-        <v>787.773</v>
+        <v>787.3</v>
       </c>
       <c r="J112" s="22" t="n">
         <v>6283.839</v>
@@ -7522,7 +7653,7 @@
         <v>1624.819</v>
       </c>
       <c r="W112" s="22" t="n">
-        <v>787.773</v>
+        <v>787.3</v>
       </c>
       <c r="X112" s="22" t="n">
         <v>8027.854</v>
@@ -7531,3262 +7662,3391 @@
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손실</t>
-        </is>
+          <t>특별이익 합계</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="22" t="n">
-        <v>0</v>
+        <v>5.868</v>
       </c>
       <c r="E113" s="22" t="n">
+        <v>1624.819</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>3709.415</v>
+      </c>
+      <c r="G113" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="22" t="n">
-        <v>0</v>
+        <v>1623.376</v>
       </c>
       <c r="I113" s="22" t="n">
+        <v>787.759</v>
+      </c>
+      <c r="J113" s="22" t="n">
+        <v>6283.839</v>
+      </c>
+      <c r="K113" s="22" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="22" t="n">
-        <v>0</v>
+        <v>137.447</v>
       </c>
       <c r="M113" s="22" t="n">
-        <v>0</v>
+        <v>8046.062</v>
+      </c>
+      <c r="N113" s="22" t="n">
+        <v>2503.629</v>
+      </c>
+      <c r="T113" s="22" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="U113" s="22" t="n">
+        <v>4.815</v>
       </c>
       <c r="V113" s="22" t="n">
-        <v>0</v>
+        <v>1624.819</v>
       </c>
       <c r="W113" s="22" t="n">
-        <v>0</v>
+        <v>787.759</v>
       </c>
       <c r="X113" s="22" t="n">
-        <v>0</v>
+        <v>8046.062</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>리스해약 손실</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="C114" s="22" t="n">
-        <v>0</v>
+        <v>1.334</v>
       </c>
       <c r="D114" s="22" t="n">
-        <v>0</v>
+        <v>0.015</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>0.134</v>
       </c>
       <c r="F114" s="22" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="H114" s="22" t="n">
-        <v>0</v>
+        <v>9.364000000000001</v>
+      </c>
+      <c r="I114" s="22" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>13.733</v>
+      </c>
+      <c r="L114" s="22" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="M114" s="22" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="N114" s="22" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="T114" s="22" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="U114" s="22" t="n">
+        <v>9.138999999999999</v>
+      </c>
+      <c r="V114" s="22" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="W114" s="22" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="X114" s="22" t="n">
+        <v>0.989</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="D115" s="22" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="E115" s="22" t="n">
-        <v>1624.953</v>
-      </c>
-      <c r="F115" s="22" t="n">
-        <v>3709.493</v>
-      </c>
-      <c r="G115" s="22" t="n">
-        <v>30.016</v>
-      </c>
-      <c r="H115" s="22" t="n">
-        <v>1631.954</v>
-      </c>
-      <c r="I115" s="22" t="n">
-        <v>830.294</v>
-      </c>
-      <c r="J115" s="22" t="n">
-        <v>6283.862</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>14.609</v>
-      </c>
-      <c r="L115" s="22" t="n">
-        <v>1.174</v>
-      </c>
-      <c r="M115" s="22" t="n">
-        <v>8028.858</v>
-      </c>
-      <c r="N115" s="22" t="n">
-        <v>2504.089</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="T115" s="22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U115" s="22" t="n">
-        <v>9.138999999999999</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>1624.953</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>830.294</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>8028.858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 중간순이익(손실)</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>98.28400000000001</v>
-      </c>
-      <c r="D116" s="12" t="n">
-        <v>152.906</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>444.214</v>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>95.13</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>976.883</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>1377.78</v>
-      </c>
-      <c r="I116" s="12" t="n">
-        <v>1529.431</v>
-      </c>
-      <c r="J116" s="12" t="n">
-        <v>-438.299</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>-388.094</v>
-      </c>
-      <c r="L116" s="12" t="n">
-        <v>148.446</v>
-      </c>
-      <c r="M116" s="12" t="n">
-        <v>922.269</v>
-      </c>
-      <c r="N116" s="12" t="n">
-        <v>1257.605</v>
-      </c>
-      <c r="T116" s="12" t="n">
-        <v>294.062</v>
-      </c>
-      <c r="U116" s="12" t="n">
-        <v>345.913</v>
-      </c>
-      <c r="V116" s="12" t="n">
-        <v>444.214</v>
-      </c>
-      <c r="W116" s="12" t="n">
-        <v>1529.431</v>
-      </c>
-      <c r="X116" s="12" t="n">
-        <v>922.269</v>
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 매각손실</t>
+        </is>
+      </c>
+      <c r="H116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="22" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="M116" s="22" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="T116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="22" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>고정자산 압축손실</t>
         </is>
       </c>
       <c r="C117" s="22" t="n">
-        <v>128.224</v>
+        <v>0</v>
       </c>
       <c r="D117" s="22" t="n">
-        <v>-6.844</v>
+        <v>0</v>
       </c>
       <c r="E117" s="22" t="n">
-        <v>147.56</v>
+        <v>1624.819</v>
       </c>
       <c r="F117" s="22" t="n">
-        <v>15.041</v>
+        <v>3709.381</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>479.685</v>
+        <v>0</v>
       </c>
       <c r="H117" s="22" t="n">
-        <v>437.255</v>
+        <v>1622.59</v>
       </c>
       <c r="I117" s="22" t="n">
-        <v>543.503</v>
+        <v>787.773</v>
       </c>
       <c r="J117" s="22" t="n">
-        <v>-5.14</v>
+        <v>6283.839</v>
       </c>
       <c r="K117" s="22" t="n">
-        <v>24.327</v>
+        <v>0</v>
       </c>
       <c r="L117" s="22" t="n">
-        <v>21.516</v>
+        <v>0</v>
       </c>
       <c r="M117" s="22" t="n">
-        <v>391.47</v>
+        <v>8027.854</v>
       </c>
       <c r="N117" s="22" t="n">
-        <v>480.114</v>
-      </c>
-      <c r="T117" s="22" t="n">
-        <v>78.794</v>
-      </c>
-      <c r="U117" s="22" t="n">
-        <v>124.161</v>
+        <v>2503.629</v>
       </c>
       <c r="V117" s="22" t="n">
-        <v>147.56</v>
+        <v>1624.819</v>
       </c>
       <c r="W117" s="22" t="n">
-        <v>543.503</v>
+        <v>787.773</v>
       </c>
       <c r="X117" s="22" t="n">
-        <v>391.47</v>
+        <v>8027.854</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="n">
-        <v>-81.782</v>
+          <t>투자유가증권 평가손실</t>
+        </is>
       </c>
       <c r="D118" s="22" t="n">
-        <v>29.266</v>
+        <v>0</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>-57.046</v>
-      </c>
-      <c r="F118" s="22" t="n">
-        <v>39.379</v>
-      </c>
-      <c r="G118" s="22" t="n">
-        <v>-170.251</v>
+        <v>0</v>
       </c>
       <c r="H118" s="22" t="n">
-        <v>4.362</v>
+        <v>0</v>
       </c>
       <c r="I118" s="22" t="n">
-        <v>-323.105</v>
-      </c>
-      <c r="J118" s="22" t="n">
-        <v>-114.178</v>
-      </c>
-      <c r="K118" s="22" t="n">
-        <v>-114.122</v>
+        <v>0</v>
       </c>
       <c r="L118" s="22" t="n">
-        <v>45.517</v>
+        <v>0</v>
       </c>
       <c r="M118" s="22" t="n">
-        <v>-239.864</v>
-      </c>
-      <c r="N118" s="22" t="n">
-        <v>-80.08199999999999</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>-5.992</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>-40.595</v>
+        <v>0</v>
       </c>
       <c r="V118" s="22" t="n">
-        <v>-57.046</v>
+        <v>0</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>-323.105</v>
+        <v>0</v>
       </c>
       <c r="X118" s="22" t="n">
-        <v>-239.864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
+          <t>리스해약 손실</t>
         </is>
       </c>
       <c r="C119" s="22" t="n">
-        <v>46.442</v>
+        <v>0</v>
       </c>
       <c r="D119" s="22" t="n">
-        <v>22.421</v>
-      </c>
-      <c r="E119" s="22" t="n">
-        <v>90.515</v>
+        <v>0</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>54.421</v>
+        <v>0</v>
       </c>
       <c r="G119" s="22" t="n">
-        <v>309.433</v>
+        <v>0</v>
       </c>
       <c r="H119" s="22" t="n">
-        <v>441.617</v>
-      </c>
-      <c r="I119" s="22" t="n">
-        <v>220.398</v>
-      </c>
-      <c r="J119" s="22" t="n">
-        <v>-119.319</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>-89.794</v>
-      </c>
-      <c r="L119" s="22" t="n">
-        <v>67.03400000000001</v>
-      </c>
-      <c r="M119" s="22" t="n">
-        <v>151.604</v>
-      </c>
-      <c r="N119" s="22" t="n">
-        <v>400.032</v>
-      </c>
-      <c r="T119" s="22" t="n">
-        <v>72.80200000000001</v>
-      </c>
-      <c r="U119" s="22" t="n">
-        <v>83.566</v>
-      </c>
-      <c r="V119" s="22" t="n">
-        <v>90.515</v>
-      </c>
-      <c r="W119" s="22" t="n">
-        <v>220.398</v>
-      </c>
-      <c r="X119" s="22" t="n">
-        <v>151.604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>중간순이익(손실)</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="n">
-        <v>51.842</v>
-      </c>
-      <c r="D120" s="12" t="n">
-        <v>130.486</v>
-      </c>
-      <c r="E120" s="12" t="n">
-        <v>353.699</v>
-      </c>
-      <c r="F120" s="12" t="n">
-        <v>40.709</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>667.449</v>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>936.164</v>
-      </c>
-      <c r="I120" s="12" t="n">
-        <v>1309.033</v>
-      </c>
-      <c r="J120" s="12" t="n">
-        <v>-318.98</v>
-      </c>
-      <c r="K120" s="12" t="n">
-        <v>-298.3</v>
-      </c>
-      <c r="L120" s="12" t="n">
-        <v>81.413</v>
-      </c>
-      <c r="M120" s="12" t="n">
-        <v>770.664</v>
-      </c>
-      <c r="N120" s="12" t="n">
-        <v>857.572</v>
-      </c>
-      <c r="T120" s="12" t="n">
-        <v>221.26</v>
-      </c>
-      <c r="U120" s="12" t="n">
-        <v>262.348</v>
-      </c>
-      <c r="V120" s="12" t="n">
-        <v>353.699</v>
-      </c>
-      <c r="W120" s="12" t="n">
-        <v>1309.033</v>
-      </c>
-      <c r="X120" s="12" t="n">
-        <v>770.664</v>
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C120" s="22" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="D120" s="22" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="E120" s="22" t="n">
+        <v>1624.953</v>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>3709.493</v>
+      </c>
+      <c r="G120" s="22" t="n">
+        <v>30.016</v>
+      </c>
+      <c r="H120" s="22" t="n">
+        <v>1631.954</v>
+      </c>
+      <c r="I120" s="22" t="n">
+        <v>830.294</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>6283.862</v>
+      </c>
+      <c r="K120" s="22" t="n">
+        <v>14.609</v>
+      </c>
+      <c r="L120" s="22" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="M120" s="22" t="n">
+        <v>8028.858</v>
+      </c>
+      <c r="N120" s="22" t="n">
+        <v>2504.089</v>
+      </c>
+      <c r="T120" s="22" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U120" s="22" t="n">
+        <v>9.138999999999999</v>
+      </c>
+      <c r="V120" s="22" t="n">
+        <v>1624.953</v>
+      </c>
+      <c r="W120" s="22" t="n">
+        <v>830.294</v>
+      </c>
+      <c r="X120" s="22" t="n">
+        <v>8028.858</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
+          <t>법인세차감전 중간순이익(손실)</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>98.28400000000001</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>152.906</v>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>444.214</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>95.13</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>976.883</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>1377.78</v>
+      </c>
+      <c r="I121" s="12" t="n">
+        <v>1529.431</v>
+      </c>
+      <c r="J121" s="12" t="n">
+        <v>-438.299</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>-388.094</v>
+      </c>
+      <c r="L121" s="12" t="n">
+        <v>148.446</v>
+      </c>
+      <c r="M121" s="12" t="n">
+        <v>922.269</v>
+      </c>
+      <c r="N121" s="12" t="n">
+        <v>1257.605</v>
+      </c>
+      <c r="T121" s="12" t="n">
+        <v>294.062</v>
+      </c>
+      <c r="U121" s="12" t="n">
+        <v>345.913</v>
+      </c>
+      <c r="V121" s="12" t="n">
+        <v>444.214</v>
+      </c>
+      <c r="W121" s="12" t="n">
+        <v>1529.431</v>
+      </c>
+      <c r="X121" s="12" t="n">
+        <v>922.269</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="n">
+        <v>128.224</v>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>-6.844</v>
+      </c>
+      <c r="E122" s="22" t="n">
+        <v>147.56</v>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>15.041</v>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>479.685</v>
+      </c>
+      <c r="H122" s="22" t="n">
+        <v>437.255</v>
+      </c>
+      <c r="I122" s="22" t="n">
+        <v>543.503</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>24.327</v>
+      </c>
+      <c r="L122" s="22" t="n">
+        <v>21.516</v>
+      </c>
+      <c r="M122" s="22" t="n">
+        <v>391.47</v>
+      </c>
+      <c r="N122" s="22" t="n">
+        <v>480.114</v>
+      </c>
+      <c r="T122" s="22" t="n">
+        <v>78.794</v>
+      </c>
+      <c r="U122" s="22" t="n">
+        <v>124.161</v>
+      </c>
+      <c r="V122" s="22" t="n">
+        <v>147.56</v>
+      </c>
+      <c r="W122" s="22" t="n">
+        <v>543.503</v>
+      </c>
+      <c r="X122" s="22" t="n">
+        <v>391.47</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C123" s="22" t="n">
+        <v>-81.782</v>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>29.266</v>
+      </c>
+      <c r="E123" s="22" t="n">
+        <v>-57.046</v>
+      </c>
+      <c r="F123" s="22" t="n">
+        <v>39.379</v>
+      </c>
+      <c r="G123" s="22" t="n">
+        <v>-170.251</v>
+      </c>
+      <c r="H123" s="22" t="n">
+        <v>4.362</v>
+      </c>
+      <c r="I123" s="22" t="n">
+        <v>-323.105</v>
+      </c>
+      <c r="J123" s="22" t="n">
+        <v>-114.178</v>
+      </c>
+      <c r="K123" s="22" t="n">
+        <v>-114.122</v>
+      </c>
+      <c r="L123" s="22" t="n">
+        <v>45.517</v>
+      </c>
+      <c r="M123" s="22" t="n">
+        <v>-239.864</v>
+      </c>
+      <c r="N123" s="22" t="n">
+        <v>-80.08199999999999</v>
+      </c>
+      <c r="T123" s="22" t="n">
+        <v>-5.992</v>
+      </c>
+      <c r="U123" s="22" t="n">
+        <v>-40.595</v>
+      </c>
+      <c r="V123" s="22" t="n">
+        <v>-57.046</v>
+      </c>
+      <c r="W123" s="22" t="n">
+        <v>-323.105</v>
+      </c>
+      <c r="X123" s="22" t="n">
+        <v>-239.864</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C124" s="22" t="n">
+        <v>46.442</v>
+      </c>
+      <c r="D124" s="22" t="n">
+        <v>22.421</v>
+      </c>
+      <c r="E124" s="22" t="n">
+        <v>90.515</v>
+      </c>
+      <c r="F124" s="22" t="n">
+        <v>54.421</v>
+      </c>
+      <c r="G124" s="22" t="n">
+        <v>309.433</v>
+      </c>
+      <c r="H124" s="22" t="n">
+        <v>441.617</v>
+      </c>
+      <c r="I124" s="22" t="n">
+        <v>220.398</v>
+      </c>
+      <c r="J124" s="22" t="n">
+        <v>-119.319</v>
+      </c>
+      <c r="K124" s="22" t="n">
+        <v>-89.794</v>
+      </c>
+      <c r="L124" s="22" t="n">
+        <v>67.03400000000001</v>
+      </c>
+      <c r="M124" s="22" t="n">
+        <v>151.604</v>
+      </c>
+      <c r="N124" s="22" t="n">
+        <v>400.032</v>
+      </c>
+      <c r="T124" s="22" t="n">
+        <v>72.80200000000001</v>
+      </c>
+      <c r="U124" s="22" t="n">
+        <v>83.566</v>
+      </c>
+      <c r="V124" s="22" t="n">
+        <v>90.515</v>
+      </c>
+      <c r="W124" s="22" t="n">
+        <v>220.398</v>
+      </c>
+      <c r="X124" s="22" t="n">
+        <v>151.604</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>중간순이익(손실)</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="n">
+        <v>51.842</v>
+      </c>
+      <c r="D125" s="12" t="n">
+        <v>130.486</v>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>353.699</v>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>40.709</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>667.449</v>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>936.164</v>
+      </c>
+      <c r="I125" s="12" t="n">
+        <v>1309.033</v>
+      </c>
+      <c r="J125" s="12" t="n">
+        <v>-318.98</v>
+      </c>
+      <c r="K125" s="12" t="n">
+        <v>-298.3</v>
+      </c>
+      <c r="L125" s="12" t="n">
+        <v>81.413</v>
+      </c>
+      <c r="M125" s="12" t="n">
+        <v>770.664</v>
+      </c>
+      <c r="N125" s="12" t="n">
+        <v>857.572</v>
+      </c>
+      <c r="T125" s="12" t="n">
+        <v>221.26</v>
+      </c>
+      <c r="U125" s="12" t="n">
+        <v>262.348</v>
+      </c>
+      <c r="V125" s="12" t="n">
+        <v>353.699</v>
+      </c>
+      <c r="W125" s="12" t="n">
+        <v>1309.033</v>
+      </c>
+      <c r="X125" s="12" t="n">
+        <v>770.664</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G126" s="17">
+        <f>IF(OR(G125="",C125=""),"",IF(C125&lt;=0,"",IFERROR(G125/C125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H126" s="17">
+        <f>IF(OR(H125="",D125=""),"",IF(D125&lt;=0,"",IFERROR(H125/D125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I126" s="17">
+        <f>IF(OR(I125="",E125=""),"",IF(E125&lt;=0,"",IFERROR(I125/E125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J126" s="17">
+        <f>IF(OR(J125="",F125=""),"",IF(F125&lt;=0,"",IFERROR(J125/F125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K126" s="17">
+        <f>IF(OR(K125="",G125=""),"",IF(G125&lt;=0,"",IFERROR(K125/G125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L126" s="17">
+        <f>IF(OR(L125="",H125=""),"",IF(H125&lt;=0,"",IFERROR(L125/H125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M126" s="17">
+        <f>IF(OR(M125="",I125=""),"",IF(I125&lt;=0,"",IFERROR(M125/I125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N126" s="17">
+        <f>IF(OR(N125="",J125=""),"",IF(J125&lt;=0,"",IFERROR(N125/J125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T126" s="17">
+        <f>IF(OR(T125="",S125=""),"",IF(S125&lt;=0,"",IFERROR(T125/S125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U126" s="17">
+        <f>IF(OR(U125="",T125=""),"",IF(T125&lt;=0,"",IFERROR(U125/T125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V126" s="17">
+        <f>IF(OR(V125="",U125=""),"",IF(U125&lt;=0,"",IFERROR(V125/U125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W126" s="17">
+        <f>IF(OR(W125="",V125=""),"",IF(V125&lt;=0,"",IFERROR(W125/V125-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X126" s="17">
+        <f>IF(OR(X125="",W125=""),"",IF(W125&lt;=0,"",IFERROR(X125/W125-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
           <t>비지배주주 순이익</t>
         </is>
       </c>
-      <c r="C121" s="12" t="n">
+      <c r="C127" s="12" t="n">
         <v>-14.831</v>
       </c>
-      <c r="D121" s="12" t="n">
+      <c r="D127" s="12" t="n">
         <v>1.62</v>
       </c>
-      <c r="E121" s="12" t="n">
+      <c r="E127" s="12" t="n">
         <v>5.987</v>
       </c>
-      <c r="F121" s="12" t="n">
+      <c r="F127" s="12" t="n">
         <v>-1.011</v>
       </c>
-      <c r="G121" s="12" t="n">
+      <c r="G127" s="12" t="n">
         <v>-0.901</v>
       </c>
-      <c r="H121" s="12" t="n">
+      <c r="H127" s="12" t="n">
         <v>3.962</v>
       </c>
-      <c r="I121" s="12" t="n">
+      <c r="I127" s="12" t="n">
         <v>13.845</v>
       </c>
-      <c r="J121" s="12" t="n">
+      <c r="J127" s="12" t="n">
         <v>5.398</v>
       </c>
-      <c r="K121" s="12" t="n">
+      <c r="K127" s="12" t="n">
         <v>4.084</v>
       </c>
-      <c r="L121" s="12" t="n">
+      <c r="L127" s="12" t="n">
         <v>5.675</v>
       </c>
-      <c r="M121" s="12" t="n">
+      <c r="M127" s="12" t="n">
         <v>3.616</v>
       </c>
-      <c r="N121" s="12" t="n">
+      <c r="N127" s="12" t="n">
         <v>1.646</v>
       </c>
-      <c r="T121" s="12" t="n">
+      <c r="T127" s="12" t="n">
         <v>23.371</v>
       </c>
-      <c r="U121" s="12" t="n">
+      <c r="U127" s="12" t="n">
         <v>13.437</v>
       </c>
-      <c r="V121" s="12" t="n">
+      <c r="V127" s="12" t="n">
         <v>5.987</v>
       </c>
-      <c r="W121" s="12" t="n">
+      <c r="W127" s="12" t="n">
         <v>13.845</v>
       </c>
-      <c r="X121" s="12" t="n">
+      <c r="X127" s="12" t="n">
         <v>3.616</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>지배주주 귀속 중간순이익(손실)</t>
         </is>
       </c>
-      <c r="C122" s="12" t="n">
+      <c r="C128" s="12" t="n">
         <v>66.672</v>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="D128" s="12" t="n">
         <v>128.866</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="E128" s="12" t="n">
         <v>347.712</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="F128" s="12" t="n">
         <v>41.721</v>
       </c>
-      <c r="G122" s="12" t="n">
+      <c r="G128" s="12" t="n">
         <v>668.35</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="H128" s="12" t="n">
         <v>932.2</v>
       </c>
-      <c r="I122" s="12" t="n">
+      <c r="I128" s="12" t="n">
         <v>1295.188</v>
       </c>
-      <c r="J122" s="12" t="n">
+      <c r="J128" s="12" t="n">
         <v>-324.379</v>
       </c>
-      <c r="K122" s="12" t="n">
+      <c r="K128" s="12" t="n">
         <v>-302.384</v>
       </c>
-      <c r="L122" s="12" t="n">
+      <c r="L128" s="12" t="n">
         <v>75.738</v>
       </c>
-      <c r="M122" s="12" t="n">
+      <c r="M128" s="12" t="n">
         <v>767.048</v>
       </c>
-      <c r="N122" s="12" t="n">
+      <c r="N128" s="12" t="n">
         <v>855.926</v>
       </c>
-      <c r="T122" s="12" t="n">
+      <c r="T128" s="12" t="n">
         <v>197.888</v>
       </c>
-      <c r="U122" s="12" t="n">
+      <c r="U128" s="12" t="n">
         <v>248.91</v>
       </c>
-      <c r="V122" s="12" t="n">
+      <c r="V128" s="12" t="n">
         <v>347.712</v>
       </c>
-      <c r="W122" s="12" t="n">
+      <c r="W128" s="12" t="n">
         <v>1295.188</v>
       </c>
-      <c r="X122" s="12" t="n">
+      <c r="X128" s="12" t="n">
         <v>767.048</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="18" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G129" s="17">
+        <f>IF(OR(G128="",C128=""),"",IF(C128&lt;=0,"",IFERROR(G128/C128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H129" s="17">
+        <f>IF(OR(H128="",D128=""),"",IF(D128&lt;=0,"",IFERROR(H128/D128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I129" s="17">
+        <f>IF(OR(I128="",E128=""),"",IF(E128&lt;=0,"",IFERROR(I128/E128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J129" s="17">
+        <f>IF(OR(J128="",F128=""),"",IF(F128&lt;=0,"",IFERROR(J128/F128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K129" s="17">
+        <f>IF(OR(K128="",G128=""),"",IF(G128&lt;=0,"",IFERROR(K128/G128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L129" s="17">
+        <f>IF(OR(L128="",H128=""),"",IF(H128&lt;=0,"",IFERROR(L128/H128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M129" s="17">
+        <f>IF(OR(M128="",I128=""),"",IF(I128&lt;=0,"",IFERROR(M128/I128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N129" s="17">
+        <f>IF(OR(N128="",J128=""),"",IF(J128&lt;=0,"",IFERROR(N128/J128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T129" s="17">
+        <f>IF(OR(T128="",S128=""),"",IF(S128&lt;=0,"",IFERROR(T128/S128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U129" s="17">
+        <f>IF(OR(U128="",T128=""),"",IF(T128&lt;=0,"",IFERROR(U128/T128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V129" s="17">
+        <f>IF(OR(V128="",U128=""),"",IF(U128&lt;=0,"",IFERROR(V128/U128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W129" s="17">
+        <f>IF(OR(W128="",V128=""),"",IF(V128&lt;=0,"",IFERROR(W128/V128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X129" s="17">
+        <f>IF(OR(X128="",W128=""),"",IF(W128&lt;=0,"",IFERROR(X128/W128-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="18" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B124" s="44" t="inlineStr">
+      <c r="B131" s="44" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C124" s="18" t="n"/>
-      <c r="D124" s="18" t="n"/>
-      <c r="E124" s="18" t="n"/>
-      <c r="F124" s="18" t="n"/>
-      <c r="G124" s="18" t="n"/>
-      <c r="H124" s="18" t="n"/>
-      <c r="I124" s="18" t="n"/>
-      <c r="J124" s="18" t="n"/>
-      <c r="K124" s="18" t="n"/>
-      <c r="L124" s="18" t="n"/>
-      <c r="M124" s="18" t="n"/>
-      <c r="N124" s="18" t="n"/>
-      <c r="O124" s="18" t="n"/>
-      <c r="P124" s="18" t="n"/>
-      <c r="Q124" s="18" t="n"/>
-      <c r="R124" s="18" t="n"/>
-      <c r="S124" s="18" t="n"/>
-      <c r="T124" s="18" t="n"/>
-      <c r="U124" s="18" t="n"/>
-      <c r="V124" s="18" t="n"/>
-      <c r="W124" s="18" t="n"/>
-      <c r="X124" s="18" t="n"/>
-      <c r="Y124" s="18" t="n"/>
-      <c r="Z124" s="18" t="n"/>
-      <c r="AA124" s="18" t="n"/>
-      <c r="AB124" s="18" t="n"/>
-      <c r="AC124" s="18" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
+      <c r="C131" s="18" t="n"/>
+      <c r="D131" s="18" t="n"/>
+      <c r="E131" s="18" t="n"/>
+      <c r="F131" s="18" t="n"/>
+      <c r="G131" s="18" t="n"/>
+      <c r="H131" s="18" t="n"/>
+      <c r="I131" s="18" t="n"/>
+      <c r="J131" s="18" t="n"/>
+      <c r="K131" s="18" t="n"/>
+      <c r="L131" s="18" t="n"/>
+      <c r="M131" s="18" t="n"/>
+      <c r="N131" s="18" t="n"/>
+      <c r="O131" s="18" t="n"/>
+      <c r="P131" s="18" t="n"/>
+      <c r="Q131" s="18" t="n"/>
+      <c r="R131" s="18" t="n"/>
+      <c r="S131" s="18" t="n"/>
+      <c r="T131" s="18" t="n"/>
+      <c r="U131" s="18" t="n"/>
+      <c r="V131" s="18" t="n"/>
+      <c r="W131" s="18" t="n"/>
+      <c r="X131" s="18" t="n"/>
+      <c r="Y131" s="18" t="n"/>
+      <c r="Z131" s="18" t="n"/>
+      <c r="AA131" s="18" t="n"/>
+      <c r="AB131" s="18" t="n"/>
+      <c r="AC131" s="18" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E125" s="5" t="inlineStr">
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F125" s="5" t="inlineStr">
+      <c r="F132" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J125" s="5" t="inlineStr">
+      <c r="J132" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K125" s="5" t="inlineStr">
+      <c r="K132" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L125" s="5" t="inlineStr">
+      <c r="L132" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M125" s="5" t="inlineStr">
+      <c r="M132" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N125" s="5" t="inlineStr">
+      <c r="N132" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O125" s="5" t="inlineStr">
+      <c r="O132" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P125" s="5" t="inlineStr">
+      <c r="P132" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q125" s="5" t="inlineStr">
+      <c r="Q132" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R125" s="5" t="inlineStr">
+      <c r="R132" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S125" s="5" t="inlineStr">
+      <c r="S132" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T125" s="5" t="inlineStr">
+      <c r="T132" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U125" s="5" t="inlineStr">
+      <c r="U132" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V125" s="5" t="inlineStr">
+      <c r="V132" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W125" s="5" t="inlineStr">
+      <c r="W132" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X125" s="5" t="inlineStr">
+      <c r="X132" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y125" s="5" t="inlineStr">
+      <c r="Y132" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z125" s="5" t="inlineStr">
+      <c r="Z132" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA125" s="5" t="inlineStr">
+      <c r="AA132" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB125" s="5" t="inlineStr">
+      <c r="AB132" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC125" s="5" t="inlineStr">
+      <c r="AC132" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>중간순이익(손실)</t>
-        </is>
-      </c>
-      <c r="C126" s="12" t="n">
-        <v>51.842</v>
-      </c>
-      <c r="D126" s="12" t="n">
-        <v>130.486</v>
-      </c>
-      <c r="E126" s="12" t="n">
-        <v>353.699</v>
-      </c>
-      <c r="F126" s="12" t="n">
-        <v>40.709</v>
-      </c>
-      <c r="G126" s="12" t="n">
-        <v>667.449</v>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>936.164</v>
-      </c>
-      <c r="I126" s="12" t="n">
-        <v>1309.033</v>
-      </c>
-      <c r="J126" s="12" t="n">
-        <v>-318.98</v>
-      </c>
-      <c r="K126" s="12" t="n">
-        <v>-298.3</v>
-      </c>
-      <c r="L126" s="12" t="n">
-        <v>81.413</v>
-      </c>
-      <c r="M126" s="12" t="n">
-        <v>770.664</v>
-      </c>
-      <c r="N126" s="12" t="n">
-        <v>857.572</v>
-      </c>
-      <c r="T126" s="12" t="n">
-        <v>221.26</v>
-      </c>
-      <c r="U126" s="12" t="n">
-        <v>262.348</v>
-      </c>
-      <c r="V126" s="12" t="n">
-        <v>353.699</v>
-      </c>
-      <c r="W126" s="12" t="n">
-        <v>1309.033</v>
-      </c>
-      <c r="X126" s="12" t="n">
-        <v>770.664</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C127" s="22" t="n">
-        <v>-54.413</v>
-      </c>
-      <c r="D127" s="22" t="n">
-        <v>-83.655</v>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>31.081</v>
-      </c>
-      <c r="F127" s="22" t="n">
-        <v>-30.201</v>
-      </c>
-      <c r="G127" s="22" t="n">
-        <v>-33.611</v>
-      </c>
-      <c r="H127" s="22" t="n">
-        <v>-8.762</v>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>52.12</v>
-      </c>
-      <c r="J127" s="22" t="n">
-        <v>45.913</v>
-      </c>
-      <c r="K127" s="22" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="L127" s="22" t="n">
-        <v>-125.285</v>
-      </c>
-      <c r="M127" s="22" t="n">
-        <v>-19.547</v>
-      </c>
-      <c r="N127" s="22" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="T127" s="22" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="U127" s="22" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>31.081</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>52.12</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>-19.547</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>이연헤지손익</t>
-        </is>
-      </c>
-      <c r="C128" s="22" t="n">
-        <v>-3.074</v>
-      </c>
-      <c r="D128" s="22" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="E128" s="22" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="F128" s="22" t="n">
-        <v>-0.155</v>
-      </c>
-      <c r="G128" s="22" t="n">
-        <v>-2.211</v>
-      </c>
-      <c r="H128" s="22" t="n">
-        <v>9.288</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>-7.093</v>
-      </c>
-      <c r="J128" s="22" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <v>6.086</v>
-      </c>
-      <c r="L128" s="22" t="n">
-        <v>1.672</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>-6.611</v>
-      </c>
-      <c r="N128" s="22" t="n">
-        <v>2.258</v>
-      </c>
-      <c r="T128" s="22" t="n">
-        <v>-0.638</v>
-      </c>
-      <c r="U128" s="22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V128" s="22" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>-7.093</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>-6.611</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C129" s="22" t="n">
-        <v>1.183</v>
-      </c>
-      <c r="D129" s="22" t="n">
-        <v>-1.739</v>
-      </c>
-      <c r="E129" s="22" t="n">
-        <v>2.256</v>
-      </c>
-      <c r="F129" s="22" t="n">
-        <v>2.296</v>
-      </c>
-      <c r="G129" s="22" t="n">
-        <v>-4.244</v>
-      </c>
-      <c r="H129" s="22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>-2.098</v>
-      </c>
-      <c r="J129" s="22" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="K129" s="22" t="n">
-        <v>1.358</v>
-      </c>
-      <c r="L129" s="22" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="N129" s="22" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>-0.08400000000000001</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>2.256</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>-2.098</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>0.496</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20" t="inlineStr">
-        <is>
-          <t>지분법 적용회사 지분 해당액</t>
-        </is>
-      </c>
-      <c r="C130" s="22" t="n">
-        <v>1.772</v>
-      </c>
-      <c r="D130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="22" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="F130" s="22" t="n">
-        <v>3.729</v>
-      </c>
-      <c r="G130" s="22" t="n">
-        <v>-7.079</v>
-      </c>
-      <c r="H130" s="22" t="n">
-        <v>5.963</v>
-      </c>
-      <c r="I130" s="22" t="n">
-        <v>-3.342</v>
-      </c>
-      <c r="J130" s="22" t="n">
-        <v>-1.934</v>
-      </c>
-      <c r="K130" s="22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="L130" s="22" t="n">
-        <v>2.926</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>1.265</v>
-      </c>
-      <c r="N130" s="22" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="T130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" s="22" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="V130" s="22" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="W130" s="22" t="n">
-        <v>-3.342</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>1.265</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C131" s="22" t="n">
-        <v>-54.53</v>
-      </c>
-      <c r="D131" s="22" t="n">
-        <v>-85.426</v>
-      </c>
-      <c r="E131" s="22" t="n">
-        <v>34.22</v>
-      </c>
-      <c r="F131" s="22" t="n">
-        <v>-24.331</v>
-      </c>
-      <c r="G131" s="22" t="n">
-        <v>-47.147</v>
-      </c>
-      <c r="H131" s="22" t="n">
-        <v>10.293</v>
-      </c>
-      <c r="I131" s="22" t="n">
-        <v>39.584</v>
-      </c>
-      <c r="J131" s="22" t="n">
-        <v>41.627</v>
-      </c>
-      <c r="K131" s="22" t="n">
-        <v>6.136</v>
-      </c>
-      <c r="L131" s="22" t="n">
-        <v>-118.811</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>-24.396</v>
-      </c>
-      <c r="N131" s="22" t="n">
-        <v>3.788</v>
-      </c>
-      <c r="T131" s="22" t="n">
-        <v>1.609</v>
-      </c>
-      <c r="U131" s="22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V131" s="22" t="n">
-        <v>34.22</v>
-      </c>
-      <c r="W131" s="22" t="n">
-        <v>39.584</v>
-      </c>
-      <c r="X131" s="22" t="n">
-        <v>-24.396</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="n">
-        <v>-2.688</v>
-      </c>
-      <c r="D132" s="12" t="n">
-        <v>45.059</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>387.919</v>
-      </c>
-      <c r="F132" s="12" t="n">
-        <v>16.377</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>620.303</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>946.456</v>
-      </c>
-      <c r="I132" s="12" t="n">
-        <v>1348.617</v>
-      </c>
-      <c r="J132" s="12" t="n">
-        <v>-277.352</v>
-      </c>
-      <c r="K132" s="12" t="n">
-        <v>-292.164</v>
-      </c>
-      <c r="L132" s="12" t="n">
-        <v>-37.4</v>
-      </c>
-      <c r="M132" s="12" t="n">
-        <v>746.268</v>
-      </c>
-      <c r="N132" s="12" t="n">
-        <v>861.361</v>
-      </c>
-      <c r="T132" s="12" t="n">
-        <v>222.869</v>
-      </c>
-      <c r="U132" s="12" t="n">
-        <v>263.868</v>
-      </c>
-      <c r="V132" s="12" t="n">
-        <v>387.919</v>
-      </c>
-      <c r="W132" s="12" t="n">
-        <v>1348.617</v>
-      </c>
-      <c r="X132" s="12" t="n">
-        <v>746.268</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
+          <t>중간순이익(손실)</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="n">
+        <v>51.842</v>
+      </c>
+      <c r="D133" s="12" t="n">
+        <v>130.486</v>
+      </c>
+      <c r="E133" s="12" t="n">
+        <v>353.699</v>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>40.709</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>667.449</v>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>936.164</v>
+      </c>
+      <c r="I133" s="12" t="n">
+        <v>1309.033</v>
+      </c>
+      <c r="J133" s="12" t="n">
+        <v>-318.98</v>
+      </c>
+      <c r="K133" s="12" t="n">
+        <v>-298.3</v>
+      </c>
+      <c r="L133" s="12" t="n">
+        <v>81.413</v>
+      </c>
+      <c r="M133" s="12" t="n">
+        <v>770.664</v>
+      </c>
+      <c r="N133" s="12" t="n">
+        <v>857.572</v>
+      </c>
+      <c r="T133" s="12" t="n">
+        <v>221.26</v>
+      </c>
+      <c r="U133" s="12" t="n">
+        <v>262.348</v>
+      </c>
+      <c r="V133" s="12" t="n">
+        <v>353.699</v>
+      </c>
+      <c r="W133" s="12" t="n">
+        <v>1309.033</v>
+      </c>
+      <c r="X133" s="12" t="n">
+        <v>770.664</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>-54.413</v>
+      </c>
+      <c r="D134" s="22" t="n">
+        <v>-83.655</v>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>31.081</v>
+      </c>
+      <c r="F134" s="22" t="n">
+        <v>-30.201</v>
+      </c>
+      <c r="G134" s="22" t="n">
+        <v>-33.611</v>
+      </c>
+      <c r="H134" s="22" t="n">
+        <v>-8.762</v>
+      </c>
+      <c r="I134" s="22" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="J134" s="22" t="n">
+        <v>45.913</v>
+      </c>
+      <c r="K134" s="22" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="L134" s="22" t="n">
+        <v>-125.285</v>
+      </c>
+      <c r="M134" s="22" t="n">
+        <v>-19.547</v>
+      </c>
+      <c r="N134" s="22" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="T134" s="22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U134" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V134" s="22" t="n">
+        <v>31.081</v>
+      </c>
+      <c r="W134" s="22" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="X134" s="22" t="n">
+        <v>-19.547</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>이연헤지손익</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n">
+        <v>-3.074</v>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="E135" s="22" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="F135" s="22" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>-2.211</v>
+      </c>
+      <c r="H135" s="22" t="n">
+        <v>9.288</v>
+      </c>
+      <c r="I135" s="22" t="n">
+        <v>-7.093</v>
+      </c>
+      <c r="J135" s="22" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="K135" s="22" t="n">
+        <v>6.086</v>
+      </c>
+      <c r="L135" s="22" t="n">
+        <v>1.672</v>
+      </c>
+      <c r="M135" s="22" t="n">
+        <v>-6.611</v>
+      </c>
+      <c r="N135" s="22" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="T135" s="22" t="n">
+        <v>-0.638</v>
+      </c>
+      <c r="U135" s="22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V135" s="22" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="W135" s="22" t="n">
+        <v>-7.093</v>
+      </c>
+      <c r="X135" s="22" t="n">
+        <v>-6.611</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="D136" s="22" t="n">
+        <v>-1.739</v>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>2.256</v>
+      </c>
+      <c r="F136" s="22" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="G136" s="22" t="n">
+        <v>-4.244</v>
+      </c>
+      <c r="H136" s="22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>-2.098</v>
+      </c>
+      <c r="J136" s="22" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="K136" s="22" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="L136" s="22" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="N136" s="22" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="T136" s="22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>2.256</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>-2.098</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>0.496</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>지분법 적용회사 지분 해당액</t>
+        </is>
+      </c>
+      <c r="C137" s="22" t="n">
+        <v>1.772</v>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="22" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>3.729</v>
+      </c>
+      <c r="G137" s="22" t="n">
+        <v>-7.079</v>
+      </c>
+      <c r="H137" s="22" t="n">
+        <v>5.963</v>
+      </c>
+      <c r="I137" s="22" t="n">
+        <v>-3.342</v>
+      </c>
+      <c r="J137" s="22" t="n">
+        <v>-1.934</v>
+      </c>
+      <c r="K137" s="22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L137" s="22" t="n">
+        <v>2.926</v>
+      </c>
+      <c r="M137" s="22" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="N137" s="22" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="T137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" s="22" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="V137" s="22" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-3.342</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>1.265</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="C138" s="22" t="n">
+        <v>-54.53</v>
+      </c>
+      <c r="D138" s="22" t="n">
+        <v>-85.426</v>
+      </c>
+      <c r="E138" s="22" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="F138" s="22" t="n">
+        <v>-24.331</v>
+      </c>
+      <c r="G138" s="22" t="n">
+        <v>-47.147</v>
+      </c>
+      <c r="H138" s="22" t="n">
+        <v>10.293</v>
+      </c>
+      <c r="I138" s="22" t="n">
+        <v>39.584</v>
+      </c>
+      <c r="J138" s="22" t="n">
+        <v>41.627</v>
+      </c>
+      <c r="K138" s="22" t="n">
+        <v>6.136</v>
+      </c>
+      <c r="L138" s="22" t="n">
+        <v>-118.811</v>
+      </c>
+      <c r="M138" s="22" t="n">
+        <v>-24.396</v>
+      </c>
+      <c r="N138" s="22" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="T138" s="22" t="n">
+        <v>1.609</v>
+      </c>
+      <c r="U138" s="22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V138" s="22" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="W138" s="22" t="n">
+        <v>39.584</v>
+      </c>
+      <c r="X138" s="22" t="n">
+        <v>-24.396</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="n">
+        <v>-2.688</v>
+      </c>
+      <c r="D139" s="12" t="n">
+        <v>45.059</v>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>387.919</v>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>16.377</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>620.303</v>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>946.456</v>
+      </c>
+      <c r="I139" s="12" t="n">
+        <v>1348.617</v>
+      </c>
+      <c r="J139" s="12" t="n">
+        <v>-277.352</v>
+      </c>
+      <c r="K139" s="12" t="n">
+        <v>-292.164</v>
+      </c>
+      <c r="L139" s="12" t="n">
+        <v>-37.4</v>
+      </c>
+      <c r="M139" s="12" t="n">
+        <v>746.268</v>
+      </c>
+      <c r="N139" s="12" t="n">
+        <v>861.361</v>
+      </c>
+      <c r="T139" s="12" t="n">
+        <v>222.869</v>
+      </c>
+      <c r="U139" s="12" t="n">
+        <v>263.868</v>
+      </c>
+      <c r="V139" s="12" t="n">
+        <v>387.919</v>
+      </c>
+      <c r="W139" s="12" t="n">
+        <v>1348.617</v>
+      </c>
+      <c r="X139" s="12" t="n">
+        <v>746.268</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C133" s="12" t="n">
+      <c r="C140" s="12" t="n">
         <v>12.142</v>
       </c>
-      <c r="D133" s="12" t="n">
+      <c r="D140" s="12" t="n">
         <v>43.44</v>
       </c>
-      <c r="E133" s="12" t="n">
+      <c r="E140" s="12" t="n">
         <v>381.931</v>
       </c>
-      <c r="F133" s="12" t="n">
+      <c r="F140" s="12" t="n">
         <v>17.389</v>
       </c>
-      <c r="G133" s="12" t="n">
+      <c r="G140" s="12" t="n">
         <v>621.204</v>
       </c>
-      <c r="H133" s="12" t="n">
+      <c r="H140" s="12" t="n">
         <v>942.4930000000001</v>
       </c>
-      <c r="I133" s="12" t="n">
+      <c r="I140" s="12" t="n">
         <v>1334.771</v>
       </c>
-      <c r="J133" s="12" t="n">
+      <c r="J140" s="12" t="n">
         <v>-282.751</v>
       </c>
-      <c r="K133" s="12" t="n">
+      <c r="K140" s="12" t="n">
         <v>-296.248</v>
       </c>
-      <c r="L133" s="12" t="n">
+      <c r="L140" s="12" t="n">
         <v>-43.075</v>
       </c>
-      <c r="M133" s="12" t="n">
+      <c r="M140" s="12" t="n">
         <v>742.652</v>
       </c>
-      <c r="N133" s="12" t="n">
+      <c r="N140" s="12" t="n">
         <v>859.715</v>
       </c>
-      <c r="T133" s="12" t="n">
+      <c r="T140" s="12" t="n">
         <v>199.498</v>
       </c>
-      <c r="U133" s="12" t="n">
+      <c r="U140" s="12" t="n">
         <v>250.43</v>
       </c>
-      <c r="V133" s="12" t="n">
+      <c r="V140" s="12" t="n">
         <v>381.931</v>
       </c>
-      <c r="W133" s="12" t="n">
+      <c r="W140" s="12" t="n">
         <v>1334.771</v>
       </c>
-      <c r="X133" s="12" t="n">
+      <c r="X140" s="12" t="n">
         <v>742.652</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="9" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C134" s="12" t="n">
+      <c r="C141" s="12" t="n">
         <v>-14.831</v>
       </c>
-      <c r="D134" s="12" t="n">
+      <c r="D141" s="12" t="n">
         <v>1.62</v>
       </c>
-      <c r="E134" s="12" t="n">
+      <c r="E141" s="12" t="n">
         <v>5.987</v>
       </c>
-      <c r="F134" s="12" t="n">
+      <c r="F141" s="12" t="n">
         <v>-1.011</v>
       </c>
-      <c r="G134" s="12" t="n">
+      <c r="G141" s="12" t="n">
         <v>-0.901</v>
       </c>
-      <c r="H134" s="12" t="n">
+      <c r="H141" s="12" t="n">
         <v>3.962</v>
       </c>
-      <c r="I134" s="12" t="n">
+      <c r="I141" s="12" t="n">
         <v>13.845</v>
       </c>
-      <c r="J134" s="12" t="n">
+      <c r="J141" s="12" t="n">
         <v>5.398</v>
       </c>
-      <c r="K134" s="12" t="n">
+      <c r="K141" s="12" t="n">
         <v>4.084</v>
       </c>
-      <c r="L134" s="12" t="n">
+      <c r="L141" s="12" t="n">
         <v>5.675</v>
       </c>
-      <c r="M134" s="12" t="n">
+      <c r="M141" s="12" t="n">
         <v>3.616</v>
       </c>
-      <c r="N134" s="12" t="n">
+      <c r="N141" s="12" t="n">
         <v>1.646</v>
       </c>
-      <c r="T134" s="12" t="n">
+      <c r="T141" s="12" t="n">
         <v>23.371</v>
       </c>
-      <c r="U134" s="12" t="n">
+      <c r="U141" s="12" t="n">
         <v>13.437</v>
       </c>
-      <c r="V134" s="12" t="n">
+      <c r="V141" s="12" t="n">
         <v>5.987</v>
       </c>
-      <c r="W134" s="12" t="n">
+      <c r="W141" s="12" t="n">
         <v>13.845</v>
       </c>
-      <c r="X134" s="12" t="n">
+      <c r="X141" s="12" t="n">
         <v>3.616</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="18" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B136" s="44" t="inlineStr">
+      <c r="B143" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C136" s="18" t="n"/>
-      <c r="D136" s="18" t="n"/>
-      <c r="E136" s="18" t="n"/>
-      <c r="F136" s="18" t="n"/>
-      <c r="G136" s="18" t="n"/>
-      <c r="H136" s="18" t="n"/>
-      <c r="I136" s="18" t="n"/>
-      <c r="J136" s="18" t="n"/>
-      <c r="K136" s="18" t="n"/>
-      <c r="L136" s="18" t="n"/>
-      <c r="M136" s="18" t="n"/>
-      <c r="N136" s="18" t="n"/>
-      <c r="O136" s="18" t="n"/>
-      <c r="P136" s="18" t="n"/>
-      <c r="Q136" s="18" t="n"/>
-      <c r="R136" s="18" t="n"/>
-      <c r="S136" s="18" t="n"/>
-      <c r="T136" s="18" t="n"/>
-      <c r="U136" s="18" t="n"/>
-      <c r="V136" s="18" t="n"/>
-      <c r="W136" s="18" t="n"/>
-      <c r="X136" s="18" t="n"/>
-      <c r="Y136" s="18" t="n"/>
-      <c r="Z136" s="18" t="n"/>
-      <c r="AA136" s="18" t="n"/>
-      <c r="AB136" s="18" t="n"/>
-      <c r="AC136" s="18" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="C143" s="18" t="n"/>
+      <c r="D143" s="18" t="n"/>
+      <c r="E143" s="18" t="n"/>
+      <c r="F143" s="18" t="n"/>
+      <c r="G143" s="18" t="n"/>
+      <c r="H143" s="18" t="n"/>
+      <c r="I143" s="18" t="n"/>
+      <c r="J143" s="18" t="n"/>
+      <c r="K143" s="18" t="n"/>
+      <c r="L143" s="18" t="n"/>
+      <c r="M143" s="18" t="n"/>
+      <c r="N143" s="18" t="n"/>
+      <c r="O143" s="18" t="n"/>
+      <c r="P143" s="18" t="n"/>
+      <c r="Q143" s="18" t="n"/>
+      <c r="R143" s="18" t="n"/>
+      <c r="S143" s="18" t="n"/>
+      <c r="T143" s="18" t="n"/>
+      <c r="U143" s="18" t="n"/>
+      <c r="V143" s="18" t="n"/>
+      <c r="W143" s="18" t="n"/>
+      <c r="X143" s="18" t="n"/>
+      <c r="Y143" s="18" t="n"/>
+      <c r="Z143" s="18" t="n"/>
+      <c r="AA143" s="18" t="n"/>
+      <c r="AB143" s="18" t="n"/>
+      <c r="AC143" s="18" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E144" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
+      <c r="F144" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G137" s="5" t="inlineStr">
+      <c r="G144" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H137" s="5" t="inlineStr">
+      <c r="H144" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I137" s="5" t="inlineStr">
+      <c r="I144" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J137" s="5" t="inlineStr">
+      <c r="J144" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K137" s="5" t="inlineStr">
+      <c r="K144" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L137" s="5" t="inlineStr">
+      <c r="L144" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M137" s="5" t="inlineStr">
+      <c r="M144" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N137" s="5" t="inlineStr">
+      <c r="N144" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O137" s="5" t="inlineStr">
+      <c r="O144" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P137" s="5" t="inlineStr">
+      <c r="P144" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q137" s="5" t="inlineStr">
+      <c r="Q144" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R137" s="5" t="inlineStr">
+      <c r="R144" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S137" s="5" t="inlineStr">
+      <c r="S144" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T137" s="5" t="inlineStr">
+      <c r="T144" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U137" s="5" t="inlineStr">
+      <c r="U144" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V137" s="5" t="inlineStr">
+      <c r="V144" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W137" s="5" t="inlineStr">
+      <c r="W144" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X137" s="5" t="inlineStr">
+      <c r="X144" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y137" s="5" t="inlineStr">
+      <c r="Y144" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z137" s="5" t="inlineStr">
+      <c r="Z144" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA137" s="5" t="inlineStr">
+      <c r="AA144" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB137" s="5" t="inlineStr">
+      <c r="AB144" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC137" s="5" t="inlineStr">
+      <c r="AC144" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="9" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="E138" s="12" t="n">
+      <c r="E145" s="12" t="n">
         <v>829.668</v>
       </c>
-      <c r="I138" s="12" t="n">
+      <c r="I145" s="12" t="n">
         <v>3979.224</v>
       </c>
-      <c r="M138" s="12" t="n">
+      <c r="M145" s="12" t="n">
         <v>244.322</v>
       </c>
-      <c r="O138" s="12" t="n">
+      <c r="O145" s="12" t="n">
         <v>796.029</v>
       </c>
-      <c r="P138" s="12" t="n">
+      <c r="P145" s="12" t="n">
         <v>542.249</v>
       </c>
-      <c r="Q138" s="12" t="n">
+      <c r="Q145" s="12" t="n">
         <v>323.905</v>
       </c>
-      <c r="R138" s="12" t="n">
+      <c r="R145" s="12" t="n">
         <v>376.804</v>
       </c>
-      <c r="S138" s="12" t="n">
+      <c r="S145" s="12" t="n">
         <v>1084.857</v>
       </c>
-      <c r="T138" s="12" t="n">
+      <c r="T145" s="12" t="n">
         <v>386.549</v>
       </c>
-      <c r="U138" s="12" t="n">
+      <c r="U145" s="12" t="n">
         <v>959.799</v>
       </c>
-      <c r="V138" s="12" t="n">
+      <c r="V145" s="12" t="n">
         <v>829.668</v>
       </c>
-      <c r="W138" s="12" t="n">
+      <c r="W145" s="12" t="n">
         <v>3979.224</v>
       </c>
-      <c r="X138" s="12" t="n">
+      <c r="X145" s="12" t="n">
         <v>244.322</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E139" s="22" t="n">
-        <v>3135.503</v>
-      </c>
-      <c r="I139" s="22" t="n">
-        <v>4768.734</v>
-      </c>
-      <c r="M139" s="22" t="n">
-        <v>7739.239</v>
-      </c>
-      <c r="O139" s="22" t="n">
-        <v>1598.375</v>
-      </c>
-      <c r="P139" s="22" t="n">
-        <v>2250.153</v>
-      </c>
-      <c r="Q139" s="22" t="n">
-        <v>2529.559</v>
-      </c>
-      <c r="R139" s="22" t="n">
-        <v>3022.923</v>
-      </c>
-      <c r="S139" s="22" t="n">
-        <v>3166.814</v>
-      </c>
-      <c r="T139" s="22" t="n">
-        <v>3253.506</v>
-      </c>
-      <c r="U139" s="22" t="n">
-        <v>2774.76</v>
-      </c>
-      <c r="V139" s="22" t="n">
-        <v>3135.503</v>
-      </c>
-      <c r="W139" s="22" t="n">
-        <v>4768.734</v>
-      </c>
-      <c r="X139" s="22" t="n">
-        <v>7739.239</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="O140" s="22" t="n">
-        <v>10.627</v>
-      </c>
-      <c r="P140" s="22" t="n">
-        <v>6.857</v>
-      </c>
-      <c r="Q140" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" s="22" t="n">
-        <v>405.838</v>
-      </c>
-      <c r="S140" s="22" t="n">
-        <v>100.019</v>
-      </c>
-      <c r="T140" s="22" t="n">
-        <v>142.73</v>
-      </c>
-      <c r="U140" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="E141" s="22" t="n">
-        <v>2.919</v>
-      </c>
-      <c r="I141" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" s="22" t="n">
-        <v>49.551</v>
-      </c>
-      <c r="P141" s="22" t="n">
-        <v>67.35899999999999</v>
-      </c>
-      <c r="Q141" s="22" t="n">
-        <v>129.404</v>
-      </c>
-      <c r="R141" s="22" t="n">
-        <v>52.133</v>
-      </c>
-      <c r="S141" s="22" t="n">
-        <v>23.479</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>23.479</v>
-      </c>
-      <c r="U141" s="22" t="n">
-        <v>14.658</v>
-      </c>
-      <c r="V141" s="22" t="n">
-        <v>2.919</v>
-      </c>
-      <c r="W141" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="E142" s="22" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="I142" s="22" t="n">
-        <v>2.048</v>
-      </c>
-      <c r="M142" s="22" t="n">
-        <v>5.522</v>
-      </c>
-      <c r="O142" s="22" t="n">
-        <v>-0.974</v>
-      </c>
-      <c r="P142" s="22" t="n">
-        <v>0.712</v>
-      </c>
-      <c r="Q142" s="22" t="n">
-        <v>-5.953</v>
-      </c>
-      <c r="R142" s="22" t="n">
-        <v>8.863</v>
-      </c>
-      <c r="S142" s="22" t="n">
-        <v>-25.518</v>
-      </c>
-      <c r="T142" s="22" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="U142" s="22" t="n">
-        <v>-0.154</v>
-      </c>
-      <c r="V142" s="22" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="W142" s="22" t="n">
-        <v>2.048</v>
-      </c>
-      <c r="X142" s="22" t="n">
-        <v>5.522</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E143" s="22" t="n">
-        <v>60.376</v>
-      </c>
-      <c r="I143" s="22" t="n">
-        <v>212.255</v>
-      </c>
-      <c r="M143" s="22" t="n">
-        <v>108.983</v>
-      </c>
-      <c r="O143" s="22" t="n">
-        <v>35.808</v>
-      </c>
-      <c r="P143" s="22" t="n">
-        <v>19.694</v>
-      </c>
-      <c r="Q143" s="22" t="n">
-        <v>35.053</v>
-      </c>
-      <c r="R143" s="22" t="n">
-        <v>22.654</v>
-      </c>
-      <c r="S143" s="22" t="n">
-        <v>31.609</v>
-      </c>
-      <c r="T143" s="22" t="n">
-        <v>25.66</v>
-      </c>
-      <c r="U143" s="22" t="n">
-        <v>37.614</v>
-      </c>
-      <c r="V143" s="22" t="n">
-        <v>60.376</v>
-      </c>
-      <c r="W143" s="22" t="n">
-        <v>212.255</v>
-      </c>
-      <c r="X143" s="22" t="n">
-        <v>108.983</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="20" t="inlineStr">
-        <is>
-          <t>임원 상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E144" s="22" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="I144" s="22" t="n">
-        <v>48.735</v>
-      </c>
-      <c r="M144" s="22" t="n">
-        <v>-16.435</v>
-      </c>
-      <c r="S144" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" s="22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U144" s="22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V144" s="22" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="W144" s="22" t="n">
-        <v>48.735</v>
-      </c>
-      <c r="X144" s="22" t="n">
-        <v>-16.435</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="20" t="inlineStr">
-        <is>
-          <t>주식급여 충당금 증감</t>
-        </is>
-      </c>
-      <c r="E145" s="22" t="n">
-        <v>30.662</v>
-      </c>
-      <c r="I145" s="22" t="n">
-        <v>31.186</v>
-      </c>
-      <c r="M145" s="22" t="n">
-        <v>-6.461</v>
-      </c>
-      <c r="T145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" s="22" t="n">
-        <v>28.666</v>
-      </c>
-      <c r="V145" s="22" t="n">
-        <v>30.662</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>31.186</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>-6.461</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>임원 퇴직위로 충당금 증감</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E146" s="22" t="n">
-        <v>0</v>
+        <v>3135.503</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>50.638</v>
+        <v>4768.734</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>20.141</v>
+        <v>7739.239</v>
+      </c>
+      <c r="O146" s="22" t="n">
+        <v>1598.375</v>
+      </c>
+      <c r="P146" s="22" t="n">
+        <v>2250.153</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>2529.559</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>3022.923</v>
+      </c>
+      <c r="S146" s="22" t="n">
+        <v>3166.814</v>
+      </c>
+      <c r="T146" s="22" t="n">
+        <v>3253.506</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>2774.76</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>0</v>
+        <v>3135.503</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>50.638</v>
+        <v>4768.734</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>20.141</v>
+        <v>7739.239</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="I147" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="M147" s="22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="W147" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="X147" s="22" t="n">
-        <v>3.05</v>
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="O147" s="22" t="n">
+        <v>10.627</v>
+      </c>
+      <c r="P147" s="22" t="n">
+        <v>6.857</v>
+      </c>
+      <c r="Q147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" s="22" t="n">
+        <v>405.838</v>
+      </c>
+      <c r="S147" s="22" t="n">
+        <v>100.019</v>
+      </c>
+      <c r="T147" s="22" t="n">
+        <v>142.73</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>영업권 상각</t>
         </is>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-5.173</v>
+        <v>2.919</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>-21.614</v>
-      </c>
-      <c r="M148" s="22" t="n">
-        <v>-52.094</v>
+        <v>0</v>
       </c>
       <c r="O148" s="22" t="n">
-        <v>-2.496</v>
+        <v>49.551</v>
       </c>
       <c r="P148" s="22" t="n">
-        <v>-2.508</v>
+        <v>67.35899999999999</v>
       </c>
       <c r="Q148" s="22" t="n">
-        <v>-2.505</v>
+        <v>129.404</v>
       </c>
       <c r="R148" s="22" t="n">
-        <v>-4.02</v>
+        <v>52.133</v>
       </c>
       <c r="S148" s="22" t="n">
-        <v>-3.157</v>
+        <v>23.479</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>-3.873</v>
+        <v>23.479</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>-3.639</v>
+        <v>14.658</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>-5.173</v>
+        <v>2.919</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>-21.614</v>
-      </c>
-      <c r="X148" s="22" t="n">
-        <v>-52.094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="E149" s="22" t="n">
-        <v>173.679</v>
+        <v>0.437</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>255.562</v>
+        <v>2.048</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>538.822</v>
+        <v>5.522</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>169.504</v>
+        <v>-0.974</v>
       </c>
       <c r="P149" s="22" t="n">
-        <v>189.024</v>
+        <v>0.712</v>
       </c>
       <c r="Q149" s="22" t="n">
-        <v>191.605</v>
+        <v>-5.953</v>
       </c>
       <c r="R149" s="22" t="n">
-        <v>197.629</v>
+        <v>8.863</v>
       </c>
       <c r="S149" s="22" t="n">
-        <v>199.731</v>
+        <v>-25.518</v>
       </c>
       <c r="T149" s="22" t="n">
-        <v>171.05</v>
+        <v>-1.4</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>154.641</v>
+        <v>-0.154</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>173.679</v>
+        <v>0.437</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>255.562</v>
+        <v>2.048</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>538.822</v>
+        <v>5.522</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="E150" s="22" t="n">
-        <v>1.459</v>
+        <v>60.376</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>109.528</v>
+        <v>212.255</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>0</v>
+        <v>108.983</v>
+      </c>
+      <c r="O150" s="22" t="n">
+        <v>35.808</v>
+      </c>
+      <c r="P150" s="22" t="n">
+        <v>19.694</v>
+      </c>
+      <c r="Q150" s="22" t="n">
+        <v>35.053</v>
+      </c>
+      <c r="R150" s="22" t="n">
+        <v>22.654</v>
+      </c>
+      <c r="S150" s="22" t="n">
+        <v>31.609</v>
+      </c>
+      <c r="T150" s="22" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="U150" s="22" t="n">
+        <v>37.614</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>1.459</v>
+        <v>60.376</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>109.528</v>
+        <v>212.255</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>0</v>
+        <v>108.983</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>Loss Gain On Investments In Partnership Ope CF</t>
+          <t>임원 상여충당금 증감</t>
         </is>
       </c>
       <c r="E151" s="22" t="n">
-        <v>4.287</v>
+        <v>-2.25</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>-14.746</v>
+        <v>48.735</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>8.773999999999999</v>
-      </c>
-      <c r="O151" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" s="22" t="n">
-        <v>-9.741</v>
-      </c>
-      <c r="Q151" s="22" t="n">
-        <v>5.484</v>
-      </c>
-      <c r="R151" s="22" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-16.435</v>
       </c>
       <c r="S151" s="22" t="n">
-        <v>1.317</v>
+        <v>0</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>18.336</v>
+        <v>1.35</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>7.83</v>
+        <v>5.4</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>4.287</v>
+        <v>-2.25</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>-14.746</v>
+        <v>48.735</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>8.773999999999999</v>
+        <v>-16.435</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
+          <t>주식급여 충당금 증감</t>
         </is>
       </c>
       <c r="E152" s="22" t="n">
-        <v>1.483</v>
+        <v>30.662</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>52.012</v>
+        <v>31.186</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>14.713</v>
-      </c>
-      <c r="O152" s="22" t="n">
-        <v>9.007999999999999</v>
-      </c>
-      <c r="P152" s="22" t="n">
-        <v>24.287</v>
-      </c>
-      <c r="Q152" s="22" t="n">
-        <v>2.787</v>
-      </c>
-      <c r="R152" s="22" t="n">
-        <v>13.473</v>
-      </c>
-      <c r="S152" s="22" t="n">
-        <v>19.824</v>
+        <v>-6.461</v>
       </c>
       <c r="T152" s="22" t="n">
-        <v>43.822</v>
+        <v>0</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>13.291</v>
+        <v>28.666</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>1.483</v>
+        <v>30.662</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>52.012</v>
+        <v>31.186</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>14.713</v>
+        <v>-6.461</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>Income By Government Subsidies Ope CF</t>
+          <t>임원 퇴직위로 충당금 증감</t>
         </is>
       </c>
       <c r="E153" s="22" t="n">
-        <v>-1624.819</v>
+        <v>0</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>-6119.744</v>
+        <v>50.638</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>-14311.693</v>
-      </c>
-      <c r="P153" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q153" s="22" t="n">
-        <v>-311.213</v>
-      </c>
-      <c r="R153" s="22" t="n">
-        <v>-77.202</v>
-      </c>
-      <c r="S153" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U153" s="22" t="n">
-        <v>0</v>
+        <v>20.141</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>-1624.819</v>
+        <v>0</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>-6119.744</v>
+        <v>50.638</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>-14311.693</v>
+        <v>20.141</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>고정자산 압축손실</t>
-        </is>
-      </c>
-      <c r="E154" s="22" t="n">
-        <v>1624.819</v>
+          <t>퇴직급여부채 증감</t>
+        </is>
       </c>
       <c r="I154" s="22" t="n">
-        <v>6119.744</v>
+        <v>30</v>
       </c>
       <c r="M154" s="22" t="n">
-        <v>14311.693</v>
-      </c>
-      <c r="P154" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" s="22" t="n">
-        <v>265.277</v>
-      </c>
-      <c r="R154" s="22" t="n">
-        <v>77.202</v>
-      </c>
-      <c r="S154" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" s="22" t="n">
-        <v>1624.819</v>
+        <v>3.05</v>
       </c>
       <c r="W154" s="22" t="n">
-        <v>6119.744</v>
+        <v>30</v>
       </c>
       <c r="X154" s="22" t="n">
-        <v>14311.693</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손익</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="E155" s="22" t="n">
-        <v>-5.868</v>
+        <v>-5.173</v>
       </c>
       <c r="I155" s="22" t="n">
-        <v>-0.806</v>
+        <v>-21.614</v>
       </c>
       <c r="M155" s="22" t="n">
-        <v>2.036</v>
+        <v>-52.094</v>
       </c>
       <c r="O155" s="22" t="n">
-        <v>0.166</v>
+        <v>-2.496</v>
       </c>
       <c r="P155" s="22" t="n">
-        <v>0</v>
+        <v>-2.508</v>
       </c>
       <c r="Q155" s="22" t="n">
-        <v>-0.004</v>
+        <v>-2.505</v>
       </c>
       <c r="R155" s="22" t="n">
-        <v>2.527</v>
+        <v>-4.02</v>
       </c>
       <c r="S155" s="22" t="n">
-        <v>6.316</v>
+        <v>-3.157</v>
       </c>
       <c r="T155" s="22" t="n">
-        <v>-9.720000000000001</v>
+        <v>-3.873</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>-8.574</v>
+        <v>-3.639</v>
       </c>
       <c r="V155" s="22" t="n">
-        <v>-5.868</v>
+        <v>-5.173</v>
       </c>
       <c r="W155" s="22" t="n">
-        <v>-0.806</v>
+        <v>-21.614</v>
       </c>
       <c r="X155" s="22" t="n">
-        <v>2.036</v>
+        <v>-52.094</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>고정자산 수증이익</t>
-        </is>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="E156" s="22" t="n">
+        <v>173.679</v>
+      </c>
+      <c r="I156" s="22" t="n">
+        <v>255.562</v>
+      </c>
+      <c r="M156" s="22" t="n">
+        <v>538.822</v>
       </c>
       <c r="O156" s="22" t="n">
-        <v>-4.702</v>
+        <v>169.504</v>
       </c>
       <c r="P156" s="22" t="n">
-        <v>0</v>
+        <v>189.024</v>
+      </c>
+      <c r="Q156" s="22" t="n">
+        <v>191.605</v>
+      </c>
+      <c r="R156" s="22" t="n">
+        <v>197.629</v>
+      </c>
+      <c r="S156" s="22" t="n">
+        <v>199.731</v>
+      </c>
+      <c r="T156" s="22" t="n">
+        <v>171.05</v>
+      </c>
+      <c r="U156" s="22" t="n">
+        <v>154.641</v>
+      </c>
+      <c r="V156" s="22" t="n">
+        <v>173.679</v>
+      </c>
+      <c r="W156" s="22" t="n">
+        <v>255.562</v>
+      </c>
+      <c r="X156" s="22" t="n">
+        <v>538.822</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>위약금 수입</t>
-        </is>
-      </c>
-      <c r="R157" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" s="22" t="n">
-        <v>-72.67</v>
-      </c>
-      <c r="T157" s="22" t="n">
+          <t>주식교부비</t>
+        </is>
+      </c>
+      <c r="E157" s="22" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="I157" s="22" t="n">
+        <v>109.528</v>
+      </c>
+      <c r="M157" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="22" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="W157" s="22" t="n">
+        <v>109.528</v>
+      </c>
+      <c r="X157" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>Settlement Received Ope CF</t>
-        </is>
+          <t>투자사업조합 운용 손익(△는 이익)</t>
+        </is>
+      </c>
+      <c r="E158" s="22" t="n">
+        <v>4.287</v>
+      </c>
+      <c r="I158" s="22" t="n">
+        <v>-14.746</v>
+      </c>
+      <c r="M158" s="22" t="n">
+        <v>8.773999999999999</v>
+      </c>
+      <c r="O158" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="22" t="n">
+        <v>-9.741</v>
+      </c>
+      <c r="Q158" s="22" t="n">
+        <v>5.484</v>
       </c>
       <c r="R158" s="22" t="n">
-        <v>0</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="S158" s="22" t="n">
-        <v>-54.513</v>
+        <v>1.317</v>
       </c>
       <c r="T158" s="22" t="n">
-        <v>0</v>
+        <v>18.336</v>
+      </c>
+      <c r="U158" s="22" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="V158" s="22" t="n">
+        <v>4.287</v>
+      </c>
+      <c r="W158" s="22" t="n">
+        <v>-14.746</v>
+      </c>
+      <c r="X158" s="22" t="n">
+        <v>8.773999999999999</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
-        </is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="E159" s="22" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="I159" s="22" t="n">
+        <v>52.012</v>
+      </c>
+      <c r="M159" s="22" t="n">
+        <v>14.713</v>
+      </c>
+      <c r="O159" s="22" t="n">
+        <v>9.007999999999999</v>
+      </c>
+      <c r="P159" s="22" t="n">
+        <v>24.287</v>
       </c>
       <c r="Q159" s="22" t="n">
-        <v>0</v>
+        <v>2.787</v>
       </c>
       <c r="R159" s="22" t="n">
-        <v>-10</v>
+        <v>13.473</v>
       </c>
       <c r="S159" s="22" t="n">
-        <v>0</v>
+        <v>19.824</v>
+      </c>
+      <c r="T159" s="22" t="n">
+        <v>43.822</v>
+      </c>
+      <c r="U159" s="22" t="n">
+        <v>13.291</v>
+      </c>
+      <c r="V159" s="22" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="W159" s="22" t="n">
+        <v>52.012</v>
+      </c>
+      <c r="X159" s="22" t="n">
+        <v>14.713</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>Settlement Package Ope CF</t>
-        </is>
+          <t>Income By Government Subsidies Ope CF</t>
+        </is>
+      </c>
+      <c r="E160" s="22" t="n">
+        <v>-1624.819</v>
+      </c>
+      <c r="I160" s="22" t="n">
+        <v>-6119.744</v>
+      </c>
+      <c r="M160" s="22" t="n">
+        <v>-14311.693</v>
+      </c>
+      <c r="P160" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="22" t="n">
+        <v>-311.213</v>
       </c>
       <c r="R160" s="22" t="n">
-        <v>0</v>
+        <v>-77.202</v>
       </c>
       <c r="S160" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T160" s="22" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U160" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="22" t="n">
+        <v>-1624.819</v>
+      </c>
+      <c r="W160" s="22" t="n">
+        <v>-6119.744</v>
+      </c>
+      <c r="X160" s="22" t="n">
+        <v>-14311.693</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
+          <t>고정자산 압축손실</t>
         </is>
       </c>
       <c r="E161" s="22" t="n">
-        <v>-61.318</v>
+        <v>1624.819</v>
       </c>
       <c r="I161" s="22" t="n">
-        <v>0</v>
+        <v>6119.744</v>
       </c>
       <c r="M161" s="22" t="n">
-        <v>-155.595</v>
-      </c>
-      <c r="O161" s="22" t="n">
-        <v>-17.071</v>
+        <v>14311.693</v>
       </c>
       <c r="P161" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="Q161" s="22" t="n">
+        <v>265.277</v>
+      </c>
+      <c r="R161" s="22" t="n">
+        <v>77.202</v>
+      </c>
+      <c r="S161" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="U161" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>-61.318</v>
+        <v>1624.819</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>0</v>
+        <v>6119.744</v>
       </c>
       <c r="X161" s="22" t="n">
-        <v>-155.595</v>
+        <v>14311.693</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
+          <t>고정자산 매각손익</t>
         </is>
       </c>
       <c r="E162" s="22" t="n">
-        <v>0</v>
+        <v>-5.868</v>
       </c>
       <c r="I162" s="22" t="n">
-        <v>29.999</v>
+        <v>-0.806</v>
       </c>
       <c r="M162" s="22" t="n">
-        <v>0</v>
+        <v>2.036</v>
       </c>
       <c r="O162" s="22" t="n">
-        <v>13.184</v>
+        <v>0.166</v>
       </c>
       <c r="P162" s="22" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="22" t="n">
-        <v>103.045</v>
+        <v>-0.004</v>
       </c>
       <c r="R162" s="22" t="n">
-        <v>1.908</v>
+        <v>2.527</v>
       </c>
       <c r="S162" s="22" t="n">
-        <v>0</v>
+        <v>6.316</v>
+      </c>
+      <c r="T162" s="22" t="n">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="U162" s="22" t="n">
+        <v>-8.574</v>
       </c>
       <c r="V162" s="22" t="n">
-        <v>0</v>
+        <v>-5.868</v>
       </c>
       <c r="W162" s="22" t="n">
-        <v>29.999</v>
+        <v>-0.806</v>
       </c>
       <c r="X162" s="22" t="n">
-        <v>0</v>
+        <v>2.036</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>미수 소비세 증감</t>
-        </is>
-      </c>
-      <c r="E163" s="22" t="n">
-        <v>-356.745</v>
-      </c>
-      <c r="I163" s="22" t="n">
-        <v>-1274.235</v>
-      </c>
-      <c r="M163" s="22" t="n">
-        <v>-544.572</v>
+          <t>고정자산 수증이익</t>
+        </is>
       </c>
       <c r="O163" s="22" t="n">
-        <v>-252.734</v>
+        <v>-4.702</v>
       </c>
       <c r="P163" s="22" t="n">
-        <v>376.446</v>
-      </c>
-      <c r="Q163" s="22" t="n">
-        <v>-199.607</v>
-      </c>
-      <c r="R163" s="22" t="n">
-        <v>199.607</v>
-      </c>
-      <c r="S163" s="22" t="n">
-        <v>-55.032</v>
-      </c>
-      <c r="T163" s="22" t="n">
-        <v>55.032</v>
-      </c>
-      <c r="U163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V163" s="22" t="n">
-        <v>-356.745</v>
-      </c>
-      <c r="W163" s="22" t="n">
-        <v>-1274.235</v>
-      </c>
-      <c r="X163" s="22" t="n">
-        <v>-544.572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="E164" s="22" t="n">
-        <v>-131.375</v>
-      </c>
-      <c r="I164" s="22" t="n">
-        <v>-8.226000000000001</v>
-      </c>
-      <c r="M164" s="22" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="O164" s="22" t="n">
-        <v>12.765</v>
-      </c>
-      <c r="P164" s="22" t="n">
-        <v>249.375</v>
-      </c>
-      <c r="Q164" s="22" t="n">
-        <v>-99.048</v>
+          <t>위약금 수입</t>
+        </is>
       </c>
       <c r="R164" s="22" t="n">
-        <v>448.6</v>
+        <v>0</v>
       </c>
       <c r="S164" s="22" t="n">
-        <v>-258.123</v>
+        <v>-72.67</v>
       </c>
       <c r="T164" s="22" t="n">
-        <v>-77.179</v>
-      </c>
-      <c r="U164" s="22" t="n">
-        <v>37.46</v>
-      </c>
-      <c r="V164" s="22" t="n">
-        <v>-131.375</v>
-      </c>
-      <c r="W164" s="22" t="n">
-        <v>-8.226000000000001</v>
-      </c>
-      <c r="X164" s="22" t="n">
-        <v>0.9350000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="E165" s="22" t="n">
-        <v>-848.745</v>
-      </c>
-      <c r="I165" s="22" t="n">
-        <v>-4336.737</v>
-      </c>
-      <c r="M165" s="22" t="n">
-        <v>2764.99</v>
-      </c>
-      <c r="O165" s="22" t="n">
-        <v>-190.419</v>
-      </c>
-      <c r="P165" s="22" t="n">
-        <v>-155.664</v>
-      </c>
-      <c r="Q165" s="22" t="n">
-        <v>-433.373</v>
+          <t>화해금 수령</t>
+        </is>
       </c>
       <c r="R165" s="22" t="n">
-        <v>-301.119</v>
+        <v>0</v>
       </c>
       <c r="S165" s="22" t="n">
-        <v>139.068</v>
+        <v>-54.513</v>
       </c>
       <c r="T165" s="22" t="n">
-        <v>-532.948</v>
-      </c>
-      <c r="U165" s="22" t="n">
-        <v>307.77</v>
-      </c>
-      <c r="V165" s="22" t="n">
-        <v>-848.745</v>
-      </c>
-      <c r="W165" s="22" t="n">
-        <v>-4336.737</v>
-      </c>
-      <c r="X165" s="22" t="n">
-        <v>2764.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>선수금 증감</t>
-        </is>
-      </c>
-      <c r="E166" s="22" t="n">
-        <v>114.746</v>
-      </c>
-      <c r="I166" s="22" t="n">
-        <v>1109.342</v>
-      </c>
-      <c r="M166" s="22" t="n">
-        <v>2549.518</v>
-      </c>
-      <c r="O166" s="22" t="n">
-        <v>118.988</v>
-      </c>
-      <c r="P166" s="22" t="n">
-        <v>230.646</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="Q166" s="22" t="n">
-        <v>313.213</v>
+        <v>0</v>
       </c>
       <c r="R166" s="22" t="n">
-        <v>883.6130000000001</v>
+        <v>-10</v>
       </c>
       <c r="S166" s="22" t="n">
-        <v>276.043</v>
-      </c>
-      <c r="T166" s="22" t="n">
-        <v>36.803</v>
-      </c>
-      <c r="U166" s="22" t="n">
-        <v>439.754</v>
-      </c>
-      <c r="V166" s="22" t="n">
-        <v>114.746</v>
-      </c>
-      <c r="W166" s="22" t="n">
-        <v>1109.342</v>
-      </c>
-      <c r="X166" s="22" t="n">
-        <v>2549.518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="E167" s="22" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="I167" s="22" t="n">
-        <v>-41.905</v>
-      </c>
-      <c r="M167" s="22" t="n">
-        <v>-489.31</v>
-      </c>
-      <c r="O167" s="22" t="n">
-        <v>-6.025</v>
-      </c>
-      <c r="P167" s="22" t="n">
-        <v>-300.177</v>
-      </c>
-      <c r="Q167" s="22" t="n">
-        <v>-246.773</v>
+          <t>Settlement Package Ope CF</t>
+        </is>
       </c>
       <c r="R167" s="22" t="n">
-        <v>291.377</v>
+        <v>0</v>
       </c>
       <c r="S167" s="22" t="n">
-        <v>113.209</v>
+        <v>10</v>
       </c>
       <c r="T167" s="22" t="n">
-        <v>-105.562</v>
-      </c>
-      <c r="U167" s="22" t="n">
-        <v>162.001</v>
-      </c>
-      <c r="V167" s="22" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="W167" s="22" t="n">
-        <v>-41.905</v>
-      </c>
-      <c r="X167" s="22" t="n">
-        <v>-489.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>투자유가증권 매각손익</t>
         </is>
       </c>
       <c r="E168" s="22" t="n">
-        <v>-288.711</v>
+        <v>-61.318</v>
       </c>
       <c r="I168" s="22" t="n">
-        <v>1047.14</v>
+        <v>0</v>
       </c>
       <c r="M168" s="22" t="n">
-        <v>-535.282</v>
+        <v>-155.595</v>
       </c>
       <c r="O168" s="22" t="n">
-        <v>62.735</v>
+        <v>-17.071</v>
       </c>
       <c r="P168" s="22" t="n">
-        <v>57.431</v>
-      </c>
-      <c r="Q168" s="22" t="n">
-        <v>172.379</v>
-      </c>
-      <c r="R168" s="22" t="n">
-        <v>-3.145</v>
-      </c>
-      <c r="S168" s="22" t="n">
-        <v>-133.081</v>
-      </c>
-      <c r="T168" s="22" t="n">
-        <v>1055.893</v>
+        <v>0</v>
       </c>
       <c r="U168" s="22" t="n">
-        <v>-696.37</v>
+        <v>0</v>
       </c>
       <c r="V168" s="22" t="n">
-        <v>-288.711</v>
+        <v>-61.318</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>1047.14</v>
+        <v>0</v>
       </c>
       <c r="X168" s="22" t="n">
-        <v>-535.282</v>
+        <v>-155.595</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>투자유가증권 평가손익</t>
         </is>
       </c>
       <c r="E169" s="22" t="n">
-        <v>694.696</v>
+        <v>0</v>
       </c>
       <c r="I169" s="22" t="n">
-        <v>302.101</v>
+        <v>29.999</v>
       </c>
       <c r="M169" s="22" t="n">
-        <v>-4141.055</v>
+        <v>0</v>
       </c>
       <c r="O169" s="22" t="n">
-        <v>-152.043</v>
+        <v>13.184</v>
       </c>
       <c r="P169" s="22" t="n">
-        <v>1.054</v>
+        <v>0</v>
       </c>
       <c r="Q169" s="22" t="n">
-        <v>-130.426</v>
+        <v>103.045</v>
       </c>
       <c r="R169" s="22" t="n">
-        <v>-546.058</v>
+        <v>1.908</v>
       </c>
       <c r="S169" s="22" t="n">
-        <v>-75.792</v>
-      </c>
-      <c r="T169" s="22" t="n">
-        <v>-207.995</v>
-      </c>
-      <c r="U169" s="22" t="n">
-        <v>-62.786</v>
+        <v>0</v>
       </c>
       <c r="V169" s="22" t="n">
-        <v>694.696</v>
+        <v>0</v>
       </c>
       <c r="W169" s="22" t="n">
-        <v>302.101</v>
+        <v>29.999</v>
       </c>
       <c r="X169" s="22" t="n">
-        <v>-4141.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>미수 소비세 증감</t>
         </is>
       </c>
       <c r="E170" s="22" t="n">
-        <v>3357.899</v>
+        <v>-356.745</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>6330.24</v>
+        <v>-1274.235</v>
       </c>
       <c r="M170" s="22" t="n">
-        <v>8060.243</v>
+        <v>-544.572</v>
       </c>
       <c r="O170" s="22" t="n">
-        <v>2250.277</v>
+        <v>-252.734</v>
       </c>
       <c r="P170" s="22" t="n">
-        <v>3547.201</v>
+        <v>376.446</v>
       </c>
       <c r="Q170" s="22" t="n">
-        <v>2642.81</v>
+        <v>-199.607</v>
       </c>
       <c r="R170" s="22" t="n">
-        <v>5062.678</v>
+        <v>199.607</v>
       </c>
       <c r="S170" s="22" t="n">
-        <v>4494.401</v>
+        <v>-55.032</v>
       </c>
       <c r="T170" s="22" t="n">
-        <v>4275.535</v>
+        <v>55.032</v>
       </c>
       <c r="U170" s="22" t="n">
-        <v>4172.125</v>
+        <v>0</v>
       </c>
       <c r="V170" s="22" t="n">
-        <v>3357.899</v>
+        <v>-356.745</v>
       </c>
       <c r="W170" s="22" t="n">
-        <v>6330.24</v>
+        <v>-1274.235</v>
       </c>
       <c r="X170" s="22" t="n">
-        <v>8060.243</v>
+        <v>-544.572</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="E171" s="22" t="n">
-        <v>5.084</v>
+        <v>-131.375</v>
       </c>
       <c r="I171" s="22" t="n">
-        <v>21.078</v>
+        <v>-8.226000000000001</v>
       </c>
       <c r="M171" s="22" t="n">
-        <v>39.093</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="O171" s="22" t="n">
-        <v>2.495</v>
+        <v>12.765</v>
       </c>
       <c r="P171" s="22" t="n">
-        <v>2.509</v>
+        <v>249.375</v>
       </c>
       <c r="Q171" s="22" t="n">
-        <v>2.504</v>
+        <v>-99.048</v>
       </c>
       <c r="R171" s="22" t="n">
-        <v>4.017</v>
+        <v>448.6</v>
       </c>
       <c r="S171" s="22" t="n">
-        <v>3.163</v>
+        <v>-258.123</v>
       </c>
       <c r="T171" s="22" t="n">
-        <v>3.872</v>
+        <v>-77.179</v>
       </c>
       <c r="U171" s="22" t="n">
-        <v>3.639</v>
+        <v>37.46</v>
       </c>
       <c r="V171" s="22" t="n">
-        <v>5.084</v>
+        <v>-131.375</v>
       </c>
       <c r="W171" s="22" t="n">
-        <v>21.078</v>
+        <v>-8.226000000000001</v>
       </c>
       <c r="X171" s="22" t="n">
-        <v>39.093</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="E172" s="22" t="n">
-        <v>-173.507</v>
+        <v>-848.745</v>
       </c>
       <c r="I172" s="22" t="n">
-        <v>-259.091</v>
+        <v>-4336.737</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>-548.114</v>
+        <v>2764.99</v>
       </c>
       <c r="O172" s="22" t="n">
-        <v>-169.374</v>
+        <v>-190.419</v>
       </c>
       <c r="P172" s="22" t="n">
-        <v>-189.022</v>
+        <v>-155.664</v>
       </c>
       <c r="Q172" s="22" t="n">
-        <v>-192.286</v>
+        <v>-433.373</v>
       </c>
       <c r="R172" s="22" t="n">
-        <v>-197.362</v>
+        <v>-301.119</v>
       </c>
       <c r="S172" s="22" t="n">
-        <v>-199.303</v>
+        <v>139.068</v>
       </c>
       <c r="T172" s="22" t="n">
-        <v>-170.445</v>
+        <v>-532.948</v>
       </c>
       <c r="U172" s="22" t="n">
-        <v>-154.745</v>
+        <v>307.77</v>
       </c>
       <c r="V172" s="22" t="n">
-        <v>-173.507</v>
+        <v>-848.745</v>
       </c>
       <c r="W172" s="22" t="n">
-        <v>-259.091</v>
+        <v>-4336.737</v>
       </c>
       <c r="X172" s="22" t="n">
-        <v>-548.114</v>
+        <v>2764.99</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>선수금 증감</t>
         </is>
       </c>
       <c r="E173" s="22" t="n">
-        <v>-305.342</v>
+        <v>114.746</v>
       </c>
       <c r="I173" s="22" t="n">
-        <v>-304.663</v>
+        <v>1109.342</v>
       </c>
       <c r="M173" s="22" t="n">
-        <v>-1327.646</v>
+        <v>2549.518</v>
       </c>
       <c r="O173" s="22" t="n">
-        <v>-230.676</v>
+        <v>118.988</v>
       </c>
       <c r="P173" s="22" t="n">
-        <v>-292.8</v>
+        <v>230.646</v>
       </c>
       <c r="Q173" s="22" t="n">
-        <v>-221.753</v>
+        <v>313.213</v>
       </c>
       <c r="R173" s="22" t="n">
-        <v>-297.139</v>
+        <v>883.6130000000001</v>
       </c>
       <c r="S173" s="22" t="n">
-        <v>-304.808</v>
+        <v>276.043</v>
       </c>
       <c r="T173" s="22" t="n">
-        <v>-151.215</v>
+        <v>36.803</v>
       </c>
       <c r="U173" s="22" t="n">
-        <v>-57.599</v>
+        <v>439.754</v>
       </c>
       <c r="V173" s="22" t="n">
-        <v>-305.342</v>
+        <v>114.746</v>
       </c>
       <c r="W173" s="22" t="n">
-        <v>-304.663</v>
+        <v>1109.342</v>
       </c>
       <c r="X173" s="22" t="n">
-        <v>-1327.646</v>
+        <v>2549.518</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
-        </is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="E174" s="22" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="I174" s="22" t="n">
+        <v>-41.905</v>
+      </c>
+      <c r="M174" s="22" t="n">
+        <v>-489.31</v>
+      </c>
+      <c r="O174" s="22" t="n">
+        <v>-6.025</v>
+      </c>
+      <c r="P174" s="22" t="n">
+        <v>-300.177</v>
       </c>
       <c r="Q174" s="22" t="n">
-        <v>0</v>
+        <v>-246.773</v>
       </c>
       <c r="R174" s="22" t="n">
-        <v>10</v>
+        <v>291.377</v>
       </c>
       <c r="S174" s="22" t="n">
-        <v>0</v>
+        <v>113.209</v>
+      </c>
+      <c r="T174" s="22" t="n">
+        <v>-105.562</v>
+      </c>
+      <c r="U174" s="22" t="n">
+        <v>162.001</v>
+      </c>
+      <c r="V174" s="22" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="W174" s="22" t="n">
+        <v>-41.905</v>
+      </c>
+      <c r="X174" s="22" t="n">
+        <v>-489.31</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>Penalty Income Received Ope CF</t>
-        </is>
+          <t>매입채무 증감</t>
+        </is>
+      </c>
+      <c r="E175" s="22" t="n">
+        <v>-288.711</v>
+      </c>
+      <c r="I175" s="22" t="n">
+        <v>1047.14</v>
+      </c>
+      <c r="M175" s="22" t="n">
+        <v>-535.282</v>
+      </c>
+      <c r="O175" s="22" t="n">
+        <v>62.735</v>
+      </c>
+      <c r="P175" s="22" t="n">
+        <v>57.431</v>
+      </c>
+      <c r="Q175" s="22" t="n">
+        <v>172.379</v>
       </c>
       <c r="R175" s="22" t="n">
-        <v>0</v>
+        <v>-3.145</v>
       </c>
       <c r="S175" s="22" t="n">
-        <v>72.67</v>
+        <v>-133.081</v>
       </c>
       <c r="T175" s="22" t="n">
-        <v>0</v>
+        <v>1055.893</v>
+      </c>
+      <c r="U175" s="22" t="n">
+        <v>-696.37</v>
+      </c>
+      <c r="V175" s="22" t="n">
+        <v>-288.711</v>
+      </c>
+      <c r="W175" s="22" t="n">
+        <v>1047.14</v>
+      </c>
+      <c r="X175" s="22" t="n">
+        <v>-535.282</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>화해금 수취액</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E176" s="22" t="n">
+        <v>694.696</v>
+      </c>
+      <c r="I176" s="22" t="n">
+        <v>302.101</v>
+      </c>
+      <c r="M176" s="22" t="n">
+        <v>-4141.055</v>
+      </c>
+      <c r="O176" s="22" t="n">
+        <v>-152.043</v>
+      </c>
+      <c r="P176" s="22" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="Q176" s="22" t="n">
+        <v>-130.426</v>
       </c>
       <c r="R176" s="22" t="n">
-        <v>0</v>
+        <v>-546.058</v>
       </c>
       <c r="S176" s="22" t="n">
-        <v>54.513</v>
+        <v>-75.792</v>
       </c>
       <c r="T176" s="22" t="n">
-        <v>0</v>
+        <v>-207.995</v>
+      </c>
+      <c r="U176" s="22" t="n">
+        <v>-62.786</v>
+      </c>
+      <c r="V176" s="22" t="n">
+        <v>694.696</v>
+      </c>
+      <c r="W176" s="22" t="n">
+        <v>302.101</v>
+      </c>
+      <c r="X176" s="22" t="n">
+        <v>-4141.055</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>Settlement Package Paid Ope CF</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="E177" s="22" t="n">
+        <v>3357.899</v>
+      </c>
+      <c r="I177" s="22" t="n">
+        <v>6330.24</v>
+      </c>
+      <c r="M177" s="22" t="n">
+        <v>8060.243</v>
+      </c>
+      <c r="O177" s="22" t="n">
+        <v>2250.277</v>
+      </c>
+      <c r="P177" s="22" t="n">
+        <v>3547.201</v>
+      </c>
+      <c r="Q177" s="22" t="n">
+        <v>2642.81</v>
       </c>
       <c r="R177" s="22" t="n">
-        <v>0</v>
+        <v>5062.678</v>
       </c>
       <c r="S177" s="22" t="n">
-        <v>-10</v>
+        <v>4494.401</v>
       </c>
       <c r="T177" s="22" t="n">
-        <v>0</v>
+        <v>4275.535</v>
+      </c>
+      <c r="U177" s="22" t="n">
+        <v>4172.125</v>
+      </c>
+      <c r="V177" s="22" t="n">
+        <v>3357.899</v>
+      </c>
+      <c r="W177" s="22" t="n">
+        <v>6330.24</v>
+      </c>
+      <c r="X177" s="22" t="n">
+        <v>8060.243</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E178" s="12" t="n">
-        <v>2884.133</v>
-      </c>
-      <c r="I178" s="12" t="n">
-        <v>5787.563</v>
-      </c>
-      <c r="M178" s="12" t="n">
-        <v>6223.575</v>
-      </c>
-      <c r="O178" s="12" t="n">
-        <v>1852.721</v>
-      </c>
-      <c r="P178" s="12" t="n">
-        <v>3067.888</v>
-      </c>
-      <c r="Q178" s="12" t="n">
-        <v>2231.274</v>
-      </c>
-      <c r="R178" s="12" t="n">
-        <v>4582.193</v>
-      </c>
-      <c r="S178" s="12" t="n">
-        <v>4110.636</v>
-      </c>
-      <c r="T178" s="12" t="n">
-        <v>3957.746</v>
-      </c>
-      <c r="U178" s="12" t="n">
-        <v>3963.42</v>
-      </c>
-      <c r="V178" s="12" t="n">
-        <v>2884.133</v>
-      </c>
-      <c r="W178" s="12" t="n">
-        <v>5787.563</v>
-      </c>
-      <c r="X178" s="12" t="n">
-        <v>6223.575</v>
+      <c r="A178" s="20" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="E178" s="22" t="n">
+        <v>5.084</v>
+      </c>
+      <c r="I178" s="22" t="n">
+        <v>21.078</v>
+      </c>
+      <c r="M178" s="22" t="n">
+        <v>39.093</v>
+      </c>
+      <c r="O178" s="22" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="P178" s="22" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="Q178" s="22" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="R178" s="22" t="n">
+        <v>4.017</v>
+      </c>
+      <c r="S178" s="22" t="n">
+        <v>3.163</v>
+      </c>
+      <c r="T178" s="22" t="n">
+        <v>3.872</v>
+      </c>
+      <c r="U178" s="22" t="n">
+        <v>3.639</v>
+      </c>
+      <c r="V178" s="22" t="n">
+        <v>5.084</v>
+      </c>
+      <c r="W178" s="22" t="n">
+        <v>21.078</v>
+      </c>
+      <c r="X178" s="22" t="n">
+        <v>39.093</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="E179" s="22" t="n">
-        <v>-3481.799</v>
+        <v>-173.507</v>
       </c>
       <c r="I179" s="22" t="n">
-        <v>-17657.769</v>
+        <v>-259.091</v>
       </c>
       <c r="M179" s="22" t="n">
-        <v>-36336.695</v>
+        <v>-548.114</v>
       </c>
       <c r="O179" s="22" t="n">
-        <v>-4754.476</v>
+        <v>-169.374</v>
       </c>
       <c r="P179" s="22" t="n">
-        <v>-1121.804</v>
+        <v>-189.022</v>
       </c>
       <c r="Q179" s="22" t="n">
-        <v>-2381.784</v>
+        <v>-192.286</v>
       </c>
       <c r="R179" s="22" t="n">
-        <v>-2754.54</v>
+        <v>-197.362</v>
       </c>
       <c r="S179" s="22" t="n">
-        <v>-1350.518</v>
+        <v>-199.303</v>
       </c>
       <c r="T179" s="22" t="n">
-        <v>-1293.13</v>
+        <v>-170.445</v>
       </c>
       <c r="U179" s="22" t="n">
-        <v>-498.24</v>
+        <v>-154.745</v>
       </c>
       <c r="V179" s="22" t="n">
-        <v>-3481.799</v>
+        <v>-173.507</v>
       </c>
       <c r="W179" s="22" t="n">
-        <v>-17657.769</v>
+        <v>-259.091</v>
       </c>
       <c r="X179" s="22" t="n">
-        <v>-36336.695</v>
+        <v>-548.114</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
+          <t>법인세 납부·환급</t>
+        </is>
+      </c>
+      <c r="E180" s="22" t="n">
+        <v>-305.342</v>
       </c>
       <c r="I180" s="22" t="n">
-        <v>0.806</v>
+        <v>-304.663</v>
       </c>
       <c r="M180" s="22" t="n">
-        <v>470.776</v>
+        <v>-1327.646</v>
       </c>
       <c r="O180" s="22" t="n">
-        <v>1.871</v>
+        <v>-230.676</v>
       </c>
       <c r="P180" s="22" t="n">
-        <v>0</v>
+        <v>-292.8</v>
+      </c>
+      <c r="Q180" s="22" t="n">
+        <v>-221.753</v>
+      </c>
+      <c r="R180" s="22" t="n">
+        <v>-297.139</v>
+      </c>
+      <c r="S180" s="22" t="n">
+        <v>-304.808</v>
+      </c>
+      <c r="T180" s="22" t="n">
+        <v>-151.215</v>
+      </c>
+      <c r="U180" s="22" t="n">
+        <v>-57.599</v>
+      </c>
+      <c r="V180" s="22" t="n">
+        <v>-305.342</v>
       </c>
       <c r="W180" s="22" t="n">
-        <v>0.806</v>
+        <v>-304.663</v>
       </c>
       <c r="X180" s="22" t="n">
-        <v>470.776</v>
+        <v>-1327.646</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
-        </is>
-      </c>
-      <c r="E181" s="22" t="n">
-        <v>-136.977</v>
-      </c>
-      <c r="I181" s="22" t="n">
-        <v>-895.994</v>
-      </c>
-      <c r="M181" s="22" t="n">
-        <v>-1106.251</v>
-      </c>
-      <c r="O181" s="22" t="n">
-        <v>-214.38</v>
-      </c>
-      <c r="P181" s="22" t="n">
-        <v>-197.418</v>
+          <t>보상금 수취</t>
+        </is>
       </c>
       <c r="Q181" s="22" t="n">
-        <v>-173.406</v>
+        <v>0</v>
       </c>
       <c r="R181" s="22" t="n">
-        <v>-133.741</v>
+        <v>10</v>
       </c>
       <c r="S181" s="22" t="n">
-        <v>-141.78</v>
-      </c>
-      <c r="T181" s="22" t="n">
-        <v>-132.947</v>
-      </c>
-      <c r="U181" s="22" t="n">
-        <v>-272.099</v>
-      </c>
-      <c r="V181" s="22" t="n">
-        <v>-136.977</v>
-      </c>
-      <c r="W181" s="22" t="n">
-        <v>-895.994</v>
-      </c>
-      <c r="X181" s="22" t="n">
-        <v>-1106.251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>Income By Government Subsidies Inv CF</t>
-        </is>
-      </c>
-      <c r="E182" s="22" t="n">
-        <v>1634.371</v>
-      </c>
-      <c r="I182" s="22" t="n">
-        <v>10299.156</v>
-      </c>
-      <c r="M182" s="22" t="n">
-        <v>12346.456</v>
-      </c>
-      <c r="P182" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" s="22" t="n">
-        <v>153.629</v>
+          <t>Penalty Income Received Ope CF</t>
+        </is>
       </c>
       <c r="R182" s="22" t="n">
-        <v>155.995</v>
+        <v>0</v>
       </c>
       <c r="S182" s="22" t="n">
-        <v>78.79300000000001</v>
+        <v>72.67</v>
       </c>
       <c r="T182" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="U182" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" s="22" t="n">
-        <v>1634.371</v>
-      </c>
-      <c r="W182" s="22" t="n">
-        <v>10299.156</v>
-      </c>
-      <c r="X182" s="22" t="n">
-        <v>12346.456</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채 이행 지출</t>
-        </is>
-      </c>
-      <c r="O183" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" s="22" t="n">
-        <v>-20.901</v>
-      </c>
-      <c r="Q183" s="22" t="n">
+          <t>화해금 수취액</t>
+        </is>
+      </c>
+      <c r="R183" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" s="22" t="n">
+        <v>54.513</v>
+      </c>
+      <c r="T183" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
-        </is>
-      </c>
-      <c r="E184" s="22" t="n">
-        <v>-21</v>
-      </c>
-      <c r="I184" s="22" t="n">
-        <v>-11</v>
-      </c>
-      <c r="M184" s="22" t="n">
-        <v>-217.931</v>
-      </c>
-      <c r="O184" s="22" t="n">
-        <v>-34.5</v>
-      </c>
-      <c r="P184" s="22" t="n">
-        <v>-66.932</v>
-      </c>
-      <c r="Q184" s="22" t="n">
-        <v>-105.615</v>
+          <t>Settlement Package Paid Ope CF</t>
+        </is>
       </c>
       <c r="R184" s="22" t="n">
-        <v>-148</v>
+        <v>0</v>
       </c>
       <c r="S184" s="22" t="n">
-        <v>-80</v>
+        <v>-10</v>
       </c>
       <c r="T184" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="U184" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="V184" s="22" t="n">
-        <v>-21</v>
-      </c>
-      <c r="W184" s="22" t="n">
-        <v>-11</v>
-      </c>
-      <c r="X184" s="22" t="n">
-        <v>-217.931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="20" t="inlineStr">
-        <is>
-          <t>투자조합 분배 수입</t>
-        </is>
-      </c>
-      <c r="O185" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P185" s="22" t="n">
-        <v>14.967</v>
-      </c>
-      <c r="Q185" s="22" t="n">
-        <v>0</v>
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E185" s="12" t="n">
+        <v>2884.133</v>
+      </c>
+      <c r="I185" s="12" t="n">
+        <v>5787.563</v>
+      </c>
+      <c r="M185" s="12" t="n">
+        <v>6223.575</v>
+      </c>
+      <c r="O185" s="12" t="n">
+        <v>1852.721</v>
+      </c>
+      <c r="P185" s="12" t="n">
+        <v>3067.888</v>
+      </c>
+      <c r="Q185" s="12" t="n">
+        <v>2231.274</v>
+      </c>
+      <c r="R185" s="12" t="n">
+        <v>4582.193</v>
+      </c>
+      <c r="S185" s="12" t="n">
+        <v>4110.636</v>
+      </c>
+      <c r="T185" s="12" t="n">
+        <v>3957.746</v>
+      </c>
+      <c r="U185" s="12" t="n">
+        <v>3963.42</v>
+      </c>
+      <c r="V185" s="12" t="n">
+        <v>2884.133</v>
+      </c>
+      <c r="W185" s="12" t="n">
+        <v>5787.563</v>
+      </c>
+      <c r="X185" s="12" t="n">
+        <v>6223.575</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>관계회사 주식 취득</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="E186" s="22" t="n">
+        <v>-3481.799</v>
+      </c>
+      <c r="I186" s="22" t="n">
+        <v>-17657.769</v>
+      </c>
+      <c r="M186" s="22" t="n">
+        <v>-36336.695</v>
+      </c>
+      <c r="O186" s="22" t="n">
+        <v>-4754.476</v>
+      </c>
+      <c r="P186" s="22" t="n">
+        <v>-1121.804</v>
+      </c>
+      <c r="Q186" s="22" t="n">
+        <v>-2381.784</v>
+      </c>
+      <c r="R186" s="22" t="n">
+        <v>-2754.54</v>
       </c>
       <c r="S186" s="22" t="n">
-        <v>0</v>
+        <v>-1350.518</v>
       </c>
       <c r="T186" s="22" t="n">
-        <v>-108</v>
+        <v>-1293.13</v>
       </c>
       <c r="U186" s="22" t="n">
-        <v>0</v>
+        <v>-498.24</v>
+      </c>
+      <c r="V186" s="22" t="n">
+        <v>-3481.799</v>
+      </c>
+      <c r="W186" s="22" t="n">
+        <v>-17657.769</v>
+      </c>
+      <c r="X186" s="22" t="n">
+        <v>-36336.695</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
+          <t>유형자산 매각</t>
         </is>
       </c>
       <c r="I187" s="22" t="n">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="M187" s="22" t="n">
-        <v>187.185</v>
+        <v>470.776</v>
       </c>
       <c r="O187" s="22" t="n">
-        <v>17.071</v>
+        <v>1.871</v>
       </c>
       <c r="P187" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W187" s="22" t="n">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="X187" s="22" t="n">
-        <v>187.185</v>
+        <v>470.776</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 납입</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="E188" s="22" t="n">
-        <v>-94.59699999999999</v>
+        <v>-136.977</v>
       </c>
       <c r="I188" s="22" t="n">
-        <v>-64.92100000000001</v>
+        <v>-895.994</v>
       </c>
       <c r="M188" s="22" t="n">
-        <v>-0.732</v>
+        <v>-1106.251</v>
       </c>
       <c r="O188" s="22" t="n">
-        <v>-343.935</v>
+        <v>-214.38</v>
       </c>
       <c r="P188" s="22" t="n">
-        <v>-4.1</v>
+        <v>-197.418</v>
       </c>
       <c r="Q188" s="22" t="n">
-        <v>-75.621</v>
+        <v>-173.406</v>
       </c>
       <c r="R188" s="22" t="n">
-        <v>-93.71899999999999</v>
+        <v>-133.741</v>
       </c>
       <c r="S188" s="22" t="n">
-        <v>0</v>
+        <v>-141.78</v>
       </c>
       <c r="T188" s="22" t="n">
-        <v>-27.009</v>
+        <v>-132.947</v>
       </c>
       <c r="U188" s="22" t="n">
-        <v>-20.555</v>
+        <v>-272.099</v>
       </c>
       <c r="V188" s="22" t="n">
-        <v>-94.59699999999999</v>
+        <v>-136.977</v>
       </c>
       <c r="W188" s="22" t="n">
-        <v>-64.92100000000001</v>
+        <v>-895.994</v>
       </c>
       <c r="X188" s="22" t="n">
-        <v>-0.732</v>
+        <v>-1106.251</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 회수</t>
+          <t>Income By Government Subsidies Inv CF</t>
         </is>
       </c>
       <c r="E189" s="22" t="n">
-        <v>0</v>
+        <v>1634.371</v>
       </c>
       <c r="I189" s="22" t="n">
-        <v>0.201</v>
+        <v>10299.156</v>
       </c>
       <c r="M189" s="22" t="n">
-        <v>6.374</v>
-      </c>
-      <c r="O189" s="22" t="n">
-        <v>0.7</v>
+        <v>12346.456</v>
       </c>
       <c r="P189" s="22" t="n">
-        <v>22.021</v>
+        <v>0</v>
       </c>
       <c r="Q189" s="22" t="n">
-        <v>1.094</v>
+        <v>153.629</v>
       </c>
       <c r="R189" s="22" t="n">
-        <v>0</v>
+        <v>155.995</v>
       </c>
       <c r="S189" s="22" t="n">
-        <v>151.35</v>
+        <v>78.79300000000001</v>
       </c>
       <c r="T189" s="22" t="n">
-        <v>63.289</v>
+        <v>0</v>
       </c>
       <c r="U189" s="22" t="n">
-        <v>356.746</v>
+        <v>0</v>
       </c>
       <c r="V189" s="22" t="n">
-        <v>0</v>
+        <v>1634.371</v>
       </c>
       <c r="W189" s="22" t="n">
-        <v>0.201</v>
+        <v>10299.156</v>
       </c>
       <c r="X189" s="22" t="n">
-        <v>6.374</v>
+        <v>12346.456</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
+          <t>자산복구부채 이행 지출</t>
         </is>
       </c>
       <c r="O190" s="22" t="n">
-        <v>-83.26600000000001</v>
+        <v>0</v>
       </c>
       <c r="P190" s="22" t="n">
-        <v>-8.58</v>
+        <v>-20.901</v>
       </c>
       <c r="Q190" s="22" t="n">
         <v>0</v>
@@ -10795,789 +11055,1000 @@
     <row r="191">
       <c r="A191" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득(수입)</t>
-        </is>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="E191" s="22" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I191" s="22" t="n">
+        <v>-11</v>
+      </c>
+      <c r="M191" s="22" t="n">
+        <v>-217.931</v>
+      </c>
+      <c r="O191" s="22" t="n">
+        <v>-34.5</v>
       </c>
       <c r="P191" s="22" t="n">
-        <v>0</v>
+        <v>-66.932</v>
       </c>
       <c r="Q191" s="22" t="n">
-        <v>5.421</v>
+        <v>-105.615</v>
       </c>
       <c r="R191" s="22" t="n">
-        <v>0</v>
+        <v>-148</v>
+      </c>
+      <c r="S191" s="22" t="n">
+        <v>-80</v>
+      </c>
+      <c r="T191" s="22" t="n">
+        <v>-30</v>
+      </c>
+      <c r="U191" s="22" t="n">
+        <v>-20</v>
+      </c>
+      <c r="V191" s="22" t="n">
+        <v>-21</v>
+      </c>
+      <c r="W191" s="22" t="n">
+        <v>-11</v>
+      </c>
+      <c r="X191" s="22" t="n">
+        <v>-217.931</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="E192" s="22" t="n">
-        <v>74.364</v>
-      </c>
-      <c r="I192" s="22" t="n">
-        <v>6.408</v>
-      </c>
-      <c r="M192" s="22" t="n">
-        <v>7.716</v>
+          <t>투자조합 분배 수입</t>
+        </is>
       </c>
       <c r="O192" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P192" s="22" t="n">
-        <v>-0.078</v>
+        <v>14.967</v>
       </c>
       <c r="Q192" s="22" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="R192" s="22" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="S192" s="22" t="n">
-        <v>-17.35</v>
-      </c>
-      <c r="T192" s="22" t="n">
-        <v>-146.968</v>
-      </c>
-      <c r="U192" s="22" t="n">
-        <v>-151.979</v>
-      </c>
-      <c r="V192" s="22" t="n">
-        <v>74.364</v>
-      </c>
-      <c r="W192" s="22" t="n">
-        <v>6.408</v>
-      </c>
-      <c r="X192" s="22" t="n">
-        <v>7.716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E193" s="12" t="n">
-        <v>-2025.638</v>
-      </c>
-      <c r="I193" s="12" t="n">
-        <v>-8323.112999999999</v>
-      </c>
-      <c r="M193" s="12" t="n">
-        <v>-24643.1</v>
-      </c>
-      <c r="O193" s="12" t="n">
-        <v>-5410.917</v>
-      </c>
-      <c r="P193" s="12" t="n">
-        <v>-1382.827</v>
-      </c>
-      <c r="Q193" s="12" t="n">
-        <v>-2576.277</v>
-      </c>
-      <c r="R193" s="12" t="n">
-        <v>-2973.593</v>
-      </c>
-      <c r="S193" s="12" t="n">
-        <v>-1359.506</v>
-      </c>
-      <c r="T193" s="12" t="n">
-        <v>-1674.766</v>
-      </c>
-      <c r="U193" s="12" t="n">
-        <v>-606.129</v>
-      </c>
-      <c r="V193" s="12" t="n">
-        <v>-2025.638</v>
-      </c>
-      <c r="W193" s="12" t="n">
-        <v>-8323.112999999999</v>
-      </c>
-      <c r="X193" s="12" t="n">
-        <v>-24643.1</v>
+      <c r="A193" s="20" t="inlineStr">
+        <is>
+          <t>관계회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="S193" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="22" t="n">
+        <v>-108</v>
+      </c>
+      <c r="U193" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="20" t="inlineStr">
         <is>
-          <t>단기차입</t>
-        </is>
-      </c>
-      <c r="E194" s="22" t="n">
-        <v>1053</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="I194" s="22" t="n">
-        <v>20067</v>
+        <v>0</v>
       </c>
       <c r="M194" s="22" t="n">
-        <v>17087</v>
+        <v>187.185</v>
       </c>
       <c r="O194" s="22" t="n">
-        <v>655</v>
+        <v>17.071</v>
       </c>
       <c r="P194" s="22" t="n">
-        <v>787</v>
-      </c>
-      <c r="Q194" s="22" t="n">
-        <v>1300</v>
-      </c>
-      <c r="R194" s="22" t="n">
-        <v>2114.288</v>
-      </c>
-      <c r="S194" s="22" t="n">
-        <v>2976</v>
-      </c>
-      <c r="T194" s="22" t="n">
-        <v>2766</v>
-      </c>
-      <c r="U194" s="22" t="n">
-        <v>1396</v>
-      </c>
-      <c r="V194" s="22" t="n">
-        <v>1053</v>
+        <v>0</v>
       </c>
       <c r="W194" s="22" t="n">
-        <v>20067</v>
+        <v>0</v>
       </c>
       <c r="X194" s="22" t="n">
-        <v>17087</v>
+        <v>187.185</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 상환</t>
+          <t>임차보증금·보증금 납입</t>
         </is>
       </c>
       <c r="E195" s="22" t="n">
-        <v>-955.332</v>
+        <v>-94.59699999999999</v>
       </c>
       <c r="I195" s="22" t="n">
-        <v>-11223</v>
+        <v>-64.92100000000001</v>
       </c>
       <c r="M195" s="22" t="n">
-        <v>-15661.668</v>
+        <v>-0.732</v>
       </c>
       <c r="O195" s="22" t="n">
-        <v>-643</v>
+        <v>-343.935</v>
       </c>
       <c r="P195" s="22" t="n">
-        <v>-752</v>
+        <v>-4.1</v>
       </c>
       <c r="Q195" s="22" t="n">
-        <v>-730</v>
+        <v>-75.621</v>
       </c>
       <c r="R195" s="22" t="n">
-        <v>-1679.288</v>
+        <v>-93.71899999999999</v>
       </c>
       <c r="S195" s="22" t="n">
-        <v>-3209</v>
+        <v>0</v>
       </c>
       <c r="T195" s="22" t="n">
-        <v>-2350</v>
+        <v>-27.009</v>
       </c>
       <c r="U195" s="22" t="n">
-        <v>-2527</v>
+        <v>-20.555</v>
       </c>
       <c r="V195" s="22" t="n">
-        <v>-955.332</v>
+        <v>-94.59699999999999</v>
       </c>
       <c r="W195" s="22" t="n">
-        <v>-11223</v>
+        <v>-64.92100000000001</v>
       </c>
       <c r="X195" s="22" t="n">
-        <v>-15661.668</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>임차보증금·보증금 회수</t>
         </is>
       </c>
       <c r="E196" s="22" t="n">
-        <v>1664</v>
+        <v>0</v>
       </c>
       <c r="I196" s="22" t="n">
-        <v>5725</v>
+        <v>0.201</v>
       </c>
       <c r="M196" s="22" t="n">
-        <v>8110</v>
+        <v>6.374</v>
       </c>
       <c r="O196" s="22" t="n">
-        <v>2774</v>
+        <v>0.7</v>
       </c>
       <c r="P196" s="22" t="n">
-        <v>186</v>
+        <v>22.021</v>
       </c>
       <c r="Q196" s="22" t="n">
-        <v>3329.5</v>
+        <v>1.094</v>
       </c>
       <c r="R196" s="22" t="n">
-        <v>409.288</v>
+        <v>0</v>
       </c>
       <c r="S196" s="22" t="n">
-        <v>0</v>
+        <v>151.35</v>
       </c>
       <c r="T196" s="22" t="n">
-        <v>1010</v>
+        <v>63.289</v>
       </c>
       <c r="U196" s="22" t="n">
-        <v>0</v>
+        <v>356.746</v>
       </c>
       <c r="V196" s="22" t="n">
-        <v>1664</v>
+        <v>0</v>
       </c>
       <c r="W196" s="22" t="n">
-        <v>5725</v>
+        <v>0.201</v>
       </c>
       <c r="X196" s="22" t="n">
-        <v>8110</v>
+        <v>6.374</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="E197" s="22" t="n">
-        <v>-817.818</v>
-      </c>
-      <c r="I197" s="22" t="n">
-        <v>-4278.739</v>
-      </c>
-      <c r="M197" s="22" t="n">
-        <v>-3339.651</v>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
       </c>
       <c r="O197" s="22" t="n">
-        <v>-809.525</v>
+        <v>-83.26600000000001</v>
       </c>
       <c r="P197" s="22" t="n">
-        <v>-1256.83</v>
+        <v>-8.58</v>
       </c>
       <c r="Q197" s="22" t="n">
-        <v>-885.444</v>
-      </c>
-      <c r="R197" s="22" t="n">
-        <v>-2162.076</v>
-      </c>
-      <c r="S197" s="22" t="n">
-        <v>-1902.99</v>
-      </c>
-      <c r="T197" s="22" t="n">
-        <v>-933.568</v>
-      </c>
-      <c r="U197" s="22" t="n">
-        <v>-918.082</v>
-      </c>
-      <c r="V197" s="22" t="n">
-        <v>-817.818</v>
-      </c>
-      <c r="W197" s="22" t="n">
-        <v>-4278.739</v>
-      </c>
-      <c r="X197" s="22" t="n">
-        <v>-3339.651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="E198" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I198" s="22" t="n">
-        <v>17942.964</v>
-      </c>
-      <c r="M198" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O198" s="22" t="n">
-        <v>2702.395</v>
+          <t>연결범위 변경 자회사 주식 취득(수입)</t>
+        </is>
       </c>
       <c r="P198" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V198" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W198" s="22" t="n">
-        <v>17942.964</v>
-      </c>
-      <c r="X198" s="22" t="n">
+      <c r="Q198" s="22" t="n">
+        <v>5.421</v>
+      </c>
+      <c r="R198" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="20" t="inlineStr">
         <is>
-          <t>비지배주주 납입</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E199" s="22" t="n">
-        <v>129.041</v>
+        <v>74.364</v>
       </c>
       <c r="I199" s="22" t="n">
-        <v>0</v>
+        <v>6.408</v>
+      </c>
+      <c r="M199" s="22" t="n">
+        <v>7.716</v>
+      </c>
+      <c r="O199" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" s="22" t="n">
+        <v>-0.078</v>
+      </c>
+      <c r="Q199" s="22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="R199" s="22" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="S199" s="22" t="n">
+        <v>-17.35</v>
+      </c>
+      <c r="T199" s="22" t="n">
+        <v>-146.968</v>
       </c>
       <c r="U199" s="22" t="n">
-        <v>0</v>
+        <v>-151.979</v>
       </c>
       <c r="V199" s="22" t="n">
-        <v>129.041</v>
+        <v>74.364</v>
       </c>
       <c r="W199" s="22" t="n">
-        <v>0</v>
+        <v>6.408</v>
+      </c>
+      <c r="X199" s="22" t="n">
+        <v>7.716</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="20" t="inlineStr">
-        <is>
-          <t>리스부채 상환</t>
-        </is>
-      </c>
-      <c r="E200" s="22" t="n">
-        <v>-1566.762</v>
-      </c>
-      <c r="I200" s="22" t="n">
-        <v>-1836.513</v>
-      </c>
-      <c r="M200" s="22" t="n">
-        <v>-2649.97</v>
-      </c>
-      <c r="O200" s="22" t="n">
-        <v>-944.025</v>
-      </c>
-      <c r="P200" s="22" t="n">
-        <v>-1239.156</v>
-      </c>
-      <c r="Q200" s="22" t="n">
-        <v>-1328.085</v>
-      </c>
-      <c r="R200" s="22" t="n">
-        <v>-1366.964</v>
-      </c>
-      <c r="S200" s="22" t="n">
-        <v>-1482.328</v>
-      </c>
-      <c r="T200" s="22" t="n">
-        <v>-1358.908</v>
-      </c>
-      <c r="U200" s="22" t="n">
-        <v>-1302.251</v>
-      </c>
-      <c r="V200" s="22" t="n">
-        <v>-1566.762</v>
-      </c>
-      <c r="W200" s="22" t="n">
-        <v>-1836.513</v>
-      </c>
-      <c r="X200" s="22" t="n">
-        <v>-2649.97</v>
+      <c r="A200" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E200" s="12" t="n">
+        <v>-2025.638</v>
+      </c>
+      <c r="I200" s="12" t="n">
+        <v>-8323.112999999999</v>
+      </c>
+      <c r="M200" s="12" t="n">
+        <v>-24643.1</v>
+      </c>
+      <c r="O200" s="12" t="n">
+        <v>-5410.917</v>
+      </c>
+      <c r="P200" s="12" t="n">
+        <v>-1382.827</v>
+      </c>
+      <c r="Q200" s="12" t="n">
+        <v>-2576.277</v>
+      </c>
+      <c r="R200" s="12" t="n">
+        <v>-2973.593</v>
+      </c>
+      <c r="S200" s="12" t="n">
+        <v>-1359.506</v>
+      </c>
+      <c r="T200" s="12" t="n">
+        <v>-1674.766</v>
+      </c>
+      <c r="U200" s="12" t="n">
+        <v>-606.129</v>
+      </c>
+      <c r="V200" s="12" t="n">
+        <v>-2025.638</v>
+      </c>
+      <c r="W200" s="12" t="n">
+        <v>-8323.112999999999</v>
+      </c>
+      <c r="X200" s="12" t="n">
+        <v>-24643.1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="20" t="inlineStr">
         <is>
-          <t>세일앤리스백 수입</t>
+          <t>단기차입</t>
         </is>
       </c>
       <c r="E201" s="22" t="n">
-        <v>217.272</v>
+        <v>1053</v>
       </c>
       <c r="I201" s="22" t="n">
-        <v>512.228</v>
+        <v>20067</v>
       </c>
       <c r="M201" s="22" t="n">
-        <v>1242.652</v>
+        <v>17087</v>
       </c>
       <c r="O201" s="22" t="n">
-        <v>818.274</v>
+        <v>655</v>
       </c>
       <c r="P201" s="22" t="n">
-        <v>528.948</v>
+        <v>787</v>
       </c>
       <c r="Q201" s="22" t="n">
-        <v>351.111</v>
+        <v>1300</v>
       </c>
       <c r="R201" s="22" t="n">
-        <v>371.306</v>
+        <v>2114.288</v>
       </c>
       <c r="S201" s="22" t="n">
-        <v>632.232</v>
+        <v>2976</v>
       </c>
       <c r="T201" s="22" t="n">
-        <v>9.039</v>
+        <v>2766</v>
       </c>
       <c r="U201" s="22" t="n">
-        <v>80.358</v>
+        <v>1396</v>
       </c>
       <c r="V201" s="22" t="n">
-        <v>217.272</v>
+        <v>1053</v>
       </c>
       <c r="W201" s="22" t="n">
-        <v>512.228</v>
+        <v>20067</v>
       </c>
       <c r="X201" s="22" t="n">
-        <v>1242.652</v>
+        <v>17087</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="20" t="inlineStr">
         <is>
-          <t>Repayments Of Installment Payables Fin CF</t>
+          <t>단기차입금 상환</t>
         </is>
       </c>
       <c r="E202" s="22" t="n">
-        <v>-7.75</v>
+        <v>-955.332</v>
       </c>
       <c r="I202" s="22" t="n">
-        <v>-21.232</v>
+        <v>-11223</v>
       </c>
       <c r="M202" s="22" t="n">
-        <v>-393.305</v>
+        <v>-15661.668</v>
       </c>
       <c r="O202" s="22" t="n">
-        <v>-117.405</v>
+        <v>-643</v>
       </c>
       <c r="P202" s="22" t="n">
-        <v>-101.615</v>
+        <v>-752</v>
       </c>
       <c r="Q202" s="22" t="n">
-        <v>-103.808</v>
+        <v>-730</v>
       </c>
       <c r="R202" s="22" t="n">
-        <v>-102.149</v>
+        <v>-1679.288</v>
       </c>
       <c r="S202" s="22" t="n">
-        <v>-71.84</v>
+        <v>-3209</v>
       </c>
       <c r="T202" s="22" t="n">
-        <v>-38.926</v>
+        <v>-2350</v>
       </c>
       <c r="U202" s="22" t="n">
-        <v>-17.605</v>
+        <v>-2527</v>
       </c>
       <c r="V202" s="22" t="n">
-        <v>-7.75</v>
+        <v>-955.332</v>
       </c>
       <c r="W202" s="22" t="n">
-        <v>-21.232</v>
+        <v>-11223</v>
       </c>
       <c r="X202" s="22" t="n">
-        <v>-393.305</v>
+        <v>-15661.668</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>장기차입</t>
         </is>
       </c>
       <c r="E203" s="22" t="n">
-        <v>-1.383</v>
+        <v>1664</v>
       </c>
       <c r="I203" s="22" t="n">
-        <v>-0.317</v>
+        <v>5725</v>
       </c>
       <c r="M203" s="22" t="n">
-        <v>-0.031</v>
+        <v>8110</v>
+      </c>
+      <c r="O203" s="22" t="n">
+        <v>2774</v>
       </c>
       <c r="P203" s="22" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="Q203" s="22" t="n">
-        <v>-602.1130000000001</v>
+        <v>3329.5</v>
       </c>
       <c r="R203" s="22" t="n">
+        <v>409.288</v>
+      </c>
+      <c r="S203" s="22" t="n">
         <v>0</v>
       </c>
       <c r="T203" s="22" t="n">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="U203" s="22" t="n">
-        <v>-601.282</v>
+        <v>0</v>
       </c>
       <c r="V203" s="22" t="n">
-        <v>-1.383</v>
+        <v>1664</v>
       </c>
       <c r="W203" s="22" t="n">
-        <v>-0.317</v>
+        <v>5725</v>
       </c>
       <c r="X203" s="22" t="n">
-        <v>-0.031</v>
+        <v>8110</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="20" t="inlineStr">
         <is>
-          <t>자기주식 매각</t>
-        </is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="E204" s="22" t="n">
+        <v>-817.818</v>
       </c>
       <c r="I204" s="22" t="n">
-        <v>0.963</v>
+        <v>-4278.739</v>
       </c>
       <c r="M204" s="22" t="n">
-        <v>85.861</v>
+        <v>-3339.651</v>
+      </c>
+      <c r="O204" s="22" t="n">
+        <v>-809.525</v>
+      </c>
+      <c r="P204" s="22" t="n">
+        <v>-1256.83</v>
+      </c>
+      <c r="Q204" s="22" t="n">
+        <v>-885.444</v>
+      </c>
+      <c r="R204" s="22" t="n">
+        <v>-2162.076</v>
+      </c>
+      <c r="S204" s="22" t="n">
+        <v>-1902.99</v>
+      </c>
+      <c r="T204" s="22" t="n">
+        <v>-933.568</v>
+      </c>
+      <c r="U204" s="22" t="n">
+        <v>-918.082</v>
+      </c>
+      <c r="V204" s="22" t="n">
+        <v>-817.818</v>
       </c>
       <c r="W204" s="22" t="n">
-        <v>0.963</v>
+        <v>-4278.739</v>
       </c>
       <c r="X204" s="22" t="n">
-        <v>85.861</v>
+        <v>-3339.651</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
+          <t>주식 발행</t>
         </is>
       </c>
       <c r="E205" s="22" t="n">
-        <v>-125.621</v>
+        <v>0</v>
       </c>
       <c r="I205" s="22" t="n">
-        <v>-124.699</v>
+        <v>17942.964</v>
       </c>
       <c r="M205" s="22" t="n">
-        <v>-161.619</v>
+        <v>0</v>
       </c>
       <c r="O205" s="22" t="n">
-        <v>-86.23</v>
+        <v>2702.395</v>
       </c>
       <c r="P205" s="22" t="n">
-        <v>-93.366</v>
-      </c>
-      <c r="Q205" s="22" t="n">
-        <v>-93.57899999999999</v>
-      </c>
-      <c r="R205" s="22" t="n">
-        <v>-90.79600000000001</v>
-      </c>
-      <c r="S205" s="22" t="n">
-        <v>-90.779</v>
-      </c>
-      <c r="T205" s="22" t="n">
-        <v>-108.912</v>
-      </c>
-      <c r="U205" s="22" t="n">
-        <v>-109.509</v>
+        <v>0</v>
       </c>
       <c r="V205" s="22" t="n">
-        <v>-125.621</v>
+        <v>0</v>
       </c>
       <c r="W205" s="22" t="n">
-        <v>-124.699</v>
+        <v>17942.964</v>
       </c>
       <c r="X205" s="22" t="n">
-        <v>-161.619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 없는 자회사 주식 취득</t>
-        </is>
-      </c>
-      <c r="Q206" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R206" s="22" t="n">
-        <v>-35.1</v>
-      </c>
-      <c r="S206" s="22" t="n">
+          <t>비지배주주 납입</t>
+        </is>
+      </c>
+      <c r="E206" s="22" t="n">
+        <v>129.041</v>
+      </c>
+      <c r="I206" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V206" s="22" t="n">
+        <v>129.041</v>
+      </c>
+      <c r="W206" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>리스부채 상환</t>
         </is>
       </c>
       <c r="E207" s="22" t="n">
-        <v>0.763</v>
+        <v>-1566.762</v>
       </c>
       <c r="I207" s="22" t="n">
-        <v>0.963</v>
+        <v>-1836.513</v>
+      </c>
+      <c r="M207" s="22" t="n">
+        <v>-2649.97</v>
+      </c>
+      <c r="O207" s="22" t="n">
+        <v>-944.025</v>
+      </c>
+      <c r="P207" s="22" t="n">
+        <v>-1239.156</v>
+      </c>
+      <c r="Q207" s="22" t="n">
+        <v>-1328.085</v>
+      </c>
+      <c r="R207" s="22" t="n">
+        <v>-1366.964</v>
+      </c>
+      <c r="S207" s="22" t="n">
+        <v>-1482.328</v>
+      </c>
+      <c r="T207" s="22" t="n">
+        <v>-1358.908</v>
       </c>
       <c r="U207" s="22" t="n">
-        <v>0</v>
+        <v>-1302.251</v>
       </c>
       <c r="V207" s="22" t="n">
-        <v>0.763</v>
+        <v>-1566.762</v>
       </c>
       <c r="W207" s="22" t="n">
-        <v>0.963</v>
+        <v>-1836.513</v>
+      </c>
+      <c r="X207" s="22" t="n">
+        <v>-2649.97</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E208" s="12" t="n">
-        <v>-410.59</v>
-      </c>
-      <c r="I208" s="12" t="n">
-        <v>26763.654</v>
-      </c>
-      <c r="M208" s="12" t="n">
-        <v>4319.267</v>
-      </c>
-      <c r="O208" s="12" t="n">
-        <v>4349.483</v>
-      </c>
-      <c r="P208" s="12" t="n">
-        <v>-1941.02</v>
-      </c>
-      <c r="Q208" s="12" t="n">
-        <v>1237.58</v>
-      </c>
-      <c r="R208" s="12" t="n">
-        <v>-2541.492</v>
-      </c>
-      <c r="S208" s="12" t="n">
-        <v>-3148.706</v>
-      </c>
-      <c r="T208" s="12" t="n">
-        <v>-1005.276</v>
-      </c>
-      <c r="U208" s="12" t="n">
-        <v>-3999.374</v>
-      </c>
-      <c r="V208" s="12" t="n">
-        <v>-410.59</v>
-      </c>
-      <c r="W208" s="12" t="n">
-        <v>26763.654</v>
-      </c>
-      <c r="X208" s="12" t="n">
-        <v>4319.267</v>
+      <c r="A208" s="20" t="inlineStr">
+        <is>
+          <t>세일앤리스백 수입</t>
+        </is>
+      </c>
+      <c r="E208" s="22" t="n">
+        <v>217.272</v>
+      </c>
+      <c r="I208" s="22" t="n">
+        <v>512.228</v>
+      </c>
+      <c r="M208" s="22" t="n">
+        <v>1242.652</v>
+      </c>
+      <c r="O208" s="22" t="n">
+        <v>818.274</v>
+      </c>
+      <c r="P208" s="22" t="n">
+        <v>528.948</v>
+      </c>
+      <c r="Q208" s="22" t="n">
+        <v>351.111</v>
+      </c>
+      <c r="R208" s="22" t="n">
+        <v>371.306</v>
+      </c>
+      <c r="S208" s="22" t="n">
+        <v>632.232</v>
+      </c>
+      <c r="T208" s="22" t="n">
+        <v>9.039</v>
+      </c>
+      <c r="U208" s="22" t="n">
+        <v>80.358</v>
+      </c>
+      <c r="V208" s="22" t="n">
+        <v>217.272</v>
+      </c>
+      <c r="W208" s="22" t="n">
+        <v>512.228</v>
+      </c>
+      <c r="X208" s="22" t="n">
+        <v>1242.652</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>Repayments Of Installment Payables Fin CF</t>
         </is>
       </c>
       <c r="E209" s="22" t="n">
-        <v>-0.726</v>
+        <v>-7.75</v>
       </c>
       <c r="I209" s="22" t="n">
-        <v>-2.017</v>
+        <v>-21.232</v>
       </c>
       <c r="M209" s="22" t="n">
-        <v>5.791</v>
+        <v>-393.305</v>
       </c>
       <c r="O209" s="22" t="n">
-        <v>-0.186</v>
+        <v>-117.405</v>
       </c>
       <c r="P209" s="22" t="n">
-        <v>-0.066</v>
+        <v>-101.615</v>
       </c>
       <c r="Q209" s="22" t="n">
-        <v>0.048</v>
+        <v>-103.808</v>
       </c>
       <c r="R209" s="22" t="n">
-        <v>-0.159</v>
+        <v>-102.149</v>
       </c>
       <c r="S209" s="22" t="n">
-        <v>0.019</v>
+        <v>-71.84</v>
       </c>
       <c r="T209" s="22" t="n">
-        <v>0.123</v>
+        <v>-38.926</v>
       </c>
       <c r="U209" s="22" t="n">
-        <v>0.117</v>
+        <v>-17.605</v>
       </c>
       <c r="V209" s="22" t="n">
-        <v>-0.726</v>
+        <v>-7.75</v>
       </c>
       <c r="W209" s="22" t="n">
-        <v>-2.017</v>
+        <v>-21.232</v>
       </c>
       <c r="X209" s="22" t="n">
-        <v>5.791</v>
+        <v>-393.305</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 증감</t>
+          <t>자기주식 취득</t>
         </is>
       </c>
       <c r="E210" s="22" t="n">
-        <v>447.177</v>
+        <v>-1.383</v>
       </c>
       <c r="I210" s="22" t="n">
-        <v>24226.087</v>
+        <v>-0.317</v>
       </c>
       <c r="M210" s="22" t="n">
-        <v>-14094.466</v>
-      </c>
-      <c r="O210" s="22" t="n">
-        <v>791.101</v>
+        <v>-0.031</v>
       </c>
       <c r="P210" s="22" t="n">
-        <v>-256.025</v>
+        <v>0</v>
       </c>
       <c r="Q210" s="22" t="n">
-        <v>892.626</v>
+        <v>-602.1130000000001</v>
       </c>
       <c r="R210" s="22" t="n">
-        <v>-933.052</v>
-      </c>
-      <c r="S210" s="22" t="n">
-        <v>-397.555</v>
+        <v>0</v>
       </c>
       <c r="T210" s="22" t="n">
-        <v>1277.827</v>
+        <v>0</v>
       </c>
       <c r="U210" s="22" t="n">
-        <v>-641.9640000000001</v>
+        <v>-601.282</v>
       </c>
       <c r="V210" s="22" t="n">
-        <v>447.177</v>
+        <v>-1.383</v>
       </c>
       <c r="W210" s="22" t="n">
-        <v>24226.087</v>
+        <v>-0.317</v>
       </c>
       <c r="X210" s="22" t="n">
-        <v>-14094.466</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="20" t="inlineStr">
         <is>
+          <t>자기주식 매각</t>
+        </is>
+      </c>
+      <c r="I211" s="22" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="M211" s="22" t="n">
+        <v>85.861</v>
+      </c>
+      <c r="W211" s="22" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="X211" s="22" t="n">
+        <v>85.861</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E212" s="22" t="n">
+        <v>-125.621</v>
+      </c>
+      <c r="I212" s="22" t="n">
+        <v>-124.699</v>
+      </c>
+      <c r="M212" s="22" t="n">
+        <v>-161.619</v>
+      </c>
+      <c r="O212" s="22" t="n">
+        <v>-86.23</v>
+      </c>
+      <c r="P212" s="22" t="n">
+        <v>-93.366</v>
+      </c>
+      <c r="Q212" s="22" t="n">
+        <v>-93.57899999999999</v>
+      </c>
+      <c r="R212" s="22" t="n">
+        <v>-90.79600000000001</v>
+      </c>
+      <c r="S212" s="22" t="n">
+        <v>-90.779</v>
+      </c>
+      <c r="T212" s="22" t="n">
+        <v>-108.912</v>
+      </c>
+      <c r="U212" s="22" t="n">
+        <v>-109.509</v>
+      </c>
+      <c r="V212" s="22" t="n">
+        <v>-125.621</v>
+      </c>
+      <c r="W212" s="22" t="n">
+        <v>-124.699</v>
+      </c>
+      <c r="X212" s="22" t="n">
+        <v>-161.619</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="20" t="inlineStr">
+        <is>
+          <t>연결범위 변경 없는 자회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="Q213" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" s="22" t="n">
+        <v>-35.1</v>
+      </c>
+      <c r="S213" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E214" s="22" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="I214" s="22" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="U214" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V214" s="22" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="W214" s="22" t="n">
+        <v>0.963</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E215" s="12" t="n">
+        <v>-410.59</v>
+      </c>
+      <c r="I215" s="12" t="n">
+        <v>26763.654</v>
+      </c>
+      <c r="M215" s="12" t="n">
+        <v>4319.267</v>
+      </c>
+      <c r="O215" s="12" t="n">
+        <v>4349.483</v>
+      </c>
+      <c r="P215" s="12" t="n">
+        <v>-1941.02</v>
+      </c>
+      <c r="Q215" s="12" t="n">
+        <v>1237.58</v>
+      </c>
+      <c r="R215" s="12" t="n">
+        <v>-2541.492</v>
+      </c>
+      <c r="S215" s="12" t="n">
+        <v>-3148.706</v>
+      </c>
+      <c r="T215" s="12" t="n">
+        <v>-1005.276</v>
+      </c>
+      <c r="U215" s="12" t="n">
+        <v>-3999.374</v>
+      </c>
+      <c r="V215" s="12" t="n">
+        <v>-410.59</v>
+      </c>
+      <c r="W215" s="12" t="n">
+        <v>26763.654</v>
+      </c>
+      <c r="X215" s="12" t="n">
+        <v>4319.267</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="E216" s="22" t="n">
+        <v>-0.726</v>
+      </c>
+      <c r="I216" s="22" t="n">
+        <v>-2.017</v>
+      </c>
+      <c r="M216" s="22" t="n">
+        <v>5.791</v>
+      </c>
+      <c r="O216" s="22" t="n">
+        <v>-0.186</v>
+      </c>
+      <c r="P216" s="22" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="Q216" s="22" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="R216" s="22" t="n">
+        <v>-0.159</v>
+      </c>
+      <c r="S216" s="22" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="T216" s="22" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="U216" s="22" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="V216" s="22" t="n">
+        <v>-0.726</v>
+      </c>
+      <c r="W216" s="22" t="n">
+        <v>-2.017</v>
+      </c>
+      <c r="X216" s="22" t="n">
+        <v>5.791</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 증감</t>
+        </is>
+      </c>
+      <c r="E217" s="22" t="n">
+        <v>447.177</v>
+      </c>
+      <c r="I217" s="22" t="n">
+        <v>24226.087</v>
+      </c>
+      <c r="M217" s="22" t="n">
+        <v>-14094.466</v>
+      </c>
+      <c r="O217" s="22" t="n">
+        <v>791.101</v>
+      </c>
+      <c r="P217" s="22" t="n">
+        <v>-256.025</v>
+      </c>
+      <c r="Q217" s="22" t="n">
+        <v>892.626</v>
+      </c>
+      <c r="R217" s="22" t="n">
+        <v>-933.052</v>
+      </c>
+      <c r="S217" s="22" t="n">
+        <v>-397.555</v>
+      </c>
+      <c r="T217" s="22" t="n">
+        <v>1277.827</v>
+      </c>
+      <c r="U217" s="22" t="n">
+        <v>-641.9640000000001</v>
+      </c>
+      <c r="V217" s="22" t="n">
+        <v>447.177</v>
+      </c>
+      <c r="W217" s="22" t="n">
+        <v>24226.087</v>
+      </c>
+      <c r="X217" s="22" t="n">
+        <v>-14094.466</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="20" t="inlineStr">
+        <is>
           <t>연결범위 변경에 따른 현금성자산 증감</t>
         </is>
       </c>
-      <c r="E211" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I211" s="22" t="n">
+      <c r="E218" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="22" t="n">
         <v>5.329</v>
       </c>
-      <c r="M211" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V211" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W211" s="22" t="n">
+      <c r="M218" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V218" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W218" s="22" t="n">
         <v>5.329</v>
       </c>
-      <c r="X211" s="22" t="n">
+      <c r="X218" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11618,7 +12089,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -13080,7 +13551,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -13132,7 +13603,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -13184,7 +13655,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -13236,7 +13707,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -13288,7 +13759,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -13340,7 +13811,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -13392,7 +13863,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -13402,43 +13873,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -13462,7 +13933,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -13514,7 +13985,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -13566,7 +14037,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -13618,7 +14089,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -13670,7 +14141,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -13722,7 +14193,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -13792,7 +14263,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -13844,7 +14315,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -13854,49 +14325,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -13906,49 +14377,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -13958,49 +14429,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -14010,43 +14481,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -14070,7 +14541,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -14122,7 +14593,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -14174,7 +14645,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -14226,7 +14697,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -16475,24 +16946,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>

--- a/docs/data/jp/xlsx/3778.xlsx
+++ b/docs/data/jp/xlsx/3778.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재무상태표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터 데이터" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'연간'!$3:$3</definedName>
@@ -21,14 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;;-0.0&quot;x&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;년&quot;;-0.0&quot;년&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0&quot;일&quot;;-0&quot;일&quot;;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,11 +128,31 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -155,6 +177,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -345,7 +372,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -757,7 +799,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3778 Model</t>
+          <t>사쿠라인터넷 Model</t>
         </is>
       </c>
     </row>
@@ -774,7 +816,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>3월 결산 · 일본 기준 · 2027.1Q = 2027년 3월 결산기 1분기</t>
+          <t>3월 결산 · 일본 기준 · 2027.2Q = 2027년 3월 결산기 2분기</t>
         </is>
       </c>
       <c r="Y2" s="4" t="inlineStr">
@@ -796,62 +838,62 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>2024.2Q</t>
+          <t>2024.3Q</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2024.3Q</t>
+          <t>2024.4Q</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.1Q</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
@@ -942,40 +984,40 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>5237.51</v>
+        <v>5315.83</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>5315.83</v>
+        <v>6167.796</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>6167.796</v>
+        <v>5935.785</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>5935.785</v>
+        <v>7335.885</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7335.885</v>
+        <v>8125.387</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>8125.387</v>
+        <v>10015.325</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>10015.325</v>
+        <v>7492.152</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>7492.152</v>
+        <v>8139.01</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>8139.01</v>
+        <v>8393.405000000001</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>8393.405000000001</v>
+        <v>11277.082</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>11277.082</v>
+        <v>11134.597</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>11134.597</v>
+        <v>11692.861</v>
       </c>
       <c r="O4" s="11" t="n">
         <v>13961.972</v>
@@ -1463,40 +1505,40 @@
       </c>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="21" t="n">
-        <v>3884.069</v>
+        <v>3929.928</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>3929.928</v>
+        <v>4457.149</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>4457.149</v>
+        <v>4236.884</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>4236.884</v>
+        <v>4685.563</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>4685.563</v>
+        <v>5159.102</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>5159.102</v>
+        <v>6100.555</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>6100.555</v>
+        <v>5948.216</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>5948.216</v>
+        <v>6534.127</v>
       </c>
       <c r="K11" s="22" t="n">
-        <v>6534.127</v>
+        <v>6504.314</v>
       </c>
       <c r="L11" s="22" t="n">
-        <v>6504.314</v>
+        <v>8358.476000000001</v>
       </c>
       <c r="M11" s="22" t="n">
-        <v>8358.476000000001</v>
+        <v>7713.234</v>
       </c>
       <c r="N11" s="22" t="n">
-        <v>7713.234</v>
+        <v>7801.393</v>
       </c>
       <c r="O11" s="21" t="n">
         <v>9784.241</v>
@@ -1794,40 +1836,40 @@
       </c>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="21" t="n">
-        <v>1208.361</v>
+        <v>1186.81</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>1186.81</v>
+        <v>1274.723</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>1274.723</v>
+        <v>1467.133</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>1467.133</v>
+        <v>1586.202</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>1586.202</v>
+        <v>1676.755</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>1676.755</v>
+        <v>2354.602</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>2354.602</v>
+        <v>2001.106</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>2001.106</v>
+        <v>2068.527</v>
       </c>
       <c r="K15" s="22" t="n">
-        <v>2068.527</v>
+        <v>2085.757</v>
       </c>
       <c r="L15" s="22" t="n">
-        <v>2085.757</v>
+        <v>2204.78</v>
       </c>
       <c r="M15" s="22" t="n">
-        <v>2204.78</v>
+        <v>2190.684</v>
       </c>
       <c r="N15" s="22" t="n">
-        <v>2190.684</v>
+        <v>2159.122</v>
       </c>
       <c r="O15" s="21" t="n">
         <v>3159.669</v>
@@ -1877,40 +1919,40 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>145.081</v>
+        <v>199.092</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>199.092</v>
+        <v>435.923</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>435.923</v>
+        <v>231.767</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>231.767</v>
+        <v>1064.12</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1064.12</v>
+        <v>1289.53</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>1289.53</v>
+        <v>1560.169</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>1560.169</v>
+        <v>-457.171</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>-457.171</v>
+        <v>-463.644</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>-463.644</v>
+        <v>-196.665</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>-196.665</v>
+        <v>713.826</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>713.826</v>
+        <v>1230.678</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1230.678</v>
+        <v>1732.347</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>1018.061</v>
@@ -2906,40 +2948,40 @@
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="21" t="n">
+        <v>5.868</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>1624.819</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>3709.415</v>
+      </c>
+      <c r="F32" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="22" t="n">
-        <v>5.868</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <v>1624.819</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>3709.415</v>
-      </c>
       <c r="G32" s="22" t="n">
+        <v>1623.376</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>787.759</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>6283.839</v>
+      </c>
+      <c r="J32" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>1623.376</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>787.759</v>
-      </c>
-      <c r="J32" s="22" t="n">
-        <v>6283.839</v>
-      </c>
       <c r="K32" s="22" t="n">
-        <v>0</v>
+        <v>137.447</v>
       </c>
       <c r="L32" s="22" t="n">
-        <v>137.447</v>
+        <v>8046.062</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>8046.062</v>
+        <v>2503.629</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>2503.629</v>
+        <v>1.023</v>
       </c>
       <c r="O32" s="21" t="n">
         <v>21.773</v>
@@ -3120,40 +3162,40 @@
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="21" t="n">
-        <v>1.335</v>
+        <v>0.014</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>0.014</v>
+        <v>1624.953</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>1624.953</v>
+        <v>3709.493</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>3709.493</v>
+        <v>30.016</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>30.016</v>
+        <v>1631.954</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>1631.954</v>
+        <v>830.294</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>830.294</v>
+        <v>6283.862</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>6283.862</v>
+        <v>14.609</v>
       </c>
       <c r="K34" s="22" t="n">
-        <v>14.609</v>
+        <v>1.174</v>
       </c>
       <c r="L34" s="22" t="n">
-        <v>1.174</v>
+        <v>8028.858</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>8028.858</v>
+        <v>2504.089</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>2504.089</v>
+        <v>206.542</v>
       </c>
       <c r="O34" s="21" t="n">
         <v>30.15</v>
@@ -3330,40 +3372,40 @@
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="21" t="n">
-        <v>15.082</v>
+        <v>7.783</v>
       </c>
       <c r="D36" s="22" t="n">
-        <v>7.783</v>
+        <v>91.265</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>91.265</v>
+        <v>46.58</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>46.58</v>
+        <v>29.343</v>
       </c>
       <c r="G36" s="22" t="n">
-        <v>29.343</v>
+        <v>128.899</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>128.899</v>
+        <v>92.161</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>92.161</v>
+        <v>149.528</v>
       </c>
       <c r="J36" s="22" t="n">
-        <v>149.528</v>
+        <v>223.472</v>
       </c>
       <c r="K36" s="22" t="n">
-        <v>223.472</v>
+        <v>327.182</v>
       </c>
       <c r="L36" s="22" t="n">
-        <v>327.182</v>
+        <v>363.977</v>
       </c>
       <c r="M36" s="22" t="n">
-        <v>363.977</v>
+        <v>226.474</v>
       </c>
       <c r="N36" s="22" t="n">
-        <v>226.474</v>
+        <v>272.733</v>
       </c>
       <c r="O36" s="21" t="n">
         <v>12.075</v>
@@ -3540,40 +3582,40 @@
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="21" t="n">
-        <v>60.544</v>
+        <v>59.823</v>
       </c>
       <c r="D38" s="22" t="n">
-        <v>59.823</v>
+        <v>82.84099999999999</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>82.84099999999999</v>
+        <v>183.138</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>183.138</v>
+        <v>86.565</v>
       </c>
       <c r="G38" s="22" t="n">
-        <v>86.565</v>
+        <v>32.07</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>32.07</v>
+        <v>80.364</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>80.364</v>
+        <v>130.634</v>
       </c>
       <c r="J38" s="22" t="n">
-        <v>130.634</v>
+        <v>133.313</v>
       </c>
       <c r="K38" s="22" t="n">
-        <v>133.313</v>
+        <v>118.343</v>
       </c>
       <c r="L38" s="22" t="n">
-        <v>118.343</v>
+        <v>172.737</v>
       </c>
       <c r="M38" s="22" t="n">
-        <v>172.737</v>
+        <v>199.088</v>
       </c>
       <c r="N38" s="22" t="n">
-        <v>199.088</v>
+        <v>249.181</v>
       </c>
       <c r="O38" s="21" t="n">
         <v>225.73</v>
@@ -3750,40 +3792,40 @@
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="n">
-        <v>98.28400000000001</v>
+        <v>152.906</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>152.906</v>
+        <v>444.214</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>444.214</v>
+        <v>95.13</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>95.13</v>
+        <v>976.883</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>976.883</v>
+        <v>1377.78</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>1377.78</v>
+        <v>1529.431</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>1529.431</v>
+        <v>-438.299</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>-438.299</v>
+        <v>-388.094</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>-388.094</v>
+        <v>148.446</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>148.446</v>
+        <v>922.269</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>922.269</v>
+        <v>1257.605</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>1257.605</v>
+        <v>1550.38</v>
       </c>
       <c r="O40" s="11" t="n">
         <v>796.029</v>
@@ -3844,40 +3886,40 @@
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="21" t="n">
-        <v>46.442</v>
+        <v>22.421</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>22.421</v>
+        <v>90.515</v>
       </c>
       <c r="E41" s="22" t="n">
-        <v>90.515</v>
+        <v>54.421</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>54.421</v>
+        <v>309.433</v>
       </c>
       <c r="G41" s="22" t="n">
-        <v>309.433</v>
+        <v>441.617</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>441.617</v>
+        <v>220.398</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>220.398</v>
+        <v>-119.319</v>
       </c>
       <c r="J41" s="22" t="n">
-        <v>-119.319</v>
+        <v>-89.794</v>
       </c>
       <c r="K41" s="22" t="n">
-        <v>-89.794</v>
+        <v>67.03400000000001</v>
       </c>
       <c r="L41" s="22" t="n">
-        <v>67.03400000000001</v>
+        <v>151.604</v>
       </c>
       <c r="M41" s="22" t="n">
-        <v>151.604</v>
+        <v>400.032</v>
       </c>
       <c r="N41" s="22" t="n">
-        <v>400.032</v>
+        <v>494.831</v>
       </c>
       <c r="O41" s="21" t="n">
         <v>247.158</v>
@@ -4053,40 +4095,40 @@
       </c>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="n">
-        <v>51.842</v>
+        <v>130.486</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>130.486</v>
+        <v>353.699</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>353.699</v>
+        <v>40.709</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>40.709</v>
+        <v>667.449</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>667.449</v>
+        <v>936.164</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>936.164</v>
+        <v>1309.033</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>1309.033</v>
+        <v>-318.98</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>-318.98</v>
+        <v>-298.3</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>-298.3</v>
+        <v>81.413</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>81.413</v>
+        <v>770.664</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>770.664</v>
+        <v>857.572</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>857.572</v>
+        <v>1055.55</v>
       </c>
       <c r="O43" s="11" t="n">
         <v>548.871</v>
@@ -4147,40 +4189,40 @@
       </c>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="11" t="n">
-        <v>66.672</v>
+        <v>128.866</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>128.866</v>
+        <v>347.712</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>347.712</v>
+        <v>41.721</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>41.721</v>
+        <v>668.35</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>668.35</v>
+        <v>932.2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>932.2</v>
+        <v>1295.188</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>1295.188</v>
+        <v>-324.379</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>-324.379</v>
+        <v>-302.384</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>-302.384</v>
+        <v>75.738</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>75.738</v>
+        <v>767.048</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>767.048</v>
+        <v>855.926</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>855.926</v>
+        <v>1047.917</v>
       </c>
       <c r="O44" s="11" t="n">
         <v>548.871</v>
@@ -4386,11 +4428,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.26)</t>
+          <t>현재 주가 (2026.10.28)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>2927</v>
+        <v>3090</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5627,7 +5669,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.28</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5686,62 +5728,62 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>2024.2Q</t>
+          <t>2024.3Q</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>2024.3Q</t>
+          <t>2024.4Q</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.1Q</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
@@ -5827,40 +5869,40 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>5237.51</v>
+        <v>5315.83</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>5315.83</v>
+        <v>6167.796</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>6167.796</v>
+        <v>5935.785</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>5935.785</v>
+        <v>7335.885</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>7335.885</v>
+        <v>8125.387</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>8125.387</v>
+        <v>10015.325</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>10015.325</v>
+        <v>7492.152</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>7492.152</v>
+        <v>8139.01</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>8139.01</v>
+        <v>8393.405000000001</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>8393.405000000001</v>
+        <v>11277.082</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>11277.082</v>
+        <v>11134.597</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>11134.597</v>
+        <v>11692.861</v>
       </c>
       <c r="T78" s="12" t="n">
         <v>5396.722</v>
@@ -5949,40 +5991,40 @@
         </is>
       </c>
       <c r="C80" s="22" t="n">
-        <v>3884.069</v>
+        <v>3929.928</v>
       </c>
       <c r="D80" s="22" t="n">
-        <v>3929.928</v>
+        <v>4457.149</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>4457.149</v>
+        <v>4236.884</v>
       </c>
       <c r="F80" s="22" t="n">
-        <v>4236.884</v>
+        <v>4685.563</v>
       </c>
       <c r="G80" s="22" t="n">
-        <v>4685.563</v>
+        <v>5159.102</v>
       </c>
       <c r="H80" s="22" t="n">
-        <v>5159.102</v>
+        <v>6100.555</v>
       </c>
       <c r="I80" s="22" t="n">
-        <v>6100.555</v>
+        <v>5948.216</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>5948.216</v>
+        <v>6534.127</v>
       </c>
       <c r="K80" s="22" t="n">
-        <v>6534.127</v>
+        <v>6504.314</v>
       </c>
       <c r="L80" s="22" t="n">
-        <v>6504.314</v>
+        <v>8358.476000000001</v>
       </c>
       <c r="M80" s="22" t="n">
-        <v>8358.476000000001</v>
+        <v>7713.234</v>
       </c>
       <c r="N80" s="22" t="n">
-        <v>7713.234</v>
+        <v>7801.393</v>
       </c>
       <c r="T80" s="22" t="n">
         <v>4032.635</v>
@@ -6007,40 +6049,40 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>1353.442</v>
+        <v>1385.901</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>1385.901</v>
+        <v>1710.647</v>
       </c>
       <c r="E81" s="12" t="n">
-        <v>1710.647</v>
+        <v>1698.9</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1698.9</v>
+        <v>2650.323</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>2650.323</v>
+        <v>2966.284</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>2966.284</v>
+        <v>3914.771</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>3914.771</v>
+        <v>1543.935</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>1543.935</v>
+        <v>1604.883</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>1604.883</v>
+        <v>1889.092</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>1889.092</v>
+        <v>2918.605</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>2918.605</v>
+        <v>3421.363</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>3421.363</v>
+        <v>3891.468</v>
       </c>
       <c r="T81" s="12" t="n">
         <v>1364.087</v>
@@ -6129,40 +6171,40 @@
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.577</v>
+        <v>0.316</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0.316</v>
+        <v>-0.49</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>-0.49</v>
+        <v>0.984</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.984</v>
+        <v>0.332</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0.332</v>
+        <v>0.345</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0.345</v>
+        <v>1.108</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>1.108</v>
+        <v>1.976</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>1.976</v>
+        <v>-0.201</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>-0.201</v>
+        <v>3.618</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>3.618</v>
+        <v>0.505</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>0.505</v>
+        <v>0.043</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>0.043</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="T83" s="22" t="n">
         <v>0.005</v>
@@ -6187,40 +6229,40 @@
         </is>
       </c>
       <c r="C84" s="22" t="n">
-        <v>352.304</v>
+        <v>490.886</v>
       </c>
       <c r="D84" s="22" t="n">
-        <v>490.886</v>
+        <v>368.378</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>368.378</v>
+        <v>453.048</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>453.048</v>
+        <v>465.006</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>465.006</v>
+        <v>656.981</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>656.981</v>
+        <v>607.722</v>
       </c>
       <c r="I84" s="22" t="n">
-        <v>607.722</v>
+        <v>615.433</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>615.433</v>
+        <v>679.801</v>
       </c>
       <c r="K84" s="22" t="n">
-        <v>679.801</v>
+        <v>925.864</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>925.864</v>
+        <v>715.853</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>715.853</v>
+        <v>796.379</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>796.379</v>
+        <v>732.37</v>
       </c>
       <c r="T84" s="22" t="n">
         <v>289.519</v>
@@ -6245,40 +6287,40 @@
         </is>
       </c>
       <c r="C85" s="22" t="n">
-        <v>78.821</v>
+        <v>-59.454</v>
       </c>
       <c r="D85" s="22" t="n">
-        <v>-59.454</v>
+        <v>67.70399999999999</v>
       </c>
       <c r="E85" s="22" t="n">
-        <v>67.70399999999999</v>
+        <v>92.941</v>
       </c>
       <c r="F85" s="22" t="n">
-        <v>92.941</v>
+        <v>88.996</v>
       </c>
       <c r="G85" s="22" t="n">
-        <v>88.996</v>
+        <v>-70.34999999999999</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>-70.34999999999999</v>
+        <v>178.681</v>
       </c>
       <c r="I85" s="22" t="n">
-        <v>178.681</v>
+        <v>124.814</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>124.814</v>
+        <v>162.47</v>
       </c>
       <c r="K85" s="22" t="n">
-        <v>162.47</v>
+        <v>-129.591</v>
       </c>
       <c r="L85" s="22" t="n">
-        <v>-129.591</v>
+        <v>179.255</v>
       </c>
       <c r="M85" s="22" t="n">
-        <v>179.255</v>
+        <v>159.367</v>
       </c>
       <c r="N85" s="22" t="n">
-        <v>159.367</v>
+        <v>149.951</v>
       </c>
       <c r="T85" s="22" t="n">
         <v>61.683</v>
@@ -6302,6 +6344,9 @@
           <t>임원 퇴직위로 충당금 전입</t>
         </is>
       </c>
+      <c r="E86" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="F86" s="22" t="n">
         <v>0</v>
       </c>
@@ -6309,25 +6354,25 @@
         <v>0</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>0</v>
+        <v>50.638</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>50.638</v>
+        <v>12.802</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>12.802</v>
+        <v>2.446</v>
       </c>
       <c r="K86" s="22" t="n">
         <v>2.446</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>2.446</v>
+        <v>2.447</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>2.447</v>
+        <v>14.446</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>14.446</v>
+        <v>2.846</v>
       </c>
       <c r="W86" s="22" t="n">
         <v>50.638</v>
@@ -6342,23 +6387,26 @@
           <t>퇴직급여비용</t>
         </is>
       </c>
+      <c r="G87" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="H87" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="22" t="n">
-        <v>30</v>
-      </c>
       <c r="J87" s="22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N87" s="22" t="n">
         <v>0.9</v>
@@ -6376,32 +6424,35 @@
           <t>지급수수료</t>
         </is>
       </c>
+      <c r="E88" s="22" t="n">
+        <v>305.837</v>
+      </c>
       <c r="F88" s="22" t="n">
-        <v>305.837</v>
+        <v>356.703</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>356.703</v>
+        <v>361.766</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>361.766</v>
+        <v>432.686</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>432.686</v>
+        <v>450.458</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>450.458</v>
+        <v>361.404</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>361.404</v>
+        <v>385.465</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>385.465</v>
+        <v>413.389</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>413.389</v>
+        <v>330.858</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>330.858</v>
+        <v>380.057</v>
       </c>
       <c r="W88" s="22" t="n">
         <v>432.686</v>
@@ -6417,40 +6468,40 @@
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>776.659</v>
+        <v>755.061</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>755.061</v>
+        <v>-429.901</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>-429.901</v>
+        <v>614.321</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>614.321</v>
+        <v>675.165</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>675.165</v>
+        <v>728.013</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>728.013</v>
+        <v>714.141</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>714.141</v>
+        <v>795.621</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>795.621</v>
+        <v>861.106</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>861.106</v>
+        <v>897.207</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>897.207</v>
+        <v>515.975</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>515.975</v>
+        <v>888.688</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>888.688</v>
+        <v>893.563</v>
       </c>
       <c r="T89" s="22" t="n">
         <v>-461.657</v>
@@ -6475,40 +6526,40 @@
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>1208.361</v>
+        <v>1186.81</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>1186.81</v>
+        <v>1274.723</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>1274.723</v>
+        <v>1467.133</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>1467.133</v>
+        <v>1586.202</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>1586.202</v>
+        <v>1676.755</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>1676.755</v>
+        <v>2354.602</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>2354.602</v>
+        <v>2001.106</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>2001.106</v>
+        <v>2068.527</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>2068.527</v>
+        <v>2085.757</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>2085.757</v>
+        <v>2204.78</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>2204.78</v>
+        <v>2190.684</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>2190.684</v>
+        <v>2159.122</v>
       </c>
       <c r="T90" s="22" t="n">
         <v>1039.892</v>
@@ -6533,40 +6584,40 @@
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>145.081</v>
+        <v>199.092</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>199.092</v>
+        <v>435.923</v>
       </c>
       <c r="E91" s="12" t="n">
-        <v>435.923</v>
+        <v>231.767</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>231.767</v>
+        <v>1064.12</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1064.12</v>
+        <v>1289.53</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>1289.53</v>
+        <v>1560.169</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>1560.169</v>
+        <v>-457.171</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>-457.171</v>
+        <v>-463.644</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>-463.644</v>
+        <v>-196.665</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>-196.665</v>
+        <v>713.826</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>713.826</v>
+        <v>1230.678</v>
       </c>
       <c r="N91" s="12" t="n">
-        <v>1230.678</v>
+        <v>1732.347</v>
       </c>
       <c r="T91" s="12" t="n">
         <v>324.195</v>
@@ -6735,40 +6786,40 @@
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>0.011</v>
+        <v>0.102</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>0.102</v>
+        <v>1.467</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>1.467</v>
+        <v>0.3</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>0.3</v>
+        <v>1.04</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>1.04</v>
+        <v>14.487</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>14.487</v>
+        <v>0.994</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>0.994</v>
+        <v>24.108</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>24.108</v>
+        <v>9.542999999999999</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>9.542999999999999</v>
+        <v>11.689</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>11.689</v>
+        <v>14.507</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>14.507</v>
+        <v>19.451</v>
       </c>
       <c r="T94" s="22" t="n">
         <v>0.021</v>
@@ -6805,28 +6856,28 @@
         <v>0</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>0</v>
+        <v>19.571</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>19.571</v>
+        <v>6.642</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>6.642</v>
+        <v>37.234</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>37.234</v>
+        <v>3.122</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>3.122</v>
+        <v>18.229</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>18.229</v>
+        <v>18.686</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>18.686</v>
+        <v>51.464</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>51.464</v>
+        <v>5.809</v>
       </c>
       <c r="T95" s="22" t="n">
         <v>4.56</v>
@@ -6851,25 +6902,25 @@
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>0.081</v>
+        <v>-0.01</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>-0.01</v>
+        <v>-0.182</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>-0.182</v>
+        <v>0.317</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>0.317</v>
+        <v>0.079</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>0.079</v>
+        <v>0.097</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>0.097</v>
+        <v>0.053</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="J96" s="22" t="n">
         <v>0</v>
@@ -6880,9 +6931,6 @@
       <c r="L96" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M96" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="T96" s="22" t="n">
         <v>-0.364</v>
       </c>
@@ -6905,7 +6953,7 @@
           <t>업무수탁료</t>
         </is>
       </c>
-      <c r="E97" s="22" t="n">
+      <c r="D97" s="22" t="n">
         <v>3.575</v>
       </c>
       <c r="U97" s="22" t="n">
@@ -6924,23 +6972,17 @@
       <c r="C98" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D98" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>Temporary Transfer Charges Income NOI</t>
+          <t>수입 파견료</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>3.234</v>
+        <v>2.89</v>
       </c>
       <c r="D99" s="22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E99" s="22" t="n">
         <v>1.869</v>
       </c>
       <c r="T99" s="22" t="n">
@@ -6963,37 +7005,37 @@
         <v>0</v>
       </c>
       <c r="D100" s="22" t="n">
-        <v>0</v>
+        <v>9.494999999999999</v>
       </c>
       <c r="E100" s="22" t="n">
-        <v>9.494999999999999</v>
+        <v>25.292</v>
       </c>
       <c r="F100" s="22" t="n">
-        <v>25.292</v>
+        <v>20.066</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>20.066</v>
+        <v>51.59</v>
       </c>
       <c r="H100" s="22" t="n">
-        <v>51.59</v>
+        <v>63.831</v>
       </c>
       <c r="I100" s="22" t="n">
-        <v>63.831</v>
+        <v>92.321</v>
       </c>
       <c r="J100" s="22" t="n">
-        <v>92.321</v>
+        <v>170.64</v>
       </c>
       <c r="K100" s="22" t="n">
-        <v>170.64</v>
+        <v>259.205</v>
       </c>
       <c r="L100" s="22" t="n">
-        <v>259.205</v>
+        <v>95.462</v>
       </c>
       <c r="M100" s="22" t="n">
-        <v>95.462</v>
+        <v>137.969</v>
       </c>
       <c r="N100" s="22" t="n">
-        <v>137.969</v>
+        <v>212.904</v>
       </c>
       <c r="V100" s="22" t="n">
         <v>9.494999999999999</v>
@@ -7012,40 +7054,40 @@
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>14.989</v>
+        <v>7.782</v>
       </c>
       <c r="D101" s="22" t="n">
-        <v>7.782</v>
+        <v>-14.155</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>-14.155</v>
+        <v>19.502</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>19.502</v>
+        <v>8.898999999999999</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>8.898999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>56.6</v>
+        <v>-33.707</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>-33.707</v>
+        <v>18.979</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>18.979</v>
+        <v>25.601</v>
       </c>
       <c r="K101" s="22" t="n">
-        <v>25.601</v>
+        <v>40.204</v>
       </c>
       <c r="L101" s="22" t="n">
-        <v>40.204</v>
+        <v>-13.139</v>
       </c>
       <c r="M101" s="22" t="n">
-        <v>-13.139</v>
+        <v>22.532</v>
       </c>
       <c r="N101" s="22" t="n">
-        <v>22.532</v>
+        <v>34.569</v>
       </c>
       <c r="T101" s="22" t="n">
         <v>-11.388</v>
@@ -7070,40 +7112,40 @@
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>15.082</v>
+        <v>7.783</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>7.783</v>
+        <v>91.265</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>91.265</v>
+        <v>46.58</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>46.58</v>
+        <v>29.343</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>29.343</v>
+        <v>128.899</v>
       </c>
       <c r="H102" s="22" t="n">
-        <v>128.899</v>
+        <v>92.161</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>92.161</v>
+        <v>149.528</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>149.528</v>
+        <v>223.472</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>223.472</v>
+        <v>327.182</v>
       </c>
       <c r="L102" s="22" t="n">
-        <v>327.182</v>
+        <v>363.977</v>
       </c>
       <c r="M102" s="22" t="n">
-        <v>363.977</v>
+        <v>226.474</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>226.474</v>
+        <v>272.733</v>
       </c>
       <c r="T102" s="22" t="n">
         <v>25.772</v>
@@ -7128,40 +7170,40 @@
         </is>
       </c>
       <c r="C103" s="22" t="n">
-        <v>43.376</v>
+        <v>44.217</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>44.217</v>
+        <v>45.299</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>45.299</v>
+        <v>53.729</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>53.729</v>
+        <v>59.73</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>59.73</v>
+        <v>64.011</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>64.011</v>
+        <v>78.092</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>78.092</v>
+        <v>108.696</v>
       </c>
       <c r="J103" s="22" t="n">
-        <v>108.696</v>
+        <v>125.347</v>
       </c>
       <c r="K103" s="22" t="n">
-        <v>125.347</v>
+        <v>143.082</v>
       </c>
       <c r="L103" s="22" t="n">
-        <v>143.082</v>
+        <v>161.697</v>
       </c>
       <c r="M103" s="22" t="n">
-        <v>161.697</v>
+        <v>180.876</v>
       </c>
       <c r="N103" s="22" t="n">
-        <v>180.876</v>
+        <v>237.868</v>
       </c>
       <c r="T103" s="22" t="n">
         <v>39.813</v>
@@ -7186,22 +7228,22 @@
         </is>
       </c>
       <c r="C104" s="22" t="n">
-        <v>1.667</v>
+        <v>0.749</v>
       </c>
       <c r="D104" s="22" t="n">
-        <v>0.749</v>
+        <v>-3.794</v>
       </c>
       <c r="E104" s="22" t="n">
-        <v>-3.794</v>
+        <v>7.383</v>
       </c>
       <c r="F104" s="22" t="n">
-        <v>7.383</v>
+        <v>5.031</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>5.031</v>
+        <v>-12.414</v>
       </c>
       <c r="H104" s="22" t="n">
-        <v>-12.414</v>
+        <v>0</v>
       </c>
       <c r="I104" s="22" t="n">
         <v>0</v>
@@ -7209,9 +7251,6 @@
       <c r="J104" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K104" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="U104" s="22" t="n">
         <v>1.688</v>
       </c>
@@ -7235,13 +7274,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="22" t="n">
+        <v>109.766</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>-0.238</v>
+      </c>
+      <c r="G105" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>109.766</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>-0.238</v>
       </c>
       <c r="H105" s="22" t="n">
         <v>0</v>
@@ -7258,9 +7297,6 @@
       <c r="L105" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M105" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="V105" s="22" t="n">
         <v>0</v>
       </c>
@@ -7278,40 +7314,40 @@
         </is>
       </c>
       <c r="C106" s="22" t="n">
-        <v>15.501</v>
+        <v>14.857</v>
       </c>
       <c r="D106" s="22" t="n">
-        <v>14.857</v>
+        <v>-1.96</v>
       </c>
       <c r="E106" s="22" t="n">
-        <v>-1.96</v>
+        <v>12.26</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>12.26</v>
+        <v>22.04</v>
       </c>
       <c r="G106" s="22" t="n">
-        <v>22.04</v>
+        <v>-19.526</v>
       </c>
       <c r="H106" s="22" t="n">
-        <v>-19.526</v>
+        <v>-5.101</v>
       </c>
       <c r="I106" s="22" t="n">
-        <v>-5.101</v>
+        <v>21.938</v>
       </c>
       <c r="J106" s="22" t="n">
-        <v>21.938</v>
+        <v>7.965</v>
       </c>
       <c r="K106" s="22" t="n">
-        <v>7.965</v>
+        <v>-24.739</v>
       </c>
       <c r="L106" s="22" t="n">
-        <v>-24.739</v>
+        <v>5.17</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>5.17</v>
+        <v>18.212</v>
       </c>
       <c r="N106" s="22" t="n">
-        <v>18.212</v>
+        <v>11.312</v>
       </c>
       <c r="T106" s="22" t="n">
         <v>11.257</v>
@@ -7336,40 +7372,40 @@
         </is>
       </c>
       <c r="C107" s="22" t="n">
-        <v>60.544</v>
+        <v>59.823</v>
       </c>
       <c r="D107" s="22" t="n">
-        <v>59.823</v>
+        <v>82.84099999999999</v>
       </c>
       <c r="E107" s="22" t="n">
-        <v>82.84099999999999</v>
+        <v>183.138</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>183.138</v>
+        <v>86.565</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>86.565</v>
+        <v>32.07</v>
       </c>
       <c r="H107" s="22" t="n">
-        <v>32.07</v>
+        <v>80.364</v>
       </c>
       <c r="I107" s="22" t="n">
-        <v>80.364</v>
+        <v>130.634</v>
       </c>
       <c r="J107" s="22" t="n">
-        <v>130.634</v>
+        <v>133.313</v>
       </c>
       <c r="K107" s="22" t="n">
-        <v>133.313</v>
+        <v>118.343</v>
       </c>
       <c r="L107" s="22" t="n">
-        <v>118.343</v>
+        <v>172.737</v>
       </c>
       <c r="M107" s="22" t="n">
-        <v>172.737</v>
+        <v>199.088</v>
       </c>
       <c r="N107" s="22" t="n">
-        <v>199.088</v>
+        <v>249.181</v>
       </c>
       <c r="T107" s="22" t="n">
         <v>53.426</v>
@@ -7394,40 +7430,40 @@
         </is>
       </c>
       <c r="C108" s="12" t="n">
-        <v>99.619</v>
+        <v>147.052</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>147.052</v>
+        <v>444.348</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>444.348</v>
+        <v>95.208</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>95.208</v>
+        <v>1006.9</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>1006.9</v>
+        <v>1386.358</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>1386.358</v>
+        <v>1571.965</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>1571.965</v>
+        <v>-438.277</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>-438.277</v>
+        <v>-373.485</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>-373.485</v>
+        <v>12.174</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>12.174</v>
+        <v>905.0650000000001</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>905.0650000000001</v>
+        <v>1258.064</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>1258.064</v>
+        <v>1755.9</v>
       </c>
       <c r="T108" s="12" t="n">
         <v>296.54</v>
@@ -7516,36 +7552,33 @@
         </is>
       </c>
       <c r="C110" s="22" t="n">
+        <v>5.868</v>
+      </c>
+      <c r="D110" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="22" t="n">
-        <v>5.868</v>
-      </c>
       <c r="E110" s="22" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="F110" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="22" t="n">
-        <v>0.034</v>
-      </c>
       <c r="G110" s="22" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="I110" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="H110" s="22" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="I110" s="22" t="n">
-        <v>0.459</v>
       </c>
       <c r="J110" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="22" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L110" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M110" s="22" t="n">
         <v>0</v>
       </c>
       <c r="T110" s="22" t="n">
@@ -7588,10 +7621,10 @@
       <c r="H111" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="22" t="n">
+      <c r="K111" s="22" t="n">
+        <v>137.386</v>
+      </c>
+      <c r="L111" s="22" t="n">
         <v>18.209</v>
       </c>
       <c r="U111" s="22" t="n">
@@ -7610,44 +7643,44 @@
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>AState Government Subsidy Income EI</t>
+          <t>국고보조금 등 수입</t>
         </is>
       </c>
       <c r="C112" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="22" t="n">
+        <v>1624.819</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>3709.381</v>
+      </c>
+      <c r="F112" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="22" t="n">
-        <v>1624.819</v>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>3709.381</v>
-      </c>
       <c r="G112" s="22" t="n">
+        <v>1623.063</v>
+      </c>
+      <c r="H112" s="22" t="n">
+        <v>787.3</v>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>6283.839</v>
+      </c>
+      <c r="J112" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="H112" s="22" t="n">
-        <v>1623.063</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>787.3</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>6283.839</v>
       </c>
       <c r="K112" s="22" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="22" t="n">
-        <v>0</v>
+        <v>8027.854</v>
       </c>
       <c r="M112" s="22" t="n">
-        <v>8027.854</v>
+        <v>2503.629</v>
       </c>
       <c r="N112" s="22" t="n">
-        <v>2503.629</v>
+        <v>-4.325</v>
       </c>
       <c r="V112" s="22" t="n">
         <v>1624.819</v>
@@ -7666,40 +7699,40 @@
         </is>
       </c>
       <c r="C113" s="22" t="n">
+        <v>5.868</v>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>1624.819</v>
+      </c>
+      <c r="E113" s="22" t="n">
+        <v>3709.415</v>
+      </c>
+      <c r="F113" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="22" t="n">
-        <v>5.868</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>1624.819</v>
-      </c>
-      <c r="F113" s="22" t="n">
-        <v>3709.415</v>
-      </c>
       <c r="G113" s="22" t="n">
+        <v>1623.376</v>
+      </c>
+      <c r="H113" s="22" t="n">
+        <v>787.759</v>
+      </c>
+      <c r="I113" s="22" t="n">
+        <v>6283.839</v>
+      </c>
+      <c r="J113" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="22" t="n">
-        <v>1623.376</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>787.759</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>6283.839</v>
-      </c>
       <c r="K113" s="22" t="n">
-        <v>0</v>
+        <v>137.447</v>
       </c>
       <c r="L113" s="22" t="n">
-        <v>137.447</v>
+        <v>8046.062</v>
       </c>
       <c r="M113" s="22" t="n">
-        <v>8046.062</v>
+        <v>2503.629</v>
       </c>
       <c r="N113" s="22" t="n">
-        <v>2503.629</v>
+        <v>1.023</v>
       </c>
       <c r="T113" s="22" t="n">
         <v>0.032</v>
@@ -7720,91 +7753,97 @@
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="C114" s="22" t="n">
-        <v>1.334</v>
-      </c>
-      <c r="D114" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E114" s="22" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="F114" s="22" t="n">
-        <v>0.112</v>
+          <t>고정자산 매각손실</t>
+        </is>
       </c>
       <c r="G114" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="L114" s="22" t="n">
         <v>0.016</v>
       </c>
-      <c r="H114" s="22" t="n">
-        <v>9.364000000000001</v>
-      </c>
-      <c r="I114" s="22" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="J114" s="22" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K114" s="22" t="n">
-        <v>13.733</v>
-      </c>
-      <c r="L114" s="22" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="M114" s="22" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="N114" s="22" t="n">
-        <v>0.459</v>
-      </c>
       <c r="T114" s="22" t="n">
-        <v>2.511</v>
+        <v>0</v>
       </c>
       <c r="U114" s="22" t="n">
-        <v>9.138999999999999</v>
-      </c>
-      <c r="V114" s="22" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="W114" s="22" t="n">
-        <v>42.52</v>
+        <v>0</v>
       </c>
       <c r="X114" s="22" t="n">
-        <v>0.989</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="C115" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="E115" s="22" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="F115" s="22" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G115" s="22" t="n">
+        <v>9.364000000000001</v>
+      </c>
+      <c r="H115" s="22" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="I115" s="22" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="J115" s="22" t="n">
+        <v>13.733</v>
+      </c>
+      <c r="K115" s="22" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="L115" s="22" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="M115" s="22" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="N115" s="22" t="n">
+        <v>123.56</v>
       </c>
       <c r="T115" s="22" t="n">
-        <v>0</v>
+        <v>2.511</v>
       </c>
       <c r="U115" s="22" t="n">
-        <v>0</v>
+        <v>9.138999999999999</v>
+      </c>
+      <c r="V115" s="22" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="W115" s="22" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="X115" s="22" t="n">
+        <v>0.989</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손실</t>
-        </is>
-      </c>
-      <c r="H116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="22" t="n">
-        <v>1.205</v>
-      </c>
-      <c r="M116" s="22" t="n">
-        <v>0.016</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="T116" s="22" t="n">
         <v>0</v>
@@ -7812,12 +7851,6 @@
       <c r="U116" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" s="22" t="n">
-        <v>0.016</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
@@ -7829,37 +7862,37 @@
         <v>0</v>
       </c>
       <c r="D117" s="22" t="n">
+        <v>1624.819</v>
+      </c>
+      <c r="E117" s="22" t="n">
+        <v>3709.381</v>
+      </c>
+      <c r="F117" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="22" t="n">
-        <v>1624.819</v>
-      </c>
-      <c r="F117" s="22" t="n">
-        <v>3709.381</v>
-      </c>
       <c r="G117" s="22" t="n">
+        <v>1622.59</v>
+      </c>
+      <c r="H117" s="22" t="n">
+        <v>787.773</v>
+      </c>
+      <c r="I117" s="22" t="n">
+        <v>6283.839</v>
+      </c>
+      <c r="J117" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="H117" s="22" t="n">
-        <v>1622.59</v>
-      </c>
-      <c r="I117" s="22" t="n">
-        <v>787.773</v>
-      </c>
-      <c r="J117" s="22" t="n">
-        <v>6283.839</v>
       </c>
       <c r="K117" s="22" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="22" t="n">
-        <v>0</v>
+        <v>8027.854</v>
       </c>
       <c r="M117" s="22" t="n">
-        <v>8027.854</v>
+        <v>2503.629</v>
       </c>
       <c r="N117" s="22" t="n">
-        <v>2503.629</v>
+        <v>-4.325</v>
       </c>
       <c r="V117" s="22" t="n">
         <v>1624.819</v>
@@ -7877,24 +7910,24 @@
           <t>투자유가증권 평가손실</t>
         </is>
       </c>
+      <c r="C118" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="D118" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="22" t="n">
+      <c r="G118" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I118" s="22" t="n">
+      <c r="K118" s="22" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M118" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="V118" s="22" t="n">
         <v>0</v>
       </c>
@@ -7914,7 +7947,7 @@
       <c r="C119" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="22" t="n">
+      <c r="E119" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="22" t="n">
@@ -7923,9 +7956,6 @@
       <c r="G119" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H119" s="22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
@@ -7934,40 +7964,40 @@
         </is>
       </c>
       <c r="C120" s="22" t="n">
-        <v>1.335</v>
+        <v>0.014</v>
       </c>
       <c r="D120" s="22" t="n">
-        <v>0.014</v>
+        <v>1624.953</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>1624.953</v>
+        <v>3709.493</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>3709.493</v>
+        <v>30.016</v>
       </c>
       <c r="G120" s="22" t="n">
-        <v>30.016</v>
+        <v>1631.954</v>
       </c>
       <c r="H120" s="22" t="n">
-        <v>1631.954</v>
+        <v>830.294</v>
       </c>
       <c r="I120" s="22" t="n">
-        <v>830.294</v>
+        <v>6283.862</v>
       </c>
       <c r="J120" s="22" t="n">
-        <v>6283.862</v>
+        <v>14.609</v>
       </c>
       <c r="K120" s="22" t="n">
-        <v>14.609</v>
+        <v>1.174</v>
       </c>
       <c r="L120" s="22" t="n">
-        <v>1.174</v>
+        <v>8028.858</v>
       </c>
       <c r="M120" s="22" t="n">
-        <v>8028.858</v>
+        <v>2504.089</v>
       </c>
       <c r="N120" s="22" t="n">
-        <v>2504.089</v>
+        <v>206.542</v>
       </c>
       <c r="T120" s="22" t="n">
         <v>2.51</v>
@@ -7992,40 +8022,40 @@
         </is>
       </c>
       <c r="C121" s="12" t="n">
-        <v>98.28400000000001</v>
+        <v>152.906</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>152.906</v>
+        <v>444.214</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>444.214</v>
+        <v>95.13</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>95.13</v>
+        <v>976.883</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>976.883</v>
+        <v>1377.78</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>1377.78</v>
+        <v>1529.431</v>
       </c>
       <c r="I121" s="12" t="n">
-        <v>1529.431</v>
+        <v>-438.299</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>-438.299</v>
+        <v>-388.094</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>-388.094</v>
+        <v>148.446</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>148.446</v>
+        <v>922.269</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>922.269</v>
+        <v>1257.605</v>
       </c>
       <c r="N121" s="12" t="n">
-        <v>1257.605</v>
+        <v>1550.38</v>
       </c>
       <c r="T121" s="12" t="n">
         <v>294.062</v>
@@ -8050,40 +8080,40 @@
         </is>
       </c>
       <c r="C122" s="22" t="n">
-        <v>128.224</v>
+        <v>-6.844</v>
       </c>
       <c r="D122" s="22" t="n">
-        <v>-6.844</v>
+        <v>147.56</v>
       </c>
       <c r="E122" s="22" t="n">
-        <v>147.56</v>
+        <v>15.041</v>
       </c>
       <c r="F122" s="22" t="n">
-        <v>15.041</v>
+        <v>479.685</v>
       </c>
       <c r="G122" s="22" t="n">
-        <v>479.685</v>
+        <v>437.255</v>
       </c>
       <c r="H122" s="22" t="n">
-        <v>437.255</v>
+        <v>543.503</v>
       </c>
       <c r="I122" s="22" t="n">
-        <v>543.503</v>
+        <v>-5.14</v>
       </c>
       <c r="J122" s="22" t="n">
-        <v>-5.14</v>
+        <v>24.327</v>
       </c>
       <c r="K122" s="22" t="n">
-        <v>24.327</v>
+        <v>21.516</v>
       </c>
       <c r="L122" s="22" t="n">
-        <v>21.516</v>
+        <v>391.47</v>
       </c>
       <c r="M122" s="22" t="n">
-        <v>391.47</v>
+        <v>480.114</v>
       </c>
       <c r="N122" s="22" t="n">
-        <v>480.114</v>
+        <v>899.5599999999999</v>
       </c>
       <c r="T122" s="22" t="n">
         <v>78.794</v>
@@ -8108,40 +8138,40 @@
         </is>
       </c>
       <c r="C123" s="22" t="n">
-        <v>-81.782</v>
+        <v>29.266</v>
       </c>
       <c r="D123" s="22" t="n">
-        <v>29.266</v>
+        <v>-57.046</v>
       </c>
       <c r="E123" s="22" t="n">
-        <v>-57.046</v>
+        <v>39.379</v>
       </c>
       <c r="F123" s="22" t="n">
-        <v>39.379</v>
+        <v>-170.251</v>
       </c>
       <c r="G123" s="22" t="n">
-        <v>-170.251</v>
+        <v>4.362</v>
       </c>
       <c r="H123" s="22" t="n">
-        <v>4.362</v>
+        <v>-323.105</v>
       </c>
       <c r="I123" s="22" t="n">
-        <v>-323.105</v>
+        <v>-114.178</v>
       </c>
       <c r="J123" s="22" t="n">
-        <v>-114.178</v>
+        <v>-114.122</v>
       </c>
       <c r="K123" s="22" t="n">
-        <v>-114.122</v>
+        <v>45.517</v>
       </c>
       <c r="L123" s="22" t="n">
-        <v>45.517</v>
+        <v>-239.864</v>
       </c>
       <c r="M123" s="22" t="n">
-        <v>-239.864</v>
+        <v>-80.08199999999999</v>
       </c>
       <c r="N123" s="22" t="n">
-        <v>-80.08199999999999</v>
+        <v>-404.729</v>
       </c>
       <c r="T123" s="22" t="n">
         <v>-5.992</v>
@@ -8166,40 +8196,40 @@
         </is>
       </c>
       <c r="C124" s="22" t="n">
-        <v>46.442</v>
+        <v>22.421</v>
       </c>
       <c r="D124" s="22" t="n">
-        <v>22.421</v>
+        <v>90.515</v>
       </c>
       <c r="E124" s="22" t="n">
-        <v>90.515</v>
+        <v>54.421</v>
       </c>
       <c r="F124" s="22" t="n">
-        <v>54.421</v>
+        <v>309.433</v>
       </c>
       <c r="G124" s="22" t="n">
-        <v>309.433</v>
+        <v>441.617</v>
       </c>
       <c r="H124" s="22" t="n">
-        <v>441.617</v>
+        <v>220.398</v>
       </c>
       <c r="I124" s="22" t="n">
-        <v>220.398</v>
+        <v>-119.319</v>
       </c>
       <c r="J124" s="22" t="n">
-        <v>-119.319</v>
+        <v>-89.794</v>
       </c>
       <c r="K124" s="22" t="n">
-        <v>-89.794</v>
+        <v>67.03400000000001</v>
       </c>
       <c r="L124" s="22" t="n">
-        <v>67.03400000000001</v>
+        <v>151.604</v>
       </c>
       <c r="M124" s="22" t="n">
-        <v>151.604</v>
+        <v>400.032</v>
       </c>
       <c r="N124" s="22" t="n">
-        <v>400.032</v>
+        <v>494.831</v>
       </c>
       <c r="T124" s="22" t="n">
         <v>72.80200000000001</v>
@@ -8224,40 +8254,40 @@
         </is>
       </c>
       <c r="C125" s="12" t="n">
-        <v>51.842</v>
+        <v>130.486</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>130.486</v>
+        <v>353.699</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>353.699</v>
+        <v>40.709</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>40.709</v>
+        <v>667.449</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>667.449</v>
+        <v>936.164</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>936.164</v>
+        <v>1309.033</v>
       </c>
       <c r="I125" s="12" t="n">
-        <v>1309.033</v>
+        <v>-318.98</v>
       </c>
       <c r="J125" s="12" t="n">
-        <v>-318.98</v>
+        <v>-298.3</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>-298.3</v>
+        <v>81.413</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>81.413</v>
+        <v>770.664</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>770.664</v>
+        <v>857.572</v>
       </c>
       <c r="N125" s="12" t="n">
-        <v>857.572</v>
+        <v>1055.55</v>
       </c>
       <c r="T125" s="12" t="n">
         <v>221.26</v>
@@ -8346,40 +8376,40 @@
         </is>
       </c>
       <c r="C127" s="12" t="n">
-        <v>-14.831</v>
+        <v>1.62</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>1.62</v>
+        <v>5.987</v>
       </c>
       <c r="E127" s="12" t="n">
-        <v>5.987</v>
+        <v>-1.011</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>-1.011</v>
+        <v>-0.901</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>-0.901</v>
+        <v>3.962</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>3.962</v>
+        <v>13.845</v>
       </c>
       <c r="I127" s="12" t="n">
-        <v>13.845</v>
+        <v>5.398</v>
       </c>
       <c r="J127" s="12" t="n">
-        <v>5.398</v>
+        <v>4.084</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>4.084</v>
+        <v>5.675</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>5.675</v>
+        <v>3.616</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>3.616</v>
+        <v>1.646</v>
       </c>
       <c r="N127" s="12" t="n">
-        <v>1.646</v>
+        <v>7.632</v>
       </c>
       <c r="T127" s="12" t="n">
         <v>23.371</v>
@@ -8404,40 +8434,40 @@
         </is>
       </c>
       <c r="C128" s="12" t="n">
-        <v>66.672</v>
+        <v>128.866</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128.866</v>
+        <v>347.712</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>347.712</v>
+        <v>41.721</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>41.721</v>
+        <v>668.35</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>668.35</v>
+        <v>932.2</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>932.2</v>
+        <v>1295.188</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>1295.188</v>
+        <v>-324.379</v>
       </c>
       <c r="J128" s="12" t="n">
-        <v>-324.379</v>
+        <v>-302.384</v>
       </c>
       <c r="K128" s="12" t="n">
-        <v>-302.384</v>
+        <v>75.738</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>75.738</v>
+        <v>767.048</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>767.048</v>
+        <v>855.926</v>
       </c>
       <c r="N128" s="12" t="n">
-        <v>855.926</v>
+        <v>1047.917</v>
       </c>
       <c r="T128" s="12" t="n">
         <v>197.888</v>
@@ -8571,62 +8601,62 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2024.2Q</t>
+          <t>2024.3Q</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>2024.3Q</t>
+          <t>2024.4Q</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.1Q</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="N132" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="O132" s="5" t="inlineStr">
@@ -8712,40 +8742,40 @@
         </is>
       </c>
       <c r="C133" s="12" t="n">
-        <v>51.842</v>
+        <v>130.486</v>
       </c>
       <c r="D133" s="12" t="n">
-        <v>130.486</v>
+        <v>353.699</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>353.699</v>
+        <v>40.709</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>40.709</v>
+        <v>667.449</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>667.449</v>
+        <v>936.164</v>
       </c>
       <c r="H133" s="12" t="n">
-        <v>936.164</v>
+        <v>1309.033</v>
       </c>
       <c r="I133" s="12" t="n">
-        <v>1309.033</v>
+        <v>-318.98</v>
       </c>
       <c r="J133" s="12" t="n">
-        <v>-318.98</v>
+        <v>-298.3</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>-298.3</v>
+        <v>81.413</v>
       </c>
       <c r="L133" s="12" t="n">
-        <v>81.413</v>
+        <v>770.664</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>770.664</v>
+        <v>857.572</v>
       </c>
       <c r="N133" s="12" t="n">
-        <v>857.572</v>
+        <v>1055.55</v>
       </c>
       <c r="T133" s="12" t="n">
         <v>221.26</v>
@@ -8770,40 +8800,40 @@
         </is>
       </c>
       <c r="C134" s="22" t="n">
-        <v>-54.413</v>
+        <v>-83.655</v>
       </c>
       <c r="D134" s="22" t="n">
-        <v>-83.655</v>
+        <v>31.081</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>31.081</v>
+        <v>-30.201</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>-30.201</v>
+        <v>-33.611</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>-33.611</v>
+        <v>-8.762</v>
       </c>
       <c r="H134" s="22" t="n">
-        <v>-8.762</v>
+        <v>52.12</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>52.12</v>
+        <v>45.913</v>
       </c>
       <c r="J134" s="22" t="n">
-        <v>45.913</v>
+        <v>-2.86</v>
       </c>
       <c r="K134" s="22" t="n">
-        <v>-2.86</v>
+        <v>-125.285</v>
       </c>
       <c r="L134" s="22" t="n">
-        <v>-125.285</v>
+        <v>-19.547</v>
       </c>
       <c r="M134" s="22" t="n">
-        <v>-19.547</v>
+        <v>-0.004</v>
       </c>
       <c r="N134" s="22" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="T134" s="22" t="n">
         <v>0.018</v>
@@ -8828,40 +8858,40 @@
         </is>
       </c>
       <c r="C135" s="22" t="n">
-        <v>-3.074</v>
+        <v>-0.032</v>
       </c>
       <c r="D135" s="22" t="n">
-        <v>-0.032</v>
+        <v>0.176</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>0.176</v>
+        <v>-0.155</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>-0.155</v>
+        <v>-2.211</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>-2.211</v>
+        <v>9.288</v>
       </c>
       <c r="H135" s="22" t="n">
-        <v>9.288</v>
+        <v>-7.093</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>-7.093</v>
+        <v>-0.87</v>
       </c>
       <c r="J135" s="22" t="n">
-        <v>-0.87</v>
+        <v>6.086</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>6.086</v>
+        <v>1.672</v>
       </c>
       <c r="L135" s="22" t="n">
-        <v>1.672</v>
+        <v>-6.611</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>-6.611</v>
+        <v>2.258</v>
       </c>
       <c r="N135" s="22" t="n">
-        <v>2.258</v>
+        <v>-138.371</v>
       </c>
       <c r="T135" s="22" t="n">
         <v>-0.638</v>
@@ -8886,40 +8916,40 @@
         </is>
       </c>
       <c r="C136" s="22" t="n">
-        <v>1.183</v>
+        <v>-1.739</v>
       </c>
       <c r="D136" s="22" t="n">
-        <v>-1.739</v>
+        <v>2.256</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>2.256</v>
+        <v>2.296</v>
       </c>
       <c r="F136" s="22" t="n">
-        <v>2.296</v>
+        <v>-4.244</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>-4.244</v>
+        <v>3.8</v>
       </c>
       <c r="H136" s="22" t="n">
-        <v>3.8</v>
+        <v>-2.098</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>-2.098</v>
+        <v>-1.48</v>
       </c>
       <c r="J136" s="22" t="n">
-        <v>-1.48</v>
+        <v>1.358</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>1.358</v>
+        <v>1.875</v>
       </c>
       <c r="L136" s="22" t="n">
-        <v>1.875</v>
+        <v>0.496</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>0.496</v>
+        <v>0.577</v>
       </c>
       <c r="N136" s="22" t="n">
-        <v>0.577</v>
+        <v>-1.248</v>
       </c>
       <c r="T136" s="22" t="n">
         <v>2.23</v>
@@ -8944,40 +8974,40 @@
         </is>
       </c>
       <c r="C137" s="22" t="n">
-        <v>1.772</v>
+        <v>0</v>
       </c>
       <c r="D137" s="22" t="n">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>0.706</v>
+        <v>3.729</v>
       </c>
       <c r="F137" s="22" t="n">
-        <v>3.729</v>
+        <v>-7.079</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>-7.079</v>
+        <v>5.963</v>
       </c>
       <c r="H137" s="22" t="n">
-        <v>5.963</v>
+        <v>-3.342</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>-3.342</v>
+        <v>-1.934</v>
       </c>
       <c r="J137" s="22" t="n">
-        <v>-1.934</v>
+        <v>1.55</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>1.55</v>
+        <v>2.926</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>2.926</v>
+        <v>1.265</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>1.265</v>
+        <v>0.956</v>
       </c>
       <c r="N137" s="22" t="n">
-        <v>0.956</v>
+        <v>-1.92</v>
       </c>
       <c r="T137" s="22" t="n">
         <v>0</v>
@@ -9002,40 +9032,40 @@
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>-54.53</v>
+        <v>-85.426</v>
       </c>
       <c r="D138" s="22" t="n">
-        <v>-85.426</v>
+        <v>34.22</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>34.22</v>
+        <v>-24.331</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>-24.331</v>
+        <v>-47.147</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>-47.147</v>
+        <v>10.293</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>10.293</v>
+        <v>39.584</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>39.584</v>
+        <v>41.627</v>
       </c>
       <c r="J138" s="22" t="n">
-        <v>41.627</v>
+        <v>6.136</v>
       </c>
       <c r="K138" s="22" t="n">
-        <v>6.136</v>
+        <v>-118.811</v>
       </c>
       <c r="L138" s="22" t="n">
-        <v>-118.811</v>
+        <v>-24.396</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>-24.396</v>
+        <v>3.788</v>
       </c>
       <c r="N138" s="22" t="n">
-        <v>3.788</v>
+        <v>-141.542</v>
       </c>
       <c r="T138" s="22" t="n">
         <v>1.609</v>
@@ -9060,40 +9090,40 @@
         </is>
       </c>
       <c r="C139" s="12" t="n">
-        <v>-2.688</v>
+        <v>45.059</v>
       </c>
       <c r="D139" s="12" t="n">
-        <v>45.059</v>
+        <v>387.919</v>
       </c>
       <c r="E139" s="12" t="n">
-        <v>387.919</v>
+        <v>16.377</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>16.377</v>
+        <v>620.303</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>620.303</v>
+        <v>946.456</v>
       </c>
       <c r="H139" s="12" t="n">
-        <v>946.456</v>
+        <v>1348.617</v>
       </c>
       <c r="I139" s="12" t="n">
-        <v>1348.617</v>
+        <v>-277.352</v>
       </c>
       <c r="J139" s="12" t="n">
-        <v>-277.352</v>
+        <v>-292.164</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>-292.164</v>
+        <v>-37.4</v>
       </c>
       <c r="L139" s="12" t="n">
-        <v>-37.4</v>
+        <v>746.268</v>
       </c>
       <c r="M139" s="12" t="n">
-        <v>746.268</v>
+        <v>861.361</v>
       </c>
       <c r="N139" s="12" t="n">
-        <v>861.361</v>
+        <v>914.006</v>
       </c>
       <c r="T139" s="12" t="n">
         <v>222.869</v>
@@ -9118,40 +9148,40 @@
         </is>
       </c>
       <c r="C140" s="12" t="n">
-        <v>12.142</v>
+        <v>43.44</v>
       </c>
       <c r="D140" s="12" t="n">
-        <v>43.44</v>
+        <v>381.931</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>381.931</v>
+        <v>17.389</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>17.389</v>
+        <v>621.204</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>621.204</v>
+        <v>942.4930000000001</v>
       </c>
       <c r="H140" s="12" t="n">
-        <v>942.4930000000001</v>
+        <v>1334.771</v>
       </c>
       <c r="I140" s="12" t="n">
-        <v>1334.771</v>
+        <v>-282.751</v>
       </c>
       <c r="J140" s="12" t="n">
-        <v>-282.751</v>
+        <v>-296.248</v>
       </c>
       <c r="K140" s="12" t="n">
-        <v>-296.248</v>
+        <v>-43.075</v>
       </c>
       <c r="L140" s="12" t="n">
-        <v>-43.075</v>
+        <v>742.652</v>
       </c>
       <c r="M140" s="12" t="n">
-        <v>742.652</v>
+        <v>859.715</v>
       </c>
       <c r="N140" s="12" t="n">
-        <v>859.715</v>
+        <v>906.374</v>
       </c>
       <c r="T140" s="12" t="n">
         <v>199.498</v>
@@ -9176,40 +9206,40 @@
         </is>
       </c>
       <c r="C141" s="12" t="n">
-        <v>-14.831</v>
+        <v>1.62</v>
       </c>
       <c r="D141" s="12" t="n">
-        <v>1.62</v>
+        <v>5.987</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>5.987</v>
+        <v>-1.011</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>-1.011</v>
+        <v>-0.901</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>-0.901</v>
+        <v>3.962</v>
       </c>
       <c r="H141" s="12" t="n">
-        <v>3.962</v>
+        <v>13.845</v>
       </c>
       <c r="I141" s="12" t="n">
-        <v>13.845</v>
+        <v>5.398</v>
       </c>
       <c r="J141" s="12" t="n">
-        <v>5.398</v>
+        <v>4.084</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>4.084</v>
+        <v>5.675</v>
       </c>
       <c r="L141" s="12" t="n">
-        <v>5.675</v>
+        <v>3.616</v>
       </c>
       <c r="M141" s="12" t="n">
-        <v>3.616</v>
+        <v>1.646</v>
       </c>
       <c r="N141" s="12" t="n">
-        <v>1.646</v>
+        <v>7.632</v>
       </c>
       <c r="T141" s="12" t="n">
         <v>23.371</v>
@@ -9279,62 +9309,62 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>2024.2Q</t>
+          <t>2024.3Q</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>2024.3Q</t>
+          <t>2024.4Q</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.1Q</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="N144" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="O144" s="5" t="inlineStr">
@@ -9419,13 +9449,13 @@
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="E145" s="12" t="n">
+      <c r="D145" s="12" t="n">
         <v>829.668</v>
       </c>
-      <c r="I145" s="12" t="n">
+      <c r="H145" s="12" t="n">
         <v>3979.224</v>
       </c>
-      <c r="M145" s="12" t="n">
+      <c r="L145" s="12" t="n">
         <v>244.322</v>
       </c>
       <c r="O145" s="12" t="n">
@@ -9465,13 +9495,13 @@
           <t>감가상각비</t>
         </is>
       </c>
-      <c r="E146" s="22" t="n">
+      <c r="D146" s="22" t="n">
         <v>3135.503</v>
       </c>
-      <c r="I146" s="22" t="n">
+      <c r="H146" s="22" t="n">
         <v>4768.734</v>
       </c>
-      <c r="M146" s="22" t="n">
+      <c r="L146" s="22" t="n">
         <v>7739.239</v>
       </c>
       <c r="O146" s="22" t="n">
@@ -9539,10 +9569,10 @@
           <t>영업권 상각</t>
         </is>
       </c>
-      <c r="E148" s="22" t="n">
+      <c r="D148" s="22" t="n">
         <v>2.919</v>
       </c>
-      <c r="I148" s="22" t="n">
+      <c r="H148" s="22" t="n">
         <v>0</v>
       </c>
       <c r="O148" s="22" t="n">
@@ -9579,13 +9609,13 @@
           <t>대손충당금 증감</t>
         </is>
       </c>
-      <c r="E149" s="22" t="n">
+      <c r="D149" s="22" t="n">
         <v>0.437</v>
       </c>
-      <c r="I149" s="22" t="n">
+      <c r="H149" s="22" t="n">
         <v>2.048</v>
       </c>
-      <c r="M149" s="22" t="n">
+      <c r="L149" s="22" t="n">
         <v>5.522</v>
       </c>
       <c r="O149" s="22" t="n">
@@ -9625,13 +9655,13 @@
           <t>상여충당금 증감</t>
         </is>
       </c>
-      <c r="E150" s="22" t="n">
+      <c r="D150" s="22" t="n">
         <v>60.376</v>
       </c>
-      <c r="I150" s="22" t="n">
+      <c r="H150" s="22" t="n">
         <v>212.255</v>
       </c>
-      <c r="M150" s="22" t="n">
+      <c r="L150" s="22" t="n">
         <v>108.983</v>
       </c>
       <c r="O150" s="22" t="n">
@@ -9671,13 +9701,13 @@
           <t>임원 상여충당금 증감</t>
         </is>
       </c>
-      <c r="E151" s="22" t="n">
+      <c r="D151" s="22" t="n">
         <v>-2.25</v>
       </c>
-      <c r="I151" s="22" t="n">
+      <c r="H151" s="22" t="n">
         <v>48.735</v>
       </c>
-      <c r="M151" s="22" t="n">
+      <c r="L151" s="22" t="n">
         <v>-16.435</v>
       </c>
       <c r="S151" s="22" t="n">
@@ -9705,13 +9735,13 @@
           <t>주식급여 충당금 증감</t>
         </is>
       </c>
-      <c r="E152" s="22" t="n">
+      <c r="D152" s="22" t="n">
         <v>30.662</v>
       </c>
-      <c r="I152" s="22" t="n">
+      <c r="H152" s="22" t="n">
         <v>31.186</v>
       </c>
-      <c r="M152" s="22" t="n">
+      <c r="L152" s="22" t="n">
         <v>-6.461</v>
       </c>
       <c r="T152" s="22" t="n">
@@ -9736,13 +9766,13 @@
           <t>임원 퇴직위로 충당금 증감</t>
         </is>
       </c>
-      <c r="E153" s="22" t="n">
+      <c r="D153" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I153" s="22" t="n">
+      <c r="H153" s="22" t="n">
         <v>50.638</v>
       </c>
-      <c r="M153" s="22" t="n">
+      <c r="L153" s="22" t="n">
         <v>20.141</v>
       </c>
       <c r="V153" s="22" t="n">
@@ -9761,10 +9791,10 @@
           <t>퇴직급여부채 증감</t>
         </is>
       </c>
-      <c r="I154" s="22" t="n">
+      <c r="H154" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="M154" s="22" t="n">
+      <c r="L154" s="22" t="n">
         <v>3.05</v>
       </c>
       <c r="W154" s="22" t="n">
@@ -9780,13 +9810,13 @@
           <t>이자·배당금 수익</t>
         </is>
       </c>
-      <c r="E155" s="22" t="n">
+      <c r="D155" s="22" t="n">
         <v>-5.173</v>
       </c>
-      <c r="I155" s="22" t="n">
+      <c r="H155" s="22" t="n">
         <v>-21.614</v>
       </c>
-      <c r="M155" s="22" t="n">
+      <c r="L155" s="22" t="n">
         <v>-52.094</v>
       </c>
       <c r="O155" s="22" t="n">
@@ -9826,13 +9856,13 @@
           <t>이자비용</t>
         </is>
       </c>
-      <c r="E156" s="22" t="n">
+      <c r="D156" s="22" t="n">
         <v>173.679</v>
       </c>
-      <c r="I156" s="22" t="n">
+      <c r="H156" s="22" t="n">
         <v>255.562</v>
       </c>
-      <c r="M156" s="22" t="n">
+      <c r="L156" s="22" t="n">
         <v>538.822</v>
       </c>
       <c r="O156" s="22" t="n">
@@ -9872,13 +9902,13 @@
           <t>주식교부비</t>
         </is>
       </c>
-      <c r="E157" s="22" t="n">
+      <c r="D157" s="22" t="n">
         <v>1.459</v>
       </c>
-      <c r="I157" s="22" t="n">
+      <c r="H157" s="22" t="n">
         <v>109.528</v>
       </c>
-      <c r="M157" s="22" t="n">
+      <c r="L157" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V157" s="22" t="n">
@@ -9897,13 +9927,13 @@
           <t>투자사업조합 운용 손익(△는 이익)</t>
         </is>
       </c>
-      <c r="E158" s="22" t="n">
+      <c r="D158" s="22" t="n">
         <v>4.287</v>
       </c>
-      <c r="I158" s="22" t="n">
+      <c r="H158" s="22" t="n">
         <v>-14.746</v>
       </c>
-      <c r="M158" s="22" t="n">
+      <c r="L158" s="22" t="n">
         <v>8.773999999999999</v>
       </c>
       <c r="O158" s="22" t="n">
@@ -9943,13 +9973,13 @@
           <t>고정자산 제각손실</t>
         </is>
       </c>
-      <c r="E159" s="22" t="n">
+      <c r="D159" s="22" t="n">
         <v>1.483</v>
       </c>
-      <c r="I159" s="22" t="n">
+      <c r="H159" s="22" t="n">
         <v>52.012</v>
       </c>
-      <c r="M159" s="22" t="n">
+      <c r="L159" s="22" t="n">
         <v>14.713</v>
       </c>
       <c r="O159" s="22" t="n">
@@ -9986,16 +10016,16 @@
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>Income By Government Subsidies Ope CF</t>
-        </is>
-      </c>
-      <c r="E160" s="22" t="n">
+          <t>국고보조금 등 수입</t>
+        </is>
+      </c>
+      <c r="D160" s="22" t="n">
         <v>-1624.819</v>
       </c>
-      <c r="I160" s="22" t="n">
+      <c r="H160" s="22" t="n">
         <v>-6119.744</v>
       </c>
-      <c r="M160" s="22" t="n">
+      <c r="L160" s="22" t="n">
         <v>-14311.693</v>
       </c>
       <c r="P160" s="22" t="n">
@@ -10029,13 +10059,13 @@
           <t>고정자산 압축손실</t>
         </is>
       </c>
-      <c r="E161" s="22" t="n">
+      <c r="D161" s="22" t="n">
         <v>1624.819</v>
       </c>
-      <c r="I161" s="22" t="n">
+      <c r="H161" s="22" t="n">
         <v>6119.744</v>
       </c>
-      <c r="M161" s="22" t="n">
+      <c r="L161" s="22" t="n">
         <v>14311.693</v>
       </c>
       <c r="P161" s="22" t="n">
@@ -10069,13 +10099,13 @@
           <t>고정자산 매각손익</t>
         </is>
       </c>
-      <c r="E162" s="22" t="n">
+      <c r="D162" s="22" t="n">
         <v>-5.868</v>
       </c>
-      <c r="I162" s="22" t="n">
+      <c r="H162" s="22" t="n">
         <v>-0.806</v>
       </c>
-      <c r="M162" s="22" t="n">
+      <c r="L162" s="22" t="n">
         <v>2.036</v>
       </c>
       <c r="O162" s="22" t="n">
@@ -10173,7 +10203,7 @@
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>Settlement Package Ope CF</t>
+          <t>화해금</t>
         </is>
       </c>
       <c r="R167" s="22" t="n">
@@ -10192,13 +10222,13 @@
           <t>투자유가증권 매각손익</t>
         </is>
       </c>
-      <c r="E168" s="22" t="n">
+      <c r="D168" s="22" t="n">
         <v>-61.318</v>
       </c>
-      <c r="I168" s="22" t="n">
+      <c r="H168" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M168" s="22" t="n">
+      <c r="L168" s="22" t="n">
         <v>-155.595</v>
       </c>
       <c r="O168" s="22" t="n">
@@ -10226,13 +10256,13 @@
           <t>투자유가증권 평가손익</t>
         </is>
       </c>
-      <c r="E169" s="22" t="n">
+      <c r="D169" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I169" s="22" t="n">
+      <c r="H169" s="22" t="n">
         <v>29.999</v>
       </c>
-      <c r="M169" s="22" t="n">
+      <c r="L169" s="22" t="n">
         <v>0</v>
       </c>
       <c r="O169" s="22" t="n">
@@ -10266,13 +10296,13 @@
           <t>미수 소비세 증감</t>
         </is>
       </c>
-      <c r="E170" s="22" t="n">
+      <c r="D170" s="22" t="n">
         <v>-356.745</v>
       </c>
-      <c r="I170" s="22" t="n">
+      <c r="H170" s="22" t="n">
         <v>-1274.235</v>
       </c>
-      <c r="M170" s="22" t="n">
+      <c r="L170" s="22" t="n">
         <v>-544.572</v>
       </c>
       <c r="O170" s="22" t="n">
@@ -10312,13 +10342,13 @@
           <t>미지급 소비세 증감</t>
         </is>
       </c>
-      <c r="E171" s="22" t="n">
+      <c r="D171" s="22" t="n">
         <v>-131.375</v>
       </c>
-      <c r="I171" s="22" t="n">
+      <c r="H171" s="22" t="n">
         <v>-8.226000000000001</v>
       </c>
-      <c r="M171" s="22" t="n">
+      <c r="L171" s="22" t="n">
         <v>0.9350000000000001</v>
       </c>
       <c r="O171" s="22" t="n">
@@ -10358,13 +10388,13 @@
           <t>매출채권 증감</t>
         </is>
       </c>
-      <c r="E172" s="22" t="n">
+      <c r="D172" s="22" t="n">
         <v>-848.745</v>
       </c>
-      <c r="I172" s="22" t="n">
+      <c r="H172" s="22" t="n">
         <v>-4336.737</v>
       </c>
-      <c r="M172" s="22" t="n">
+      <c r="L172" s="22" t="n">
         <v>2764.99</v>
       </c>
       <c r="O172" s="22" t="n">
@@ -10404,13 +10434,13 @@
           <t>선수금 증감</t>
         </is>
       </c>
-      <c r="E173" s="22" t="n">
+      <c r="D173" s="22" t="n">
         <v>114.746</v>
       </c>
-      <c r="I173" s="22" t="n">
+      <c r="H173" s="22" t="n">
         <v>1109.342</v>
       </c>
-      <c r="M173" s="22" t="n">
+      <c r="L173" s="22" t="n">
         <v>2549.518</v>
       </c>
       <c r="O173" s="22" t="n">
@@ -10450,13 +10480,13 @@
           <t>재고자산 증감</t>
         </is>
       </c>
-      <c r="E174" s="22" t="n">
+      <c r="D174" s="22" t="n">
         <v>8.167</v>
       </c>
-      <c r="I174" s="22" t="n">
+      <c r="H174" s="22" t="n">
         <v>-41.905</v>
       </c>
-      <c r="M174" s="22" t="n">
+      <c r="L174" s="22" t="n">
         <v>-489.31</v>
       </c>
       <c r="O174" s="22" t="n">
@@ -10496,13 +10526,13 @@
           <t>매입채무 증감</t>
         </is>
       </c>
-      <c r="E175" s="22" t="n">
+      <c r="D175" s="22" t="n">
         <v>-288.711</v>
       </c>
-      <c r="I175" s="22" t="n">
+      <c r="H175" s="22" t="n">
         <v>1047.14</v>
       </c>
-      <c r="M175" s="22" t="n">
+      <c r="L175" s="22" t="n">
         <v>-535.282</v>
       </c>
       <c r="O175" s="22" t="n">
@@ -10542,13 +10572,13 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="E176" s="22" t="n">
+      <c r="D176" s="22" t="n">
         <v>694.696</v>
       </c>
-      <c r="I176" s="22" t="n">
+      <c r="H176" s="22" t="n">
         <v>302.101</v>
       </c>
-      <c r="M176" s="22" t="n">
+      <c r="L176" s="22" t="n">
         <v>-4141.055</v>
       </c>
       <c r="O176" s="22" t="n">
@@ -10588,13 +10618,13 @@
           <t>소계</t>
         </is>
       </c>
-      <c r="E177" s="22" t="n">
+      <c r="D177" s="22" t="n">
         <v>3357.899</v>
       </c>
-      <c r="I177" s="22" t="n">
+      <c r="H177" s="22" t="n">
         <v>6330.24</v>
       </c>
-      <c r="M177" s="22" t="n">
+      <c r="L177" s="22" t="n">
         <v>8060.243</v>
       </c>
       <c r="O177" s="22" t="n">
@@ -10634,13 +10664,13 @@
           <t>이자·배당금 수취</t>
         </is>
       </c>
-      <c r="E178" s="22" t="n">
+      <c r="D178" s="22" t="n">
         <v>5.084</v>
       </c>
-      <c r="I178" s="22" t="n">
+      <c r="H178" s="22" t="n">
         <v>21.078</v>
       </c>
-      <c r="M178" s="22" t="n">
+      <c r="L178" s="22" t="n">
         <v>39.093</v>
       </c>
       <c r="O178" s="22" t="n">
@@ -10680,13 +10710,13 @@
           <t>이자 지급</t>
         </is>
       </c>
-      <c r="E179" s="22" t="n">
+      <c r="D179" s="22" t="n">
         <v>-173.507</v>
       </c>
-      <c r="I179" s="22" t="n">
+      <c r="H179" s="22" t="n">
         <v>-259.091</v>
       </c>
-      <c r="M179" s="22" t="n">
+      <c r="L179" s="22" t="n">
         <v>-548.114</v>
       </c>
       <c r="O179" s="22" t="n">
@@ -10726,13 +10756,13 @@
           <t>법인세 납부·환급</t>
         </is>
       </c>
-      <c r="E180" s="22" t="n">
+      <c r="D180" s="22" t="n">
         <v>-305.342</v>
       </c>
-      <c r="I180" s="22" t="n">
+      <c r="H180" s="22" t="n">
         <v>-304.663</v>
       </c>
-      <c r="M180" s="22" t="n">
+      <c r="L180" s="22" t="n">
         <v>-1327.646</v>
       </c>
       <c r="O180" s="22" t="n">
@@ -10785,7 +10815,7 @@
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>Penalty Income Received Ope CF</t>
+          <t>위약금 수령액</t>
         </is>
       </c>
       <c r="R182" s="22" t="n">
@@ -10817,7 +10847,7 @@
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>Settlement Package Paid Ope CF</t>
+          <t>화해금 지급액</t>
         </is>
       </c>
       <c r="R184" s="22" t="n">
@@ -10836,13 +10866,13 @@
           <t>영업활동 현금흐름</t>
         </is>
       </c>
-      <c r="E185" s="12" t="n">
+      <c r="D185" s="12" t="n">
         <v>2884.133</v>
       </c>
-      <c r="I185" s="12" t="n">
+      <c r="H185" s="12" t="n">
         <v>5787.563</v>
       </c>
-      <c r="M185" s="12" t="n">
+      <c r="L185" s="12" t="n">
         <v>6223.575</v>
       </c>
       <c r="O185" s="12" t="n">
@@ -10882,13 +10912,13 @@
           <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
-      <c r="E186" s="22" t="n">
+      <c r="D186" s="22" t="n">
         <v>-3481.799</v>
       </c>
-      <c r="I186" s="22" t="n">
+      <c r="H186" s="22" t="n">
         <v>-17657.769</v>
       </c>
-      <c r="M186" s="22" t="n">
+      <c r="L186" s="22" t="n">
         <v>-36336.695</v>
       </c>
       <c r="O186" s="22" t="n">
@@ -10928,10 +10958,10 @@
           <t>유형자산 매각</t>
         </is>
       </c>
-      <c r="I187" s="22" t="n">
+      <c r="H187" s="22" t="n">
         <v>0.806</v>
       </c>
-      <c r="M187" s="22" t="n">
+      <c r="L187" s="22" t="n">
         <v>470.776</v>
       </c>
       <c r="O187" s="22" t="n">
@@ -10953,13 +10983,13 @@
           <t>무형자산 취득</t>
         </is>
       </c>
-      <c r="E188" s="22" t="n">
+      <c r="D188" s="22" t="n">
         <v>-136.977</v>
       </c>
-      <c r="I188" s="22" t="n">
+      <c r="H188" s="22" t="n">
         <v>-895.994</v>
       </c>
-      <c r="M188" s="22" t="n">
+      <c r="L188" s="22" t="n">
         <v>-1106.251</v>
       </c>
       <c r="O188" s="22" t="n">
@@ -10996,16 +11026,16 @@
     <row r="189">
       <c r="A189" s="20" t="inlineStr">
         <is>
-          <t>Income By Government Subsidies Inv CF</t>
-        </is>
-      </c>
-      <c r="E189" s="22" t="n">
+          <t>국고보조금 등 수입</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="n">
         <v>1634.371</v>
       </c>
-      <c r="I189" s="22" t="n">
+      <c r="H189" s="22" t="n">
         <v>10299.156</v>
       </c>
-      <c r="M189" s="22" t="n">
+      <c r="L189" s="22" t="n">
         <v>12346.456</v>
       </c>
       <c r="P189" s="22" t="n">
@@ -11058,13 +11088,13 @@
           <t>투자유가증권 취득</t>
         </is>
       </c>
-      <c r="E191" s="22" t="n">
+      <c r="D191" s="22" t="n">
         <v>-21</v>
       </c>
-      <c r="I191" s="22" t="n">
+      <c r="H191" s="22" t="n">
         <v>-11</v>
       </c>
-      <c r="M191" s="22" t="n">
+      <c r="L191" s="22" t="n">
         <v>-217.931</v>
       </c>
       <c r="O191" s="22" t="n">
@@ -11136,10 +11166,10 @@
           <t>투자유가증권 매각</t>
         </is>
       </c>
-      <c r="I194" s="22" t="n">
+      <c r="H194" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M194" s="22" t="n">
+      <c r="L194" s="22" t="n">
         <v>187.185</v>
       </c>
       <c r="O194" s="22" t="n">
@@ -11161,13 +11191,13 @@
           <t>임차보증금·보증금 납입</t>
         </is>
       </c>
-      <c r="E195" s="22" t="n">
+      <c r="D195" s="22" t="n">
         <v>-94.59699999999999</v>
       </c>
-      <c r="I195" s="22" t="n">
+      <c r="H195" s="22" t="n">
         <v>-64.92100000000001</v>
       </c>
-      <c r="M195" s="22" t="n">
+      <c r="L195" s="22" t="n">
         <v>-0.732</v>
       </c>
       <c r="O195" s="22" t="n">
@@ -11207,13 +11237,13 @@
           <t>임차보증금·보증금 회수</t>
         </is>
       </c>
-      <c r="E196" s="22" t="n">
+      <c r="D196" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I196" s="22" t="n">
+      <c r="H196" s="22" t="n">
         <v>0.201</v>
       </c>
-      <c r="M196" s="22" t="n">
+      <c r="L196" s="22" t="n">
         <v>6.374</v>
       </c>
       <c r="O196" s="22" t="n">
@@ -11285,13 +11315,13 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="E199" s="22" t="n">
+      <c r="D199" s="22" t="n">
         <v>74.364</v>
       </c>
-      <c r="I199" s="22" t="n">
+      <c r="H199" s="22" t="n">
         <v>6.408</v>
       </c>
-      <c r="M199" s="22" t="n">
+      <c r="L199" s="22" t="n">
         <v>7.716</v>
       </c>
       <c r="O199" s="22" t="n">
@@ -11331,13 +11361,13 @@
           <t>투자활동 현금흐름</t>
         </is>
       </c>
-      <c r="E200" s="12" t="n">
+      <c r="D200" s="12" t="n">
         <v>-2025.638</v>
       </c>
-      <c r="I200" s="12" t="n">
+      <c r="H200" s="12" t="n">
         <v>-8323.112999999999</v>
       </c>
-      <c r="M200" s="12" t="n">
+      <c r="L200" s="12" t="n">
         <v>-24643.1</v>
       </c>
       <c r="O200" s="12" t="n">
@@ -11377,13 +11407,13 @@
           <t>단기차입</t>
         </is>
       </c>
-      <c r="E201" s="22" t="n">
+      <c r="D201" s="22" t="n">
         <v>1053</v>
       </c>
-      <c r="I201" s="22" t="n">
+      <c r="H201" s="22" t="n">
         <v>20067</v>
       </c>
-      <c r="M201" s="22" t="n">
+      <c r="L201" s="22" t="n">
         <v>17087</v>
       </c>
       <c r="O201" s="22" t="n">
@@ -11423,13 +11453,13 @@
           <t>단기차입금 상환</t>
         </is>
       </c>
-      <c r="E202" s="22" t="n">
+      <c r="D202" s="22" t="n">
         <v>-955.332</v>
       </c>
-      <c r="I202" s="22" t="n">
+      <c r="H202" s="22" t="n">
         <v>-11223</v>
       </c>
-      <c r="M202" s="22" t="n">
+      <c r="L202" s="22" t="n">
         <v>-15661.668</v>
       </c>
       <c r="O202" s="22" t="n">
@@ -11469,13 +11499,13 @@
           <t>장기차입</t>
         </is>
       </c>
-      <c r="E203" s="22" t="n">
+      <c r="D203" s="22" t="n">
         <v>1664</v>
       </c>
-      <c r="I203" s="22" t="n">
+      <c r="H203" s="22" t="n">
         <v>5725</v>
       </c>
-      <c r="M203" s="22" t="n">
+      <c r="L203" s="22" t="n">
         <v>8110</v>
       </c>
       <c r="O203" s="22" t="n">
@@ -11515,13 +11545,13 @@
           <t>장기차입금 상환</t>
         </is>
       </c>
-      <c r="E204" s="22" t="n">
+      <c r="D204" s="22" t="n">
         <v>-817.818</v>
       </c>
-      <c r="I204" s="22" t="n">
+      <c r="H204" s="22" t="n">
         <v>-4278.739</v>
       </c>
-      <c r="M204" s="22" t="n">
+      <c r="L204" s="22" t="n">
         <v>-3339.651</v>
       </c>
       <c r="O204" s="22" t="n">
@@ -11561,13 +11591,13 @@
           <t>주식 발행</t>
         </is>
       </c>
-      <c r="E205" s="22" t="n">
+      <c r="D205" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I205" s="22" t="n">
+      <c r="H205" s="22" t="n">
         <v>17942.964</v>
       </c>
-      <c r="M205" s="22" t="n">
+      <c r="L205" s="22" t="n">
         <v>0</v>
       </c>
       <c r="O205" s="22" t="n">
@@ -11592,10 +11622,10 @@
           <t>비지배주주 납입</t>
         </is>
       </c>
-      <c r="E206" s="22" t="n">
+      <c r="D206" s="22" t="n">
         <v>129.041</v>
       </c>
-      <c r="I206" s="22" t="n">
+      <c r="H206" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U206" s="22" t="n">
@@ -11614,13 +11644,13 @@
           <t>리스부채 상환</t>
         </is>
       </c>
-      <c r="E207" s="22" t="n">
+      <c r="D207" s="22" t="n">
         <v>-1566.762</v>
       </c>
-      <c r="I207" s="22" t="n">
+      <c r="H207" s="22" t="n">
         <v>-1836.513</v>
       </c>
-      <c r="M207" s="22" t="n">
+      <c r="L207" s="22" t="n">
         <v>-2649.97</v>
       </c>
       <c r="O207" s="22" t="n">
@@ -11660,13 +11690,13 @@
           <t>세일앤리스백 수입</t>
         </is>
       </c>
-      <c r="E208" s="22" t="n">
+      <c r="D208" s="22" t="n">
         <v>217.272</v>
       </c>
-      <c r="I208" s="22" t="n">
+      <c r="H208" s="22" t="n">
         <v>512.228</v>
       </c>
-      <c r="M208" s="22" t="n">
+      <c r="L208" s="22" t="n">
         <v>1242.652</v>
       </c>
       <c r="O208" s="22" t="n">
@@ -11703,16 +11733,16 @@
     <row r="209">
       <c r="A209" s="20" t="inlineStr">
         <is>
-          <t>Repayments Of Installment Payables Fin CF</t>
-        </is>
-      </c>
-      <c r="E209" s="22" t="n">
+          <t>할부채무 상환 지출</t>
+        </is>
+      </c>
+      <c r="D209" s="22" t="n">
         <v>-7.75</v>
       </c>
-      <c r="I209" s="22" t="n">
+      <c r="H209" s="22" t="n">
         <v>-21.232</v>
       </c>
-      <c r="M209" s="22" t="n">
+      <c r="L209" s="22" t="n">
         <v>-393.305</v>
       </c>
       <c r="O209" s="22" t="n">
@@ -11752,13 +11782,13 @@
           <t>자기주식 취득</t>
         </is>
       </c>
-      <c r="E210" s="22" t="n">
+      <c r="D210" s="22" t="n">
         <v>-1.383</v>
       </c>
-      <c r="I210" s="22" t="n">
+      <c r="H210" s="22" t="n">
         <v>-0.317</v>
       </c>
-      <c r="M210" s="22" t="n">
+      <c r="L210" s="22" t="n">
         <v>-0.031</v>
       </c>
       <c r="P210" s="22" t="n">
@@ -11792,10 +11822,10 @@
           <t>자기주식 매각</t>
         </is>
       </c>
-      <c r="I211" s="22" t="n">
+      <c r="H211" s="22" t="n">
         <v>0.963</v>
       </c>
-      <c r="M211" s="22" t="n">
+      <c r="L211" s="22" t="n">
         <v>85.861</v>
       </c>
       <c r="W211" s="22" t="n">
@@ -11811,13 +11841,13 @@
           <t>배당금 지급</t>
         </is>
       </c>
-      <c r="E212" s="22" t="n">
+      <c r="D212" s="22" t="n">
         <v>-125.621</v>
       </c>
-      <c r="I212" s="22" t="n">
+      <c r="H212" s="22" t="n">
         <v>-124.699</v>
       </c>
-      <c r="M212" s="22" t="n">
+      <c r="L212" s="22" t="n">
         <v>-161.619</v>
       </c>
       <c r="O212" s="22" t="n">
@@ -11873,10 +11903,10 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="E214" s="22" t="n">
+      <c r="D214" s="22" t="n">
         <v>0.763</v>
       </c>
-      <c r="I214" s="22" t="n">
+      <c r="H214" s="22" t="n">
         <v>0.963</v>
       </c>
       <c r="U214" s="22" t="n">
@@ -11895,13 +11925,13 @@
           <t>재무활동 현금흐름</t>
         </is>
       </c>
-      <c r="E215" s="12" t="n">
+      <c r="D215" s="12" t="n">
         <v>-410.59</v>
       </c>
-      <c r="I215" s="12" t="n">
+      <c r="H215" s="12" t="n">
         <v>26763.654</v>
       </c>
-      <c r="M215" s="12" t="n">
+      <c r="L215" s="12" t="n">
         <v>4319.267</v>
       </c>
       <c r="O215" s="12" t="n">
@@ -11941,13 +11971,13 @@
           <t>현금성자산 환산차이</t>
         </is>
       </c>
-      <c r="E216" s="22" t="n">
+      <c r="D216" s="22" t="n">
         <v>-0.726</v>
       </c>
-      <c r="I216" s="22" t="n">
+      <c r="H216" s="22" t="n">
         <v>-2.017</v>
       </c>
-      <c r="M216" s="22" t="n">
+      <c r="L216" s="22" t="n">
         <v>5.791</v>
       </c>
       <c r="O216" s="22" t="n">
@@ -11987,13 +12017,13 @@
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E217" s="22" t="n">
+      <c r="D217" s="22" t="n">
         <v>447.177</v>
       </c>
-      <c r="I217" s="22" t="n">
+      <c r="H217" s="22" t="n">
         <v>24226.087</v>
       </c>
-      <c r="M217" s="22" t="n">
+      <c r="L217" s="22" t="n">
         <v>-14094.466</v>
       </c>
       <c r="O217" s="22" t="n">
@@ -12033,13 +12063,13 @@
           <t>연결범위 변경에 따른 현금성자산 증감</t>
         </is>
       </c>
-      <c r="E218" s="22" t="n">
+      <c r="D218" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I218" s="22" t="n">
+      <c r="H218" s="22" t="n">
         <v>5.329</v>
       </c>
-      <c r="M218" s="22" t="n">
+      <c r="L218" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V218" s="22" t="n">
@@ -12064,7 +12094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12084,7 +12114,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3778 재무상태표</t>
+          <t>사쿠라인터넷 재무상태표</t>
         </is>
       </c>
     </row>
@@ -12113,27 +12143,27 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -12188,19 +12218,19 @@
       </c>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="11" t="n">
-        <v>33697.89</v>
+        <v>19694.627</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>19694.627</v>
+        <v>22089.296</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>22089.296</v>
+        <v>26255.316</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>26255.316</v>
+        <v>29074.46</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>29074.46</v>
+        <v>29650.725</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>9776.159</v>
@@ -12226,19 +12256,19 @@
       </c>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="21" t="n">
-        <v>24254.781</v>
+        <v>10780.435</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>10780.435</v>
+        <v>12242.841</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>12242.841</v>
+        <v>15391.081</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>15391.081</v>
+        <v>17271.165</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>17271.165</v>
+        <v>19424.963</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>5452.592</v>
@@ -12282,19 +12312,19 @@
       </c>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="21" t="n">
-        <v>2838.646</v>
+        <v>2737.055</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>2737.055</v>
+        <v>3209.464</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>3209.464</v>
+        <v>4813.239</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>4813.239</v>
+        <v>4876.587</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>4876.587</v>
+        <v>4991.425</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>2700.19</v>
@@ -12320,19 +12350,19 @@
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="21" t="n">
-        <v>517.375</v>
+        <v>441.675</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>441.675</v>
+        <v>1022.395</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>1022.395</v>
+        <v>1021.882</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>1021.882</v>
+        <v>505.42</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>505.42</v>
+        <v>531.253</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>702.027</v>
@@ -12410,19 +12440,19 @@
       </c>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="11" t="n">
-        <v>47303.133</v>
+        <v>60565.398</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>60565.398</v>
+        <v>60529.567</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>60529.567</v>
+        <v>56195.76</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>56195.76</v>
+        <v>58471.666</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>58471.666</v>
+        <v>58325.547</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>18620.168</v>
@@ -12448,19 +12478,19 @@
       </c>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="21" t="n">
-        <v>37880.622</v>
+        <v>51190.946</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>51190.946</v>
+        <v>51214.577</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>51214.577</v>
+        <v>46722.502</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>46722.502</v>
+        <v>48894.327</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>48894.327</v>
+        <v>48297.121</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>15725.557</v>
@@ -12486,19 +12516,19 @@
       </c>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="21" t="n">
-        <v>1403.956</v>
+        <v>1565.479</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>1565.479</v>
+        <v>1831.062</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>1831.062</v>
+        <v>2018.177</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>2018.177</v>
+        <v>2109.37</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>2109.37</v>
+        <v>1963.839</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>426.342</v>
@@ -12594,19 +12624,19 @@
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="11" t="n">
-        <v>81001.024</v>
+        <v>80260.02499999999</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>80260.02499999999</v>
+        <v>82618.864</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>82618.864</v>
+        <v>82451.076</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>82451.076</v>
+        <v>87546.12699999999</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>87546.12699999999</v>
+        <v>87976.272</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>28396.327</v>
@@ -12650,19 +12680,19 @@
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="11" t="n">
-        <v>37750.942</v>
+        <v>34194.632</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>34194.632</v>
+        <v>34799.76</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>34799.76</v>
+        <v>33854.933</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>33854.933</v>
+        <v>36915.473</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>36915.473</v>
+        <v>32536.822</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>11309.298</v>
@@ -12688,19 +12718,19 @@
       </c>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="21" t="n">
-        <v>607.006</v>
+        <v>660.9299999999999</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>660.9299999999999</v>
+        <v>816.725</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>816.725</v>
+        <v>1245.523</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>1245.523</v>
+        <v>554.71</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>554.71</v>
+        <v>620.46</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>1613.404</v>
@@ -12726,19 +12756,19 @@
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="21" t="n">
-        <v>6741.667</v>
+        <v>10675.668</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>10675.668</v>
+        <v>8255</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>8255</v>
+        <v>10687</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>10687</v>
+        <v>14742</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>14742</v>
+        <v>8136</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>1451</v>
@@ -12764,19 +12794,19 @@
       </c>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="21" t="n">
-        <v>2668.38</v>
+        <v>3657.66</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>3657.66</v>
+        <v>5323.383</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>5323.383</v>
+        <v>4796.832</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>4796.832</v>
+        <v>4242.518</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>4242.518</v>
+        <v>5338.588</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>918.082</v>
@@ -12854,19 +12884,19 @@
       </c>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="n">
-        <v>13430.972</v>
+        <v>16453.494</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>16453.494</v>
+        <v>18244.036</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>18244.036</v>
+        <v>18266.988</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>18266.988</v>
+        <v>19641.134</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>19641.134</v>
+        <v>23470.535</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>8637.099</v>
@@ -12892,19 +12922,19 @@
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="21" t="n">
-        <v>2542.612</v>
+        <v>4917.091</v>
       </c>
       <c r="D24" s="22" t="n">
-        <v>4917.091</v>
+        <v>6553.073</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>6553.073</v>
+        <v>5777.396</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>5777.396</v>
+        <v>5067.428</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>5067.428</v>
+        <v>6448.828</v>
       </c>
       <c r="H24" s="21" t="n">
         <v>3475.436</v>
@@ -13000,19 +13030,19 @@
       </c>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="n">
-        <v>51181.915</v>
+        <v>50648.126</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>50648.126</v>
+        <v>53043.797</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>53043.797</v>
+        <v>52121.922</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>52121.922</v>
+        <v>56556.608</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>56556.608</v>
+        <v>56007.357</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>19946.398</v>
@@ -13160,19 +13190,19 @@
       </c>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="n">
-        <v>29611.608</v>
+        <v>29400.315</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>29400.315</v>
+        <v>29357.808</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>29357.808</v>
+        <v>30101.279</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>30101.279</v>
+        <v>30759.997</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>30759.997</v>
+        <v>31738.461</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>8317.704</v>
@@ -13236,19 +13266,19 @@
       </c>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="21" t="n">
-        <v>8692.218999999999</v>
+        <v>8389.834999999999</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>8389.834999999999</v>
+        <v>8465.573</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>8465.573</v>
+        <v>9232.621999999999</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>9232.621999999999</v>
+        <v>9887.088</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>9887.088</v>
+        <v>10935.134</v>
       </c>
       <c r="H33" s="21" t="n">
         <v>5289.923</v>
@@ -13274,19 +13304,19 @@
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="21" t="n">
-        <v>207.501</v>
+        <v>211.584</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>211.584</v>
+        <v>217.259</v>
       </c>
       <c r="E34" s="22" t="n">
-        <v>217.259</v>
+        <v>227.875</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>227.875</v>
+        <v>229.521</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>229.521</v>
+        <v>230.454</v>
       </c>
       <c r="H34" s="21" t="n">
         <v>132.225</v>
@@ -13312,19 +13342,19 @@
       </c>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="n">
-        <v>29819.109</v>
+        <v>29611.899</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>29611.899</v>
+        <v>29575.067</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>29575.067</v>
+        <v>30329.154</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>30329.154</v>
+        <v>30989.518</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>30989.518</v>
+        <v>31968.915</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>8449.929</v>
@@ -13373,10 +13403,10 @@
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n">
+      <c r="E37" s="12" t="n">
         <v>6223.575</v>
       </c>
+      <c r="F37" s="12" t="n"/>
       <c r="G37" s="12" t="n"/>
       <c r="H37" s="11" t="n">
         <v>3957.746</v>
@@ -13407,10 +13437,10 @@
       </c>
       <c r="C38" s="21" t="n"/>
       <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n">
+      <c r="E38" s="22" t="n">
         <v>37442.946</v>
       </c>
+      <c r="F38" s="22" t="n"/>
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="21" t="n">
         <v>1426.077</v>
@@ -13489,10 +13519,10 @@
       </c>
       <c r="C40" s="21" t="n"/>
       <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
-      <c r="F40" s="22" t="n">
+      <c r="E40" s="22" t="n">
         <v>161.619</v>
       </c>
+      <c r="F40" s="22" t="n"/>
       <c r="G40" s="22" t="n"/>
       <c r="H40" s="21" t="n">
         <v>108.912</v>
@@ -14783,27 +14813,27 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2026.1Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -14839,19 +14869,19 @@
         </is>
       </c>
       <c r="C71" s="22" t="n">
-        <v>24254.781</v>
+        <v>10780.435</v>
       </c>
       <c r="D71" s="22" t="n">
-        <v>10780.435</v>
+        <v>12242.841</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>12242.841</v>
+        <v>15391.081</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>15391.081</v>
+        <v>17271.165</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>17271.165</v>
+        <v>19424.963</v>
       </c>
       <c r="H71" s="22" t="n">
         <v>5452.592</v>
@@ -14889,19 +14919,19 @@
         </is>
       </c>
       <c r="C73" s="22" t="n">
-        <v>2838.646</v>
+        <v>2737.055</v>
       </c>
       <c r="D73" s="22" t="n">
-        <v>2737.055</v>
+        <v>3209.464</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>3209.464</v>
+        <v>4813.239</v>
       </c>
       <c r="F73" s="22" t="n">
-        <v>4813.239</v>
+        <v>4876.587</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>4876.587</v>
+        <v>4991.425</v>
       </c>
       <c r="I73" s="22" t="n">
         <v>2392.419</v>
@@ -14923,19 +14953,19 @@
         </is>
       </c>
       <c r="C74" s="22" t="n">
-        <v>30.244</v>
+        <v>34.058</v>
       </c>
       <c r="D74" s="22" t="n">
-        <v>34.058</v>
+        <v>461.792</v>
       </c>
       <c r="E74" s="22" t="n">
-        <v>461.792</v>
+        <v>408.039</v>
       </c>
       <c r="F74" s="22" t="n">
-        <v>408.039</v>
+        <v>16.057</v>
       </c>
       <c r="G74" s="22" t="n">
-        <v>16.057</v>
+        <v>44.192</v>
       </c>
       <c r="H74" s="22" t="n">
         <v>17.179</v>
@@ -14960,19 +14990,19 @@
         </is>
       </c>
       <c r="C75" s="22" t="n">
-        <v>18.31</v>
+        <v>5.557</v>
       </c>
       <c r="D75" s="22" t="n">
-        <v>5.557</v>
+        <v>37.509</v>
       </c>
       <c r="E75" s="22" t="n">
-        <v>37.509</v>
+        <v>59.243</v>
       </c>
       <c r="F75" s="22" t="n">
-        <v>59.243</v>
+        <v>31.401</v>
       </c>
       <c r="G75" s="22" t="n">
-        <v>31.401</v>
+        <v>31.145</v>
       </c>
       <c r="H75" s="22" t="n">
         <v>32.455</v>
@@ -14997,19 +15027,19 @@
         </is>
       </c>
       <c r="C76" s="22" t="n">
-        <v>468.821</v>
+        <v>402.06</v>
       </c>
       <c r="D76" s="22" t="n">
-        <v>402.06</v>
+        <v>523.0940000000001</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>523.0940000000001</v>
+        <v>554.6</v>
       </c>
       <c r="F76" s="22" t="n">
-        <v>554.6</v>
+        <v>457.962</v>
       </c>
       <c r="G76" s="22" t="n">
-        <v>457.962</v>
+        <v>455.916</v>
       </c>
       <c r="H76" s="22" t="n">
         <v>652.393</v>
@@ -15034,19 +15064,19 @@
         </is>
       </c>
       <c r="C77" s="22" t="n">
-        <v>6105.545</v>
+        <v>5753.726</v>
       </c>
       <c r="D77" s="22" t="n">
-        <v>5753.726</v>
+        <v>5636.488</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>5636.488</v>
+        <v>5051.385</v>
       </c>
       <c r="F77" s="22" t="n">
-        <v>5051.385</v>
+        <v>6443.651</v>
       </c>
       <c r="G77" s="22" t="n">
-        <v>6443.651</v>
+        <v>4724.907</v>
       </c>
       <c r="H77" s="22" t="n">
         <v>934.809</v>
@@ -15071,19 +15101,19 @@
         </is>
       </c>
       <c r="C78" s="22" t="n">
-        <v>-18.46</v>
+        <v>-18.267</v>
       </c>
       <c r="D78" s="22" t="n">
-        <v>-18.267</v>
+        <v>-21.892</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>-21.892</v>
+        <v>-22.274</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>-22.274</v>
+        <v>-22.365</v>
       </c>
       <c r="G78" s="22" t="n">
-        <v>-22.365</v>
+        <v>-21.826</v>
       </c>
       <c r="H78" s="22" t="n">
         <v>-13.46</v>
@@ -15108,19 +15138,19 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>33697.89</v>
+        <v>19694.627</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>19694.627</v>
+        <v>22089.296</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>22089.296</v>
+        <v>26255.316</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>26255.316</v>
+        <v>29074.46</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>29074.46</v>
+        <v>29650.725</v>
       </c>
       <c r="H79" s="12" t="n">
         <v>9776.159</v>
@@ -15145,19 +15175,19 @@
         </is>
       </c>
       <c r="C80" s="22" t="n">
-        <v>9104.166999999999</v>
+        <v>8955.968000000001</v>
       </c>
       <c r="D80" s="22" t="n">
-        <v>8955.968000000001</v>
+        <v>8816.781999999999</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>8816.781999999999</v>
+        <v>9862.441999999999</v>
       </c>
       <c r="F80" s="22" t="n">
-        <v>9862.441999999999</v>
+        <v>12121.905</v>
       </c>
       <c r="G80" s="22" t="n">
-        <v>12121.905</v>
+        <v>11798.956</v>
       </c>
       <c r="H80" s="22" t="n">
         <v>7457.911</v>
@@ -15182,19 +15212,19 @@
         </is>
       </c>
       <c r="C81" s="22" t="n">
-        <v>14404.453</v>
+        <v>26716.302</v>
       </c>
       <c r="D81" s="22" t="n">
-        <v>26716.302</v>
+        <v>26662.788</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>26662.788</v>
+        <v>17950.309</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>17950.309</v>
+        <v>16741.156</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>16741.156</v>
+        <v>15176.709</v>
       </c>
       <c r="H81" s="22" t="n">
         <v>2578.257</v>
@@ -15218,7 +15248,7 @@
           <t>토지</t>
         </is>
       </c>
-      <c r="F82" s="22" t="n">
+      <c r="E82" s="22" t="n">
         <v>644.731</v>
       </c>
       <c r="H82" s="22" t="n">
@@ -15244,19 +15274,19 @@
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>11054.526</v>
+        <v>11894.061</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>11894.061</v>
+        <v>12185.318</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>12185.318</v>
+        <v>13097.016</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>13097.016</v>
+        <v>15167.649</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>15167.649</v>
+        <v>17642.443</v>
       </c>
       <c r="H83" s="22" t="n">
         <v>5049.248</v>
@@ -15280,7 +15310,7 @@
           <t>건설중인자산</t>
         </is>
       </c>
-      <c r="F84" s="22" t="n">
+      <c r="E84" s="22" t="n">
         <v>5168.003</v>
       </c>
       <c r="J84" s="22" t="n">
@@ -15300,19 +15330,19 @@
         </is>
       </c>
       <c r="C85" s="22" t="n">
-        <v>3317.475</v>
+        <v>3624.613</v>
       </c>
       <c r="D85" s="22" t="n">
-        <v>3624.613</v>
+        <v>3549.686</v>
       </c>
       <c r="E85" s="22" t="n">
-        <v>3549.686</v>
+        <v>5812.735</v>
       </c>
       <c r="F85" s="22" t="n">
-        <v>5812.735</v>
+        <v>4863.616</v>
       </c>
       <c r="G85" s="22" t="n">
-        <v>4863.616</v>
+        <v>3679.012</v>
       </c>
       <c r="H85" s="22" t="n">
         <v>0</v>
@@ -15337,19 +15367,19 @@
         </is>
       </c>
       <c r="C86" s="22" t="n">
-        <v>37880.622</v>
+        <v>51190.946</v>
       </c>
       <c r="D86" s="22" t="n">
-        <v>51190.946</v>
+        <v>51214.577</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>51214.577</v>
+        <v>46722.502</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>46722.502</v>
+        <v>48894.327</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>48894.327</v>
+        <v>48297.121</v>
       </c>
       <c r="H86" s="22" t="n">
         <v>15725.557</v>
@@ -15374,19 +15404,19 @@
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>1403.956</v>
+        <v>1565.479</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>1565.479</v>
+        <v>1831.062</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>1831.062</v>
+        <v>2018.177</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>2018.177</v>
+        <v>2109.37</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>2109.37</v>
+        <v>1963.839</v>
       </c>
       <c r="H87" s="22" t="n">
         <v>426.342</v>
@@ -15411,19 +15441,19 @@
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>1403.956</v>
+        <v>1565.479</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>1565.479</v>
+        <v>1831.062</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>1831.062</v>
+        <v>2018.177</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>2018.177</v>
+        <v>2109.37</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>2109.37</v>
+        <v>1963.839</v>
       </c>
       <c r="H88" s="22" t="n">
         <v>426.342</v>
@@ -15447,7 +15477,7 @@
           <t>투자유가증권</t>
         </is>
       </c>
-      <c r="F89" s="22" t="n">
+      <c r="E89" s="22" t="n">
         <v>820.74</v>
       </c>
       <c r="H89" s="22" t="n">
@@ -15472,7 +15502,7 @@
           <t>장기선급비용</t>
         </is>
       </c>
-      <c r="F90" s="22" t="n">
+      <c r="E90" s="22" t="n">
         <v>4822.678</v>
       </c>
       <c r="K90" s="22" t="n">
@@ -15488,7 +15518,7 @@
           <t>이연법인세자산</t>
         </is>
       </c>
-      <c r="F91" s="22" t="n">
+      <c r="E91" s="22" t="n">
         <v>1313.522</v>
       </c>
       <c r="H91" s="22" t="n">
@@ -15514,19 +15544,19 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>8023.827</v>
+        <v>7814.185</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>7814.185</v>
+        <v>7489.1</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>7489.1</v>
+        <v>7460.084</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>7460.084</v>
+        <v>7472.912</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>7472.912</v>
+        <v>8069.47</v>
       </c>
       <c r="H92" s="22" t="n">
         <v>1536.196</v>
@@ -15551,19 +15581,19 @@
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>-5.272</v>
+        <v>-5.212</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>-5.212</v>
+        <v>-5.172</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>-5.172</v>
+        <v>-5.004</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>-5.004</v>
+        <v>-4.944</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>-4.944</v>
+        <v>-4.884</v>
       </c>
       <c r="H93" s="22" t="n">
         <v>-5.964</v>
@@ -15588,19 +15618,19 @@
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>8018.554</v>
+        <v>7808.973</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>7808.973</v>
+        <v>7483.928</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>7483.928</v>
+        <v>7455.08</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>7455.08</v>
+        <v>7467.968</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>7467.968</v>
+        <v>8064.586</v>
       </c>
       <c r="H94" s="22" t="n">
         <v>2468.267</v>
@@ -15625,19 +15655,19 @@
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>47303.133</v>
+        <v>60565.398</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>60565.398</v>
+        <v>60529.567</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>60529.567</v>
+        <v>56195.76</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>56195.76</v>
+        <v>58471.666</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>58471.666</v>
+        <v>58325.547</v>
       </c>
       <c r="H95" s="12" t="n">
         <v>18620.168</v>
@@ -15662,19 +15692,19 @@
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>81001.024</v>
+        <v>80260.02499999999</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>80260.02499999999</v>
+        <v>82618.864</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>82618.864</v>
+        <v>82451.076</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>82451.076</v>
+        <v>87546.12699999999</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>87546.12699999999</v>
+        <v>87976.272</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>28396.327</v>
@@ -15699,19 +15729,19 @@
         </is>
       </c>
       <c r="C97" s="22" t="n">
-        <v>607.006</v>
+        <v>660.9299999999999</v>
       </c>
       <c r="D97" s="22" t="n">
-        <v>660.9299999999999</v>
+        <v>816.725</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>816.725</v>
+        <v>1245.523</v>
       </c>
       <c r="F97" s="22" t="n">
-        <v>1245.523</v>
+        <v>554.71</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>554.71</v>
+        <v>620.46</v>
       </c>
       <c r="H97" s="22" t="n">
         <v>1613.404</v>
@@ -15735,7 +15765,7 @@
           <t>설비관련 미지급금</t>
         </is>
       </c>
-      <c r="F98" s="22" t="n">
+      <c r="E98" s="22" t="n">
         <v>206.704</v>
       </c>
       <c r="J98" s="22" t="n">
@@ -15755,19 +15785,19 @@
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>6741.667</v>
+        <v>10675.668</v>
       </c>
       <c r="D99" s="22" t="n">
-        <v>10675.668</v>
+        <v>8255</v>
       </c>
       <c r="E99" s="22" t="n">
-        <v>8255</v>
+        <v>10687</v>
       </c>
       <c r="F99" s="22" t="n">
-        <v>10687</v>
+        <v>14742</v>
       </c>
       <c r="G99" s="22" t="n">
-        <v>14742</v>
+        <v>8136</v>
       </c>
       <c r="H99" s="22" t="n">
         <v>1451</v>
@@ -15792,19 +15822,19 @@
         </is>
       </c>
       <c r="C100" s="22" t="n">
-        <v>2668.38</v>
+        <v>3657.66</v>
       </c>
       <c r="D100" s="22" t="n">
-        <v>3657.66</v>
+        <v>5323.383</v>
       </c>
       <c r="E100" s="22" t="n">
-        <v>5323.383</v>
+        <v>4796.832</v>
       </c>
       <c r="F100" s="22" t="n">
-        <v>4796.832</v>
+        <v>4242.518</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>4242.518</v>
+        <v>5338.588</v>
       </c>
       <c r="H100" s="22" t="n">
         <v>918.082</v>
@@ -15828,7 +15858,7 @@
           <t>리스부채</t>
         </is>
       </c>
-      <c r="F101" s="22" t="n">
+      <c r="E101" s="22" t="n">
         <v>3101.105</v>
       </c>
       <c r="H101" s="22" t="n">
@@ -15854,19 +15884,19 @@
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>68.706</v>
+        <v>139.72</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>139.72</v>
+        <v>104.46</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>104.46</v>
+        <v>546.193</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>546.193</v>
+        <v>550.664</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>550.664</v>
+        <v>1525.234</v>
       </c>
       <c r="H102" s="22" t="n">
         <v>77.803</v>
@@ -15891,19 +15921,19 @@
         </is>
       </c>
       <c r="C103" s="22" t="n">
-        <v>6487.599</v>
+        <v>6801.252</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>6801.252</v>
+        <v>6588.892</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>6588.892</v>
+        <v>8658.592000000001</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>8658.592000000001</v>
+        <v>8898.355</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>8898.355</v>
+        <v>8705.008</v>
       </c>
       <c r="H103" s="22" t="n">
         <v>4420.646</v>
@@ -15924,929 +15954,945 @@
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>상여충당금</t>
-        </is>
-      </c>
-      <c r="C104" s="22" t="n">
-        <v>341.739</v>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>699.272</v>
+          <t>자산복구부채</t>
+        </is>
       </c>
       <c r="E104" s="22" t="n">
-        <v>367.872</v>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>772.41</v>
+        <v>0</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>376.674</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>353.18</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>390.795</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>451.171</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>663.426</v>
+        <v>41.385</v>
       </c>
       <c r="L104" s="22" t="n">
-        <v>772.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>임원 상여충당금</t>
+          <t>상여충당금</t>
         </is>
       </c>
       <c r="C105" s="22" t="n">
-        <v>0</v>
+        <v>699.272</v>
       </c>
       <c r="D105" s="22" t="n">
-        <v>0</v>
+        <v>367.872</v>
       </c>
       <c r="E105" s="22" t="n">
-        <v>0</v>
+        <v>772.41</v>
       </c>
       <c r="F105" s="22" t="n">
-        <v>36.8</v>
+        <v>376.674</v>
       </c>
       <c r="G105" s="22" t="n">
-        <v>0</v>
+        <v>757.588</v>
       </c>
       <c r="H105" s="22" t="n">
-        <v>1.35</v>
+        <v>353.18</v>
       </c>
       <c r="I105" s="22" t="n">
-        <v>6.75</v>
+        <v>390.795</v>
       </c>
       <c r="J105" s="22" t="n">
-        <v>4.5</v>
+        <v>451.171</v>
       </c>
       <c r="K105" s="22" t="n">
-        <v>53.235</v>
+        <v>663.426</v>
       </c>
       <c r="L105" s="22" t="n">
-        <v>36.8</v>
+        <v>772.41</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>Suspense Receipt</t>
-        </is>
+          <t>임원 상여충당금</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>36.8</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>2228.485</v>
+        <v>0</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>6.75</v>
       </c>
       <c r="J106" s="22" t="n">
-        <v>74.511</v>
+        <v>4.5</v>
       </c>
       <c r="K106" s="22" t="n">
-        <v>4538.451</v>
+        <v>53.235</v>
       </c>
       <c r="L106" s="22" t="n">
-        <v>2228.485</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
+          <t>가수금</t>
+        </is>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>2228.485</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>74.511</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>4538.451</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>2228.485</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="C107" s="22" t="n">
-        <v>20835.843</v>
-      </c>
-      <c r="D107" s="22" t="n">
+      <c r="C108" s="22" t="n">
         <v>11560.128</v>
       </c>
-      <c r="E107" s="22" t="n">
+      <c r="D108" s="22" t="n">
         <v>13343.426</v>
       </c>
-      <c r="F107" s="22" t="n">
+      <c r="E108" s="22" t="n">
         <v>7111.581</v>
       </c>
-      <c r="G107" s="22" t="n">
+      <c r="F108" s="22" t="n">
         <v>7550.549</v>
       </c>
-      <c r="H107" s="22" t="n">
+      <c r="G108" s="22" t="n">
+        <v>7412.555</v>
+      </c>
+      <c r="H108" s="22" t="n">
         <v>1277.474</v>
       </c>
-      <c r="I107" s="22" t="n">
+      <c r="I108" s="22" t="n">
         <v>1072.113</v>
       </c>
-      <c r="J107" s="22" t="n">
+      <c r="J108" s="22" t="n">
         <v>1117.777</v>
       </c>
-      <c r="K107" s="22" t="n">
+      <c r="K108" s="22" t="n">
         <v>2996.624</v>
       </c>
-      <c r="L107" s="22" t="n">
+      <c r="L108" s="22" t="n">
         <v>7111.581</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>유동부채 합계</t>
         </is>
       </c>
-      <c r="C108" s="12" t="n">
-        <v>37750.942</v>
-      </c>
-      <c r="D108" s="12" t="n">
+      <c r="C109" s="12" t="n">
         <v>34194.632</v>
       </c>
-      <c r="E108" s="12" t="n">
+      <c r="D109" s="12" t="n">
         <v>34799.76</v>
       </c>
-      <c r="F108" s="12" t="n">
+      <c r="E109" s="12" t="n">
         <v>33854.933</v>
       </c>
-      <c r="G108" s="12" t="n">
+      <c r="F109" s="12" t="n">
         <v>36915.473</v>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="G109" s="12" t="n">
+        <v>32536.822</v>
+      </c>
+      <c r="H109" s="12" t="n">
         <v>11309.298</v>
       </c>
-      <c r="I108" s="12" t="n">
+      <c r="I109" s="12" t="n">
         <v>9840.513999999999</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="J109" s="12" t="n">
         <v>10598.366</v>
       </c>
-      <c r="K108" s="12" t="n">
+      <c r="K109" s="12" t="n">
         <v>40347.49</v>
       </c>
-      <c r="L108" s="12" t="n">
+      <c r="L109" s="12" t="n">
         <v>33854.933</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>장기차입금</t>
-        </is>
-      </c>
-      <c r="C109" s="22" t="n">
-        <v>2542.612</v>
-      </c>
-      <c r="D109" s="22" t="n">
-        <v>4917.091</v>
-      </c>
-      <c r="E109" s="22" t="n">
-        <v>6553.073</v>
-      </c>
-      <c r="F109" s="22" t="n">
-        <v>5777.396</v>
-      </c>
-      <c r="G109" s="22" t="n">
-        <v>5067.428</v>
-      </c>
-      <c r="H109" s="22" t="n">
-        <v>3475.436</v>
-      </c>
-      <c r="I109" s="22" t="n">
-        <v>2662.253</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>3617.408</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <v>3154.471</v>
-      </c>
-      <c r="L109" s="22" t="n">
-        <v>5777.396</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>리스부채</t>
+          <t>장기차입금</t>
         </is>
       </c>
       <c r="C110" s="22" t="n">
-        <v>9857.245000000001</v>
+        <v>4917.091</v>
       </c>
       <c r="D110" s="22" t="n">
-        <v>10492.066</v>
+        <v>6553.073</v>
       </c>
       <c r="E110" s="22" t="n">
-        <v>10666.303</v>
+        <v>5777.396</v>
       </c>
       <c r="F110" s="22" t="n">
-        <v>11464.636</v>
+        <v>5067.428</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>13520.629</v>
+        <v>6448.828</v>
       </c>
       <c r="H110" s="22" t="n">
-        <v>4459.855</v>
+        <v>3475.436</v>
       </c>
       <c r="I110" s="22" t="n">
-        <v>4537.003</v>
+        <v>2662.253</v>
       </c>
       <c r="J110" s="22" t="n">
-        <v>5935.858</v>
+        <v>3617.408</v>
       </c>
       <c r="K110" s="22" t="n">
-        <v>6654.972</v>
+        <v>3154.471</v>
       </c>
       <c r="L110" s="22" t="n">
-        <v>11464.636</v>
+        <v>5777.396</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>자산복구부채</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="C111" s="22" t="n">
-        <v>832.576</v>
+        <v>10492.066</v>
       </c>
       <c r="D111" s="22" t="n">
-        <v>833.048</v>
+        <v>10666.303</v>
       </c>
       <c r="E111" s="22" t="n">
-        <v>833.521</v>
+        <v>11464.636</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>833.995</v>
+        <v>13520.629</v>
       </c>
       <c r="G111" s="22" t="n">
-        <v>834.4690000000001</v>
+        <v>15974.649</v>
       </c>
       <c r="H111" s="22" t="n">
-        <v>677.412</v>
+        <v>4459.855</v>
       </c>
       <c r="I111" s="22" t="n">
-        <v>680.274</v>
+        <v>4537.003</v>
       </c>
       <c r="J111" s="22" t="n">
-        <v>683.136</v>
+        <v>5935.858</v>
       </c>
       <c r="K111" s="22" t="n">
-        <v>828.955</v>
+        <v>6654.972</v>
       </c>
       <c r="L111" s="22" t="n">
-        <v>833.995</v>
+        <v>11464.636</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>주식급여 충당금</t>
+          <t>자산복구부채</t>
         </is>
       </c>
       <c r="C112" s="22" t="n">
-        <v>100.543</v>
+        <v>833.048</v>
       </c>
       <c r="D112" s="22" t="n">
-        <v>109.839</v>
+        <v>833.521</v>
       </c>
       <c r="E112" s="22" t="n">
-        <v>86.771</v>
+        <v>833.995</v>
       </c>
       <c r="F112" s="22" t="n">
-        <v>84.053</v>
+        <v>834.4690000000001</v>
       </c>
       <c r="G112" s="22" t="n">
-        <v>95.23399999999999</v>
+        <v>816.944</v>
       </c>
       <c r="H112" s="22" t="n">
-        <v>0</v>
+        <v>677.412</v>
       </c>
       <c r="I112" s="22" t="n">
-        <v>28.666</v>
+        <v>680.274</v>
       </c>
       <c r="J112" s="22" t="n">
-        <v>59.329</v>
+        <v>683.136</v>
       </c>
       <c r="K112" s="22" t="n">
-        <v>90.515</v>
+        <v>828.955</v>
       </c>
       <c r="L112" s="22" t="n">
-        <v>84.053</v>
+        <v>833.995</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
         <is>
-          <t>임원 퇴직위로 충당금</t>
+          <t>주식급여 충당금</t>
         </is>
       </c>
       <c r="C113" s="22" t="n">
-        <v>63.441</v>
+        <v>109.839</v>
       </c>
       <c r="D113" s="22" t="n">
-        <v>65.887</v>
+        <v>86.771</v>
       </c>
       <c r="E113" s="22" t="n">
-        <v>68.333</v>
+        <v>84.053</v>
       </c>
       <c r="F113" s="22" t="n">
-        <v>70.78</v>
+        <v>95.23399999999999</v>
       </c>
       <c r="G113" s="22" t="n">
-        <v>85.226</v>
+        <v>102.26</v>
+      </c>
+      <c r="H113" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="22" t="n">
+        <v>28.666</v>
       </c>
       <c r="J113" s="22" t="n">
-        <v>0</v>
+        <v>59.329</v>
       </c>
       <c r="K113" s="22" t="n">
-        <v>50.638</v>
+        <v>90.515</v>
       </c>
       <c r="L113" s="22" t="n">
-        <v>70.78</v>
+        <v>84.053</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여부채</t>
+          <t>임원 퇴직위로 충당금</t>
         </is>
       </c>
       <c r="C114" s="22" t="n">
-        <v>30</v>
+        <v>65.887</v>
       </c>
       <c r="D114" s="22" t="n">
-        <v>31.5</v>
+        <v>68.333</v>
       </c>
       <c r="E114" s="22" t="n">
-        <v>32.25</v>
+        <v>70.78</v>
       </c>
       <c r="F114" s="22" t="n">
-        <v>33.05</v>
+        <v>85.226</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>33.95</v>
+        <v>88.072</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="K114" s="22" t="n">
-        <v>30</v>
+        <v>50.638</v>
       </c>
       <c r="L114" s="22" t="n">
-        <v>33.05</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
+          <t>퇴직급여부채</t>
+        </is>
+      </c>
+      <c r="C115" s="22" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="E115" s="22" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="F115" s="22" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="G115" s="22" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="K115" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="L115" s="22" t="n">
+        <v>33.05</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="C115" s="22" t="n">
-        <v>4.553</v>
-      </c>
-      <c r="D115" s="22" t="n">
+      <c r="C116" s="22" t="n">
         <v>4.06</v>
       </c>
-      <c r="E115" s="22" t="n">
+      <c r="D116" s="22" t="n">
         <v>3.782</v>
       </c>
-      <c r="F115" s="22" t="n">
+      <c r="E116" s="22" t="n">
         <v>3.076</v>
       </c>
-      <c r="G115" s="22" t="n">
+      <c r="F116" s="22" t="n">
         <v>4.196</v>
       </c>
-      <c r="H115" s="22" t="n">
+      <c r="G116" s="22" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="H116" s="22" t="n">
         <v>24.395</v>
       </c>
-      <c r="I115" s="22" t="n">
+      <c r="I116" s="22" t="n">
         <v>21.258</v>
       </c>
-      <c r="J115" s="22" t="n">
+      <c r="J116" s="22" t="n">
         <v>9.138999999999999</v>
       </c>
-      <c r="K115" s="22" t="n">
+      <c r="K116" s="22" t="n">
         <v>5.046</v>
       </c>
-      <c r="L115" s="22" t="n">
+      <c r="L116" s="22" t="n">
         <v>3.076</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>비유동부채 합계</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>13430.972</v>
-      </c>
-      <c r="D116" s="12" t="n">
-        <v>16453.494</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>18244.036</v>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>18266.988</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>19641.134</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>8637.099</v>
-      </c>
-      <c r="I116" s="12" t="n">
-        <v>7929.456</v>
-      </c>
-      <c r="J116" s="12" t="n">
-        <v>10304.872</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>10814.598</v>
-      </c>
-      <c r="L116" s="12" t="n">
-        <v>18266.988</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
+          <t>비유동부채 합계</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>16453.494</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>18244.036</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>18266.988</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>19641.134</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>23470.535</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>8637.099</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>7929.456</v>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>10304.872</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>10814.598</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>18266.988</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
           <t>부채 합계</t>
         </is>
       </c>
-      <c r="C117" s="12" t="n">
-        <v>51181.915</v>
-      </c>
-      <c r="D117" s="12" t="n">
+      <c r="C118" s="12" t="n">
         <v>50648.126</v>
       </c>
-      <c r="E117" s="12" t="n">
+      <c r="D118" s="12" t="n">
         <v>53043.797</v>
       </c>
-      <c r="F117" s="12" t="n">
+      <c r="E118" s="12" t="n">
         <v>52121.922</v>
       </c>
-      <c r="G117" s="12" t="n">
+      <c r="F118" s="12" t="n">
         <v>56556.608</v>
       </c>
-      <c r="H117" s="12" t="n">
+      <c r="G118" s="12" t="n">
+        <v>56007.357</v>
+      </c>
+      <c r="H118" s="12" t="n">
         <v>19946.398</v>
       </c>
-      <c r="I117" s="12" t="n">
+      <c r="I118" s="12" t="n">
         <v>17769.97</v>
       </c>
-      <c r="J117" s="12" t="n">
+      <c r="J118" s="12" t="n">
         <v>20903.238</v>
       </c>
-      <c r="K117" s="12" t="n">
+      <c r="K118" s="12" t="n">
         <v>51162.089</v>
       </c>
-      <c r="L117" s="12" t="n">
+      <c r="L118" s="12" t="n">
         <v>52121.922</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>자본금</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="n">
-        <v>11283.167</v>
-      </c>
-      <c r="D118" s="22" t="n">
-        <v>11283.167</v>
-      </c>
-      <c r="E118" s="22" t="n">
-        <v>11283.167</v>
-      </c>
-      <c r="F118" s="22" t="n">
-        <v>11283.167</v>
-      </c>
-      <c r="G118" s="22" t="n">
-        <v>11283.167</v>
-      </c>
-      <c r="H118" s="22" t="n">
-        <v>2256.921</v>
-      </c>
-      <c r="I118" s="22" t="n">
-        <v>2256.921</v>
-      </c>
-      <c r="J118" s="22" t="n">
-        <v>2256.921</v>
-      </c>
-      <c r="K118" s="22" t="n">
-        <v>11283.167</v>
-      </c>
-      <c r="L118" s="22" t="n">
-        <v>11283.167</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="C119" s="22" t="n">
-        <v>10577.023</v>
+        <v>11283.167</v>
       </c>
       <c r="D119" s="22" t="n">
-        <v>10649.91</v>
+        <v>11283.167</v>
       </c>
       <c r="E119" s="22" t="n">
-        <v>10649.91</v>
+        <v>11283.167</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>10649.91</v>
+        <v>11283.167</v>
       </c>
       <c r="G119" s="22" t="n">
-        <v>10649.91</v>
+        <v>11283.167</v>
       </c>
       <c r="H119" s="22" t="n">
-        <v>1366.388</v>
+        <v>2256.921</v>
       </c>
       <c r="I119" s="22" t="n">
-        <v>1378.747</v>
+        <v>2256.921</v>
       </c>
       <c r="J119" s="22" t="n">
-        <v>1478.896</v>
+        <v>2256.921</v>
       </c>
       <c r="K119" s="22" t="n">
-        <v>10577.023</v>
+        <v>11283.167</v>
       </c>
       <c r="L119" s="22" t="n">
-        <v>10649.91</v>
+        <v>11283.167</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="C120" s="22" t="n">
-        <v>8692.218999999999</v>
+        <v>10649.91</v>
       </c>
       <c r="D120" s="22" t="n">
-        <v>8389.834999999999</v>
+        <v>10649.91</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>8465.573</v>
+        <v>10649.91</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>9232.621999999999</v>
+        <v>10649.91</v>
       </c>
       <c r="G120" s="22" t="n">
-        <v>9887.088</v>
+        <v>10707.682</v>
       </c>
       <c r="H120" s="22" t="n">
-        <v>5289.923</v>
+        <v>1366.388</v>
       </c>
       <c r="I120" s="22" t="n">
-        <v>5847.035</v>
+        <v>1378.747</v>
       </c>
       <c r="J120" s="22" t="n">
-        <v>6372.974</v>
+        <v>1478.896</v>
       </c>
       <c r="K120" s="22" t="n">
-        <v>9177.688</v>
+        <v>10577.023</v>
       </c>
       <c r="L120" s="22" t="n">
-        <v>9232.621999999999</v>
+        <v>10649.91</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
+          <t>이익잉여금</t>
+        </is>
+      </c>
+      <c r="C121" s="22" t="n">
+        <v>8389.834999999999</v>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>8465.573</v>
+      </c>
+      <c r="E121" s="22" t="n">
+        <v>9232.621999999999</v>
+      </c>
+      <c r="F121" s="22" t="n">
+        <v>9887.088</v>
+      </c>
+      <c r="G121" s="22" t="n">
+        <v>10935.134</v>
+      </c>
+      <c r="H121" s="22" t="n">
+        <v>5289.923</v>
+      </c>
+      <c r="I121" s="22" t="n">
+        <v>5847.035</v>
+      </c>
+      <c r="J121" s="22" t="n">
+        <v>6372.974</v>
+      </c>
+      <c r="K121" s="22" t="n">
+        <v>9177.688</v>
+      </c>
+      <c r="L121" s="22" t="n">
+        <v>9232.621999999999</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
           <t>자기주식</t>
         </is>
       </c>
-      <c r="C121" s="22" t="n">
-        <v>-1106.683</v>
-      </c>
-      <c r="D121" s="22" t="n">
+      <c r="C122" s="22" t="n">
         <v>-1094.615</v>
       </c>
-      <c r="E121" s="22" t="n">
+      <c r="D122" s="22" t="n">
         <v>-1094.048</v>
       </c>
-      <c r="F121" s="22" t="n">
+      <c r="E122" s="22" t="n">
         <v>-1093.229</v>
       </c>
-      <c r="G121" s="22" t="n">
+      <c r="F122" s="22" t="n">
         <v>-1092.765</v>
       </c>
-      <c r="H121" s="22" t="n">
+      <c r="G122" s="22" t="n">
+        <v>-1078.577</v>
+      </c>
+      <c r="H122" s="22" t="n">
         <v>-600.029</v>
       </c>
-      <c r="I121" s="22" t="n">
+      <c r="I122" s="22" t="n">
         <v>-1145.475</v>
       </c>
-      <c r="J121" s="22" t="n">
+      <c r="J122" s="22" t="n">
         <v>-1119.643</v>
       </c>
-      <c r="K121" s="22" t="n">
+      <c r="K122" s="22" t="n">
         <v>-1106.853</v>
       </c>
-      <c r="L121" s="22" t="n">
+      <c r="L122" s="22" t="n">
         <v>-1093.229</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>주주자본 합계</t>
         </is>
       </c>
-      <c r="C122" s="12" t="n">
-        <v>29445.726</v>
-      </c>
-      <c r="D122" s="12" t="n">
+      <c r="C123" s="12" t="n">
         <v>29228.297</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="D123" s="12" t="n">
         <v>29304.602</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="E123" s="12" t="n">
         <v>30072.47</v>
       </c>
-      <c r="G122" s="12" t="n">
+      <c r="F123" s="12" t="n">
         <v>30727.4</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="G123" s="12" t="n">
+        <v>31847.406</v>
+      </c>
+      <c r="H123" s="12" t="n">
         <v>8313.203</v>
       </c>
-      <c r="I122" s="12" t="n">
+      <c r="I123" s="12" t="n">
         <v>8337.227999999999</v>
       </c>
-      <c r="J122" s="12" t="n">
+      <c r="J123" s="12" t="n">
         <v>8989.147000000001</v>
       </c>
-      <c r="K122" s="12" t="n">
+      <c r="K123" s="12" t="n">
         <v>29931.026</v>
       </c>
-      <c r="L122" s="12" t="n">
+      <c r="L123" s="12" t="n">
         <v>30072.47</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C123" s="22" t="n">
-        <v>156.575</v>
-      </c>
-      <c r="D123" s="22" t="n">
-        <v>155.266</v>
-      </c>
-      <c r="E123" s="22" t="n">
-        <v>32.906</v>
-      </c>
-      <c r="F123" s="22" t="n">
-        <v>14.625</v>
-      </c>
-      <c r="G123" s="22" t="n">
-        <v>15.577</v>
-      </c>
-      <c r="H123" s="22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>4.632</v>
-      </c>
-      <c r="J123" s="22" t="n">
-        <v>133.781</v>
-      </c>
-      <c r="K123" s="22" t="n">
-        <v>112.597</v>
-      </c>
-      <c r="L123" s="22" t="n">
-        <v>14.625</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>해외사업환산조정</t>
+          <t>기타유가증권 평가차액</t>
         </is>
       </c>
       <c r="C124" s="22" t="n">
-        <v>10.163</v>
+        <v>155.266</v>
       </c>
       <c r="D124" s="22" t="n">
-        <v>11.521</v>
+        <v>32.906</v>
       </c>
       <c r="E124" s="22" t="n">
-        <v>13.397</v>
+        <v>14.625</v>
       </c>
       <c r="F124" s="22" t="n">
-        <v>13.893</v>
+        <v>15.577</v>
       </c>
       <c r="G124" s="22" t="n">
-        <v>14.47</v>
+        <v>13.655</v>
       </c>
       <c r="H124" s="22" t="n">
-        <v>4.468</v>
+        <v>0.03</v>
       </c>
       <c r="I124" s="22" t="n">
-        <v>7.024</v>
+        <v>4.632</v>
       </c>
       <c r="J124" s="22" t="n">
-        <v>11.89</v>
+        <v>133.781</v>
       </c>
       <c r="K124" s="22" t="n">
-        <v>11.643</v>
+        <v>112.597</v>
       </c>
       <c r="L124" s="22" t="n">
-        <v>13.893</v>
+        <v>14.625</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>이연헤지손익</t>
+          <t>해외사업환산조정</t>
         </is>
       </c>
       <c r="C125" s="22" t="n">
-        <v>-0.858</v>
+        <v>11.521</v>
       </c>
       <c r="D125" s="22" t="n">
-        <v>5.228</v>
+        <v>13.397</v>
       </c>
       <c r="E125" s="22" t="n">
-        <v>6.9</v>
+        <v>13.893</v>
       </c>
       <c r="F125" s="22" t="n">
-        <v>0.289</v>
+        <v>14.47</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>2.548</v>
+        <v>13.221</v>
       </c>
       <c r="H125" s="22" t="n">
-        <v>0</v>
+        <v>4.468</v>
       </c>
       <c r="I125" s="22" t="n">
-        <v>-0.175</v>
+        <v>7.024</v>
       </c>
       <c r="J125" s="22" t="n">
-        <v>0.183</v>
+        <v>11.89</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>0.011</v>
+        <v>11.643</v>
       </c>
       <c r="L125" s="22" t="n">
-        <v>0.289</v>
+        <v>13.893</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>기타포괄손익누계액 합계</t>
+          <t>이연헤지손익</t>
         </is>
       </c>
       <c r="C126" s="22" t="n">
-        <v>165.881</v>
+        <v>5.228</v>
       </c>
       <c r="D126" s="22" t="n">
-        <v>172.016</v>
+        <v>6.9</v>
       </c>
       <c r="E126" s="22" t="n">
-        <v>53.204</v>
+        <v>0.289</v>
       </c>
       <c r="F126" s="22" t="n">
-        <v>28.808</v>
+        <v>2.548</v>
       </c>
       <c r="G126" s="22" t="n">
-        <v>32.596</v>
+        <v>-135.823</v>
       </c>
       <c r="H126" s="22" t="n">
-        <v>4.499</v>
+        <v>0</v>
       </c>
       <c r="I126" s="22" t="n">
-        <v>11.482</v>
+        <v>-0.175</v>
       </c>
       <c r="J126" s="22" t="n">
-        <v>145.855</v>
+        <v>0.183</v>
       </c>
       <c r="K126" s="22" t="n">
-        <v>124.253</v>
+        <v>0.011</v>
       </c>
       <c r="L126" s="22" t="n">
-        <v>28.808</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
+          <t>기타포괄손익누계액 합계</t>
+        </is>
+      </c>
+      <c r="C127" s="22" t="n">
+        <v>172.016</v>
+      </c>
+      <c r="D127" s="22" t="n">
+        <v>53.204</v>
+      </c>
+      <c r="E127" s="22" t="n">
+        <v>28.808</v>
+      </c>
+      <c r="F127" s="22" t="n">
+        <v>32.596</v>
+      </c>
+      <c r="G127" s="22" t="n">
+        <v>-108.946</v>
+      </c>
+      <c r="H127" s="22" t="n">
+        <v>4.499</v>
+      </c>
+      <c r="I127" s="22" t="n">
+        <v>11.482</v>
+      </c>
+      <c r="J127" s="22" t="n">
+        <v>145.855</v>
+      </c>
+      <c r="K127" s="22" t="n">
+        <v>124.253</v>
+      </c>
+      <c r="L127" s="22" t="n">
+        <v>28.808</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
           <t>비지배지분</t>
         </is>
       </c>
-      <c r="C127" s="22" t="n">
-        <v>207.501</v>
-      </c>
-      <c r="D127" s="22" t="n">
+      <c r="C128" s="22" t="n">
         <v>211.584</v>
       </c>
-      <c r="E127" s="22" t="n">
+      <c r="D128" s="22" t="n">
         <v>217.259</v>
       </c>
-      <c r="F127" s="22" t="n">
+      <c r="E128" s="22" t="n">
         <v>227.875</v>
       </c>
-      <c r="G127" s="22" t="n">
+      <c r="F128" s="22" t="n">
         <v>229.521</v>
       </c>
-      <c r="H127" s="22" t="n">
+      <c r="G128" s="22" t="n">
+        <v>230.454</v>
+      </c>
+      <c r="H128" s="22" t="n">
         <v>132.225</v>
       </c>
-      <c r="I127" s="22" t="n">
+      <c r="I128" s="22" t="n">
         <v>137.428</v>
       </c>
-      <c r="J127" s="22" t="n">
+      <c r="J128" s="22" t="n">
         <v>186.206</v>
       </c>
-      <c r="K127" s="22" t="n">
+      <c r="K128" s="22" t="n">
         <v>202.102</v>
       </c>
-      <c r="L127" s="22" t="n">
+      <c r="L128" s="22" t="n">
         <v>227.875</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>순자산 합계</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="n">
-        <v>29819.109</v>
-      </c>
-      <c r="D128" s="12" t="n">
-        <v>29611.899</v>
-      </c>
-      <c r="E128" s="12" t="n">
-        <v>29575.067</v>
-      </c>
-      <c r="F128" s="12" t="n">
-        <v>30329.154</v>
-      </c>
-      <c r="G128" s="12" t="n">
-        <v>30989.518</v>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>8449.929</v>
-      </c>
-      <c r="I128" s="12" t="n">
-        <v>8486.138999999999</v>
-      </c>
-      <c r="J128" s="12" t="n">
-        <v>9321.209000000001</v>
-      </c>
-      <c r="K128" s="12" t="n">
-        <v>30257.381</v>
-      </c>
-      <c r="L128" s="12" t="n">
-        <v>30329.154</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
+          <t>순자산 합계</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="n">
+        <v>29611.899</v>
+      </c>
+      <c r="D129" s="12" t="n">
+        <v>29575.067</v>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>30329.154</v>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>30989.518</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>31968.915</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>8449.929</v>
+      </c>
+      <c r="I129" s="12" t="n">
+        <v>8486.138999999999</v>
+      </c>
+      <c r="J129" s="12" t="n">
+        <v>9321.209000000001</v>
+      </c>
+      <c r="K129" s="12" t="n">
+        <v>30257.381</v>
+      </c>
+      <c r="L129" s="12" t="n">
+        <v>30329.154</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
           <t>부채·순자산 합계</t>
         </is>
       </c>
-      <c r="C129" s="12" t="n">
-        <v>81001.024</v>
-      </c>
-      <c r="D129" s="12" t="n">
+      <c r="C130" s="12" t="n">
         <v>80260.02499999999</v>
       </c>
-      <c r="E129" s="12" t="n">
+      <c r="D130" s="12" t="n">
         <v>82618.864</v>
       </c>
-      <c r="F129" s="12" t="n">
+      <c r="E130" s="12" t="n">
         <v>82451.076</v>
       </c>
-      <c r="G129" s="12" t="n">
+      <c r="F130" s="12" t="n">
         <v>87546.12699999999</v>
       </c>
-      <c r="H129" s="12" t="n">
+      <c r="G130" s="12" t="n">
+        <v>87976.272</v>
+      </c>
+      <c r="H130" s="12" t="n">
         <v>28396.327</v>
       </c>
-      <c r="I129" s="12" t="n">
+      <c r="I130" s="12" t="n">
         <v>26256.109</v>
       </c>
-      <c r="J129" s="12" t="n">
+      <c r="J130" s="12" t="n">
         <v>30224.447</v>
       </c>
-      <c r="K129" s="12" t="n">
+      <c r="K130" s="12" t="n">
         <v>81419.47</v>
       </c>
-      <c r="L129" s="12" t="n">
+      <c r="L130" s="12" t="n">
         <v>82451.076</v>
       </c>
     </row>
@@ -16937,6 +16983,1143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C111"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>사쿠라인터넷 섹터·사업 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>guide · FY27 init</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>450</v>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B9" s="59" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B10" s="59" t="n">
+        <v>21.24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>guide · FY27 now</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="n"/>
+      <c r="C12" s="54" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="n">
+        <v>455</v>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B18" s="59" t="n">
+        <v>37.46</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>guide · 상반기 init</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B22" s="57" t="n">
+        <v>210</v>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B24" s="59" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>guide · 상반기 now</t>
+        </is>
+      </c>
+      <c r="B26" s="54" t="n"/>
+      <c r="C26" s="54" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C27" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B28" s="57" t="n">
+        <v>225</v>
+      </c>
+      <c r="C28" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B29" s="57" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B30" s="57" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B32" s="59" t="n">
+        <v>34.97</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="54" t="inlineStr">
+        <is>
+          <t>guide · 2Q implied</t>
+        </is>
+      </c>
+      <c r="B34" s="54" t="n"/>
+      <c r="C34" s="54" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B35" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C35" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B36" s="59" t="n">
+        <v>113.66</v>
+      </c>
+      <c r="C36" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B37" s="59" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B38" s="59" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B39" s="59" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="54" t="inlineStr">
+        <is>
+          <t>guide · 하반기 implied</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="n"/>
+      <c r="C41" s="54" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B43" s="57" t="n">
+        <v>230</v>
+      </c>
+      <c r="C43" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B44" s="57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B45" s="57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="54" t="inlineStr">
+        <is>
+          <t>guide · FY27 new</t>
+        </is>
+      </c>
+      <c r="B47" s="54" t="n"/>
+      <c r="C47" s="54" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B48" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C48" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B49" s="57" t="n">
+        <v>466</v>
+      </c>
+      <c r="C49" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B50" s="57" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B51" s="57" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B52" s="59" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B53" s="59" t="n">
+        <v>63.68</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="54" t="inlineStr">
+        <is>
+          <t>guide · 상반기 실적</t>
+        </is>
+      </c>
+      <c r="B55" s="54" t="n"/>
+      <c r="C55" s="54" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B56" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C56" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B57" s="59" t="n">
+        <v>228.27</v>
+      </c>
+      <c r="C57" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B58" s="59" t="n">
+        <v>29.63</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B59" s="59" t="n">
+        <v>30.13</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B60" s="59" t="n">
+        <v>19.03</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B61" s="59" t="n">
+        <v>47.55</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="54" t="inlineStr">
+        <is>
+          <t>guide · 하반기 implied new</t>
+        </is>
+      </c>
+      <c r="B63" s="54" t="n"/>
+      <c r="C63" s="54" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B64" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C64" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B65" s="59" t="n">
+        <v>237.72</v>
+      </c>
+      <c r="C65" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B66" s="59" t="n">
+        <v>11.36</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="56" t="inlineStr">
+        <is>
+          <t>ord</t>
+        </is>
+      </c>
+      <c r="B67" s="59" t="n">
+        <v>8.859999999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B68" s="59" t="n">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="54" t="inlineStr">
+        <is>
+          <t>cons · 2Q</t>
+        </is>
+      </c>
+      <c r="B70" s="54" t="n"/>
+      <c r="C70" s="54" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B71" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C71" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B72" s="59" t="n">
+        <v>117.03</v>
+      </c>
+      <c r="C72" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="56" t="inlineStr">
+        <is>
+          <t>매출 lo</t>
+        </is>
+      </c>
+      <c r="B73" s="59" t="n">
+        <v>113.9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="56" t="inlineStr">
+        <is>
+          <t>매출 hi</t>
+        </is>
+      </c>
+      <c r="B74" s="59" t="n">
+        <v>120.15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="56" t="inlineStr">
+        <is>
+          <t>매출 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B75" s="57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B76" s="59" t="n">
+        <v>36.93</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="56" t="inlineStr">
+        <is>
+          <t>EPS 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B77" s="57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="54" t="inlineStr">
+        <is>
+          <t>cons · FY27</t>
+        </is>
+      </c>
+      <c r="B79" s="54" t="n"/>
+      <c r="C79" s="54" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B80" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C80" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B81" s="59" t="n">
+        <v>476.77</v>
+      </c>
+      <c r="C81" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="56" t="inlineStr">
+        <is>
+          <t>매출 lo</t>
+        </is>
+      </c>
+      <c r="B82" s="57" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="56" t="inlineStr">
+        <is>
+          <t>매출 hi</t>
+        </is>
+      </c>
+      <c r="B83" s="59" t="n">
+        <v>487.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B84" s="59" t="n">
+        <v>80.06999999999999</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="56" t="inlineStr">
+        <is>
+          <t>EPS lo</t>
+        </is>
+      </c>
+      <c r="B85" s="57" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="56" t="inlineStr">
+        <is>
+          <t>EPS hi</t>
+        </is>
+      </c>
+      <c r="B86" s="59" t="n">
+        <v>147.06</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="56" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B87" s="57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="54" t="inlineStr">
+        <is>
+          <t>cons · FY28</t>
+        </is>
+      </c>
+      <c r="B89" s="54" t="n"/>
+      <c r="C89" s="54" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B90" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C90" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B91" s="59" t="n">
+        <v>609.74</v>
+      </c>
+      <c r="C91" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B92" s="59" t="n">
+        <v>173.4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="56" t="inlineStr">
+        <is>
+          <t>EPS lo</t>
+        </is>
+      </c>
+      <c r="B93" s="59" t="n">
+        <v>61.39</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="56" t="inlineStr">
+        <is>
+          <t>EPS hi</t>
+        </is>
+      </c>
+      <c r="B94" s="59" t="n">
+        <v>362.92</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="56" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B95" s="57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="54" t="inlineStr">
+        <is>
+          <t>cons · tp</t>
+        </is>
+      </c>
+      <c r="B97" s="54" t="n"/>
+      <c r="C97" s="54" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B98" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C98" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="56" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="B99" s="57" t="n">
+        <v>5473</v>
+      </c>
+      <c r="C99" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="56" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="B100" s="57" t="n">
+        <v>6870</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="56" t="inlineStr">
+        <is>
+          <t>lo</t>
+        </is>
+      </c>
+      <c r="B101" s="57" t="n">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="56" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B102" s="57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="54" t="inlineStr">
+        <is>
+          <t>cons · 3Q</t>
+        </is>
+      </c>
+      <c r="B104" s="54" t="n"/>
+      <c r="C104" s="54" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B105" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C105" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B106" s="59" t="n">
+        <v>120.33</v>
+      </c>
+      <c r="C106" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="56" t="inlineStr">
+        <is>
+          <t>매출 lo</t>
+        </is>
+      </c>
+      <c r="B107" s="59" t="n">
+        <v>116.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="56" t="inlineStr">
+        <is>
+          <t>매출 hi</t>
+        </is>
+      </c>
+      <c r="B108" s="59" t="n">
+        <v>124.16</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="56" t="inlineStr">
+        <is>
+          <t>매출 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B109" s="57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B110" s="59" t="n">
+        <v>40.86</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="56" t="inlineStr">
+        <is>
+          <t>EPS 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B111" s="57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16953,17 +18136,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -16972,272 +18155,272 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2027년 3월 결산기 1분기 결산단신</t>
+          <t>2027년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120260728500696.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120261027556964.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 연간 결산단신</t>
+          <t>2027년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120260427511113.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120260728500696.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 3분기 결산단신</t>
+          <t>2026년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120260129541884.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120260427511113.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 2분기 결산단신</t>
+          <t>2026년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120251027579530.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120260129541884.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 1분기 결산단신</t>
+          <t>2026년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120250728521679.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120251027579530.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 연간 결산단신</t>
+          <t>2026년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120250425523471.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120250728521679.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 3분기 결산단신</t>
+          <t>2025년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120250131559289.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120250425523471.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 2분기 결산단신</t>
+          <t>2025년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120241028503689.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120250131559289.pdf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 1분기 결산단신</t>
+          <t>2025년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120240704544618.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120241028503689.pdf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 연간 결산단신</t>
+          <t>2025년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120240416571384.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120240704544618.pdf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 3분기 결산단신</t>
+          <t>2024년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120240105511512.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120240416571384.pdf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 2분기 결산단신</t>
+          <t>2024년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120230925558018.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120240105511512.pdf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 1분기 결산단신</t>
+          <t>2024년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120230718523601.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120230925558018.pdf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023년 3월 결산기 연간 결산단신</t>
+          <t>2024년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120230315531230.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120230718523601.pdf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023년 3월 결산기 3분기 결산단신</t>
+          <t>2023년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120230119591013.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120230315531230.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023년 3월 결산기 2분기 결산단신</t>
+          <t>2023년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/37780/140120221018545653.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/37780/140120230119591013.pdf</t>
         </is>
       </c>
     </row>
